--- a/SerieABook.xlsx
+++ b/SerieABook.xlsx
@@ -1,21 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10110"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10208"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/solomonkalumamcharo/Desktop/Woolwich_Computing_Incorporated/Prime:Rare Cards/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/solomonkalumamcharo/Desktop/Desktop - Solomon’s MacBook Pro/Woolwich_Computing_Incorporated/Prime:Rare Cards/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BA285A47-9314-E945-8148-780F6E473480}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EE36A1B3-0E87-1447-8752-910BA17BBCD8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="740" windowWidth="30240" windowHeight="18900" xr2:uid="{8241BB8E-B7B9-3649-BB80-60B5D1E09FB7}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="17920" xr2:uid="{8241BB8E-B7B9-3649-BB80-60B5D1E09FB7}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4180" uniqueCount="866">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4182" uniqueCount="868">
   <si>
     <t>CAM</t>
   </si>
@@ -2634,6 +2634,12 @@
   </si>
   <si>
     <t>Finesse_Shot</t>
+  </si>
+  <si>
+    <t>develle_mcharo_passing</t>
+  </si>
+  <si>
+    <t>mcharo_develle_ln_price</t>
   </si>
 </sst>
 </file>
@@ -2641,7 +2647,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="170" formatCode="0.0"/>
+    <numFmt numFmtId="164" formatCode="0.0"/>
   </numFmts>
   <fonts count="1" x14ac:knownFonts="1">
     <font>
@@ -2675,14 +2681,20 @@
   <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="170" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="4">
+  <dxfs count="6">
     <dxf>
-      <numFmt numFmtId="170" formatCode="0.0"/>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="0.0"/>
     </dxf>
     <dxf>
       <numFmt numFmtId="19" formatCode="m/d/yy"/>
@@ -2707,14 +2719,14 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{C4516932-BF35-AB46-BB78-4EE644947E92}" name="Table1" displayName="Table1" ref="A1:DJ101" totalsRowShown="0">
-  <autoFilter ref="A1:DJ101" xr:uid="{C4516932-BF35-AB46-BB78-4EE644947E92}"/>
-  <tableColumns count="114">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{C4516932-BF35-AB46-BB78-4EE644947E92}" name="Table1" displayName="Table1" ref="A1:DL101" totalsRowShown="0">
+  <autoFilter ref="A1:DL101" xr:uid="{C4516932-BF35-AB46-BB78-4EE644947E92}"/>
+  <tableColumns count="116">
     <tableColumn id="1" xr3:uid="{85B23AFD-1DB8-4842-AD9A-92BE88FD3427}" name="player_id"/>
     <tableColumn id="2" xr3:uid="{08C8C578-E1A3-3648-B6AC-D2977C383186}" name="player_url"/>
     <tableColumn id="3" xr3:uid="{F9747B7A-03E9-554F-B763-7D96085A2EC9}" name="fifa_version"/>
     <tableColumn id="4" xr3:uid="{34A9B9AB-9F21-604C-92B9-4E84DEFAE6BF}" name="fifa_update"/>
-    <tableColumn id="5" xr3:uid="{C6FC4A66-7164-2A44-A88A-684C4F6D78D5}" name="fifa_update_date" dataDxfId="3"/>
+    <tableColumn id="5" xr3:uid="{C6FC4A66-7164-2A44-A88A-684C4F6D78D5}" name="fifa_update_date" dataDxfId="5"/>
     <tableColumn id="6" xr3:uid="{66A5D89A-0471-CF4D-A505-E1C39E4780BC}" name="short_name"/>
     <tableColumn id="115" xr3:uid="{03F078E7-7A85-7A43-96C9-2C3EB658B846}" name="Defender"/>
     <tableColumn id="114" xr3:uid="{E1EC0CD0-A474-7B43-9232-37F69714ECEF}" name="Midfielder"/>
@@ -2725,7 +2737,7 @@
     <tableColumn id="11" xr3:uid="{4ADB9E48-A383-7643-845C-E6C63E39F51D}" name="value_eur"/>
     <tableColumn id="12" xr3:uid="{0D67B3DC-E836-FD48-BDC7-28C02C4C458C}" name="wage_eur"/>
     <tableColumn id="13" xr3:uid="{E95E9085-AAD5-2E4D-85BF-3467767A1E85}" name="age"/>
-    <tableColumn id="14" xr3:uid="{DA776153-FE84-DD4B-BF1C-4B70651D7245}" name="dob" dataDxfId="2"/>
+    <tableColumn id="14" xr3:uid="{DA776153-FE84-DD4B-BF1C-4B70651D7245}" name="dob" dataDxfId="4"/>
     <tableColumn id="15" xr3:uid="{D7F3FAEC-2672-A846-A471-3BFA569FCC40}" name="height_cm"/>
     <tableColumn id="16" xr3:uid="{0CD9B065-227D-664E-A88E-3BA32208DDC3}" name="weight_kg"/>
     <tableColumn id="17" xr3:uid="{21713332-16B4-1247-A235-437185337F08}" name="league_id"/>
@@ -2736,7 +2748,7 @@
     <tableColumn id="22" xr3:uid="{E61963D0-E26B-3A4B-8EFE-8DC20920C14A}" name="club_position"/>
     <tableColumn id="23" xr3:uid="{24B78E99-CD82-EE44-8731-0B3EFE56A380}" name="club_jersey_number"/>
     <tableColumn id="24" xr3:uid="{9E8971F7-4352-3441-B3B3-4005E13F8CE9}" name="club_loaned_from"/>
-    <tableColumn id="25" xr3:uid="{9084F5E4-1614-BF41-9ECF-A6AE318C8224}" name="club_joined_date" dataDxfId="1"/>
+    <tableColumn id="25" xr3:uid="{9084F5E4-1614-BF41-9ECF-A6AE318C8224}" name="club_joined_date" dataDxfId="3"/>
     <tableColumn id="26" xr3:uid="{1D719DB8-A3CE-F741-8AE8-21945BFA8768}" name="club_contract_valid_until_year"/>
     <tableColumn id="27" xr3:uid="{1C639A62-8B4A-9842-8178-4F66B6E6D8C3}" name="nationality_id"/>
     <tableColumn id="28" xr3:uid="{523B063C-B85B-034B-864B-A3DA738ECB2C}" name="nationality_name"/>
@@ -2822,10 +2834,16 @@
     <tableColumn id="107" xr3:uid="{8C8A744A-8B10-E342-9029-FAB3DFEC624F}" name="rcb"/>
     <tableColumn id="108" xr3:uid="{EA55E1E2-F930-4B49-A693-C0E99F634749}" name="rb"/>
     <tableColumn id="109" xr3:uid="{A0862F14-FB36-3440-A194-61BBEC65DFFC}" name="gk"/>
-    <tableColumn id="116" xr3:uid="{BF088D61-9242-824F-BBBD-4B50E00909B9}" name="mcharo_fender_ln_price" dataDxfId="0">
+    <tableColumn id="116" xr3:uid="{BF088D61-9242-824F-BBBD-4B50E00909B9}" name="mcharo_fender_ln_price" dataDxfId="2">
       <calculatedColumnFormula>1.573405+0.0508405*Table1[[#This Row],[pace]] +0.0157776*Table1[[#This Row],[attacking_heading_accuracy]] +0.0178237*Table1[[#This Row],[passing]]+0.0113991*Table1[[#This Row],[dribbling]] +0.0362758*Table1[[#This Row],[power_strength]]+0.1658073*Table1[[#This Row],[weak_foot]]+0.2568779*Table1[[#This Row],[skill_moves]]+0.6951661*Table1[[#This Row],[Defender]]+0.4259821*Table1[[#This Row],[Midfielder]]+0.1161503*Table1[[#This Row],[Finesse_Shot]]</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="110" xr3:uid="{53AA2969-BF32-914D-B77B-B6EFA2E5072C}" name="player_face_url"/>
+    <tableColumn id="111" xr3:uid="{2CECE4AA-312C-E044-93DD-04CA703ACB27}" name="develle_mcharo_passing" dataDxfId="1">
+      <calculatedColumnFormula xml:space="preserve"> (Table1[[#This Row],[mentality_vision]]/100) + 0.809*(Table1[[#This Row],[skill_curve]]/100) + (0.75*(Table1[[#This Row],[attacking_short_passing]]/100) + 0.25*(Table1[[#This Row],[attacking_crossing]]/100)) + (0.625*(Table1[[#This Row],[skill_long_passing]]/100) + 0.1875*(Table1[[#This Row],[skill_fk_accuracy]]/100) + 0.1875*(Table1[[#This Row],[attacking_crossing]]/100)) - ((1 - ((0.75*(Table1[[#This Row],[attacking_short_passing]]/100) + 0.25*(Table1[[#This Row],[attacking_crossing]]/100) - (0.625*(Table1[[#This Row],[skill_long_passing]]/100) + 0.1875*(Table1[[#This Row],[skill_fk_accuracy]]/100) + 0.1875*(Table1[[#This Row],[attacking_crossing]]/100)))^2))  * ((1 - (Table1[[#This Row],[mentality_vision]]/100))^2))</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="112" xr3:uid="{D843D4D9-ED89-0F43-A562-2146D36E58D1}" name="mcharo_develle_ln_price" dataDxfId="0">
+      <calculatedColumnFormula>1.585332 + 0.008219*Table1[[#This Row],[power_jumping]]+ 0.047559*Table1[[#This Row],[pace]] + 0.012348*Table1[[#This Row],[attacking_heading_accuracy]] + 0.362187*Table1[[#This Row],[develle_mcharo_passing]] + 0.015238*Table1[[#This Row],[dribbling]] + 0.189748*Table1[[#This Row],[weak_foot]] + 0.033917*Table1[[#This Row],[power_strength]] + 0.26019*Table1[[#This Row],[skill_moves]] + 0.808787*Table1[[#This Row],[Defender]] + 0.472467*Table1[[#This Row],[Midfielder]] + 0.081427*Table1[[#This Row],[Finesse_Shot]]</calculatedColumnFormula>
+    </tableColumn>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -3148,7 +3166,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DD1B0981-BBF7-624E-ABCF-F6504400D045}">
-  <dimension ref="A1:DJ101"/>
+  <dimension ref="A1:DL101"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="11.5" customWidth="1"/>
@@ -3224,7 +3242,7 @@
     <col min="114" max="116" width="41.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:114" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:116" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>137</v>
       </c>
@@ -3567,8 +3585,14 @@
       <c r="DJ1" t="s">
         <v>246</v>
       </c>
+      <c r="DK1" t="s">
+        <v>866</v>
+      </c>
+      <c r="DL1" t="s">
+        <v>867</v>
+      </c>
     </row>
-    <row r="2" spans="1:114" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:116" x14ac:dyDescent="0.2">
       <c r="A2">
         <v>231478</v>
       </c>
@@ -3903,8 +3927,16 @@
       <c r="DJ2" t="s">
         <v>262</v>
       </c>
+      <c r="DK2">
+        <f xml:space="preserve"> (Table1[[#This Row],[mentality_vision]]/100) + 0.809*(Table1[[#This Row],[skill_curve]]/100) + (0.75*(Table1[[#This Row],[attacking_short_passing]]/100) + 0.25*(Table1[[#This Row],[attacking_crossing]]/100)) + (0.625*(Table1[[#This Row],[skill_long_passing]]/100) + 0.1875*(Table1[[#This Row],[skill_fk_accuracy]]/100) + 0.1875*(Table1[[#This Row],[attacking_crossing]]/100)) - ((1 - ((0.75*(Table1[[#This Row],[attacking_short_passing]]/100) + 0.25*(Table1[[#This Row],[attacking_crossing]]/100) - (0.625*(Table1[[#This Row],[skill_long_passing]]/100) + 0.1875*(Table1[[#This Row],[skill_fk_accuracy]]/100) + 0.1875*(Table1[[#This Row],[attacking_crossing]]/100)))^2))  * ((1 - (Table1[[#This Row],[mentality_vision]]/100))^2))</f>
+        <v>2.8799714516015622</v>
+      </c>
+      <c r="DL2">
+        <f>1.585332 + 0.008219*Table1[[#This Row],[power_jumping]]+ 0.047559*Table1[[#This Row],[pace]] + 0.012348*Table1[[#This Row],[attacking_heading_accuracy]] + 0.362187*Table1[[#This Row],[develle_mcharo_passing]] + 0.015238*Table1[[#This Row],[dribbling]] + 0.189748*Table1[[#This Row],[weak_foot]] + 0.033917*Table1[[#This Row],[power_strength]] + 0.26019*Table1[[#This Row],[skill_moves]] + 0.808787*Table1[[#This Row],[Defender]] + 0.472467*Table1[[#This Row],[Midfielder]] + 0.081427*Table1[[#This Row],[Finesse_Shot]]</f>
+        <v>14.083660220141214</v>
+      </c>
     </row>
-    <row r="3" spans="1:114" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:116" x14ac:dyDescent="0.2">
       <c r="A3">
         <v>224232</v>
       </c>
@@ -4239,8 +4271,16 @@
       <c r="DJ3" t="s">
         <v>274</v>
       </c>
+      <c r="DK3">
+        <f xml:space="preserve"> (Table1[[#This Row],[mentality_vision]]/100) + 0.809*(Table1[[#This Row],[skill_curve]]/100) + (0.75*(Table1[[#This Row],[attacking_short_passing]]/100) + 0.25*(Table1[[#This Row],[attacking_crossing]]/100)) + (0.625*(Table1[[#This Row],[skill_long_passing]]/100) + 0.1875*(Table1[[#This Row],[skill_fk_accuracy]]/100) + 0.1875*(Table1[[#This Row],[attacking_crossing]]/100)) - ((1 - ((0.75*(Table1[[#This Row],[attacking_short_passing]]/100) + 0.25*(Table1[[#This Row],[attacking_crossing]]/100) - (0.625*(Table1[[#This Row],[skill_long_passing]]/100) + 0.1875*(Table1[[#This Row],[skill_fk_accuracy]]/100) + 0.1875*(Table1[[#This Row],[attacking_crossing]]/100)))^2))  * ((1 - (Table1[[#This Row],[mentality_vision]]/100))^2))</f>
+        <v>3.1491607656250005</v>
+      </c>
+      <c r="DL3">
+        <f>1.585332 + 0.008219*Table1[[#This Row],[power_jumping]]+ 0.047559*Table1[[#This Row],[pace]] + 0.012348*Table1[[#This Row],[attacking_heading_accuracy]] + 0.362187*Table1[[#This Row],[develle_mcharo_passing]] + 0.015238*Table1[[#This Row],[dribbling]] + 0.189748*Table1[[#This Row],[weak_foot]] + 0.033917*Table1[[#This Row],[power_strength]] + 0.26019*Table1[[#This Row],[skill_moves]] + 0.808787*Table1[[#This Row],[Defender]] + 0.472467*Table1[[#This Row],[Midfielder]] + 0.081427*Table1[[#This Row],[Finesse_Shot]]</f>
+        <v>13.448961090219418</v>
+      </c>
     </row>
-    <row r="4" spans="1:114" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:116" x14ac:dyDescent="0.2">
       <c r="A4">
         <v>192985</v>
       </c>
@@ -4566,8 +4606,16 @@
       <c r="DJ4" t="s">
         <v>284</v>
       </c>
+      <c r="DK4">
+        <f xml:space="preserve"> (Table1[[#This Row],[mentality_vision]]/100) + 0.809*(Table1[[#This Row],[skill_curve]]/100) + (0.75*(Table1[[#This Row],[attacking_short_passing]]/100) + 0.25*(Table1[[#This Row],[attacking_crossing]]/100)) + (0.625*(Table1[[#This Row],[skill_long_passing]]/100) + 0.1875*(Table1[[#This Row],[skill_fk_accuracy]]/100) + 0.1875*(Table1[[#This Row],[attacking_crossing]]/100)) - ((1 - ((0.75*(Table1[[#This Row],[attacking_short_passing]]/100) + 0.25*(Table1[[#This Row],[attacking_crossing]]/100) - (0.625*(Table1[[#This Row],[skill_long_passing]]/100) + 0.1875*(Table1[[#This Row],[skill_fk_accuracy]]/100) + 0.1875*(Table1[[#This Row],[attacking_crossing]]/100)))^2))  * ((1 - (Table1[[#This Row],[mentality_vision]]/100))^2))</f>
+        <v>3.4997208100000003</v>
+      </c>
+      <c r="DL4">
+        <f>1.585332 + 0.008219*Table1[[#This Row],[power_jumping]]+ 0.047559*Table1[[#This Row],[pace]] + 0.012348*Table1[[#This Row],[attacking_heading_accuracy]] + 0.362187*Table1[[#This Row],[develle_mcharo_passing]] + 0.015238*Table1[[#This Row],[dribbling]] + 0.189748*Table1[[#This Row],[weak_foot]] + 0.033917*Table1[[#This Row],[power_strength]] + 0.26019*Table1[[#This Row],[skill_moves]] + 0.808787*Table1[[#This Row],[Defender]] + 0.472467*Table1[[#This Row],[Midfielder]] + 0.081427*Table1[[#This Row],[Finesse_Shot]]</f>
+        <v>13.498066381011473</v>
+      </c>
     </row>
-    <row r="5" spans="1:114" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:116" x14ac:dyDescent="0.2">
       <c r="A5">
         <v>237383</v>
       </c>
@@ -4902,8 +4950,16 @@
       <c r="DJ5" t="s">
         <v>294</v>
       </c>
+      <c r="DK5">
+        <f xml:space="preserve"> (Table1[[#This Row],[mentality_vision]]/100) + 0.809*(Table1[[#This Row],[skill_curve]]/100) + (0.75*(Table1[[#This Row],[attacking_short_passing]]/100) + 0.25*(Table1[[#This Row],[attacking_crossing]]/100)) + (0.625*(Table1[[#This Row],[skill_long_passing]]/100) + 0.1875*(Table1[[#This Row],[skill_fk_accuracy]]/100) + 0.1875*(Table1[[#This Row],[attacking_crossing]]/100)) - ((1 - ((0.75*(Table1[[#This Row],[attacking_short_passing]]/100) + 0.25*(Table1[[#This Row],[attacking_crossing]]/100) - (0.625*(Table1[[#This Row],[skill_long_passing]]/100) + 0.1875*(Table1[[#This Row],[skill_fk_accuracy]]/100) + 0.1875*(Table1[[#This Row],[attacking_crossing]]/100)))^2))  * ((1 - (Table1[[#This Row],[mentality_vision]]/100))^2))</f>
+        <v>2.6914998756249995</v>
+      </c>
+      <c r="DL5">
+        <f>1.585332 + 0.008219*Table1[[#This Row],[power_jumping]]+ 0.047559*Table1[[#This Row],[pace]] + 0.012348*Table1[[#This Row],[attacking_heading_accuracy]] + 0.362187*Table1[[#This Row],[develle_mcharo_passing]] + 0.015238*Table1[[#This Row],[dribbling]] + 0.189748*Table1[[#This Row],[weak_foot]] + 0.033917*Table1[[#This Row],[power_strength]] + 0.26019*Table1[[#This Row],[skill_moves]] + 0.808787*Table1[[#This Row],[Defender]] + 0.472467*Table1[[#This Row],[Midfielder]] + 0.081427*Table1[[#This Row],[Finesse_Shot]]</f>
+        <v>13.478752265452991</v>
+      </c>
     </row>
-    <row r="6" spans="1:114" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:116" x14ac:dyDescent="0.2">
       <c r="A6">
         <v>208128</v>
       </c>
@@ -5229,8 +5285,16 @@
       <c r="DJ6" t="s">
         <v>308</v>
       </c>
+      <c r="DK6">
+        <f xml:space="preserve"> (Table1[[#This Row],[mentality_vision]]/100) + 0.809*(Table1[[#This Row],[skill_curve]]/100) + (0.75*(Table1[[#This Row],[attacking_short_passing]]/100) + 0.25*(Table1[[#This Row],[attacking_crossing]]/100)) + (0.625*(Table1[[#This Row],[skill_long_passing]]/100) + 0.1875*(Table1[[#This Row],[skill_fk_accuracy]]/100) + 0.1875*(Table1[[#This Row],[attacking_crossing]]/100)) - ((1 - ((0.75*(Table1[[#This Row],[attacking_short_passing]]/100) + 0.25*(Table1[[#This Row],[attacking_crossing]]/100) - (0.625*(Table1[[#This Row],[skill_long_passing]]/100) + 0.1875*(Table1[[#This Row],[skill_fk_accuracy]]/100) + 0.1875*(Table1[[#This Row],[attacking_crossing]]/100)))^2))  * ((1 - (Table1[[#This Row],[mentality_vision]]/100))^2))</f>
+        <v>3.3216957987890625</v>
+      </c>
+      <c r="DL6">
+        <f>1.585332 + 0.008219*Table1[[#This Row],[power_jumping]]+ 0.047559*Table1[[#This Row],[pace]] + 0.012348*Table1[[#This Row],[attacking_heading_accuracy]] + 0.362187*Table1[[#This Row],[develle_mcharo_passing]] + 0.015238*Table1[[#This Row],[dribbling]] + 0.189748*Table1[[#This Row],[weak_foot]] + 0.033917*Table1[[#This Row],[power_strength]] + 0.26019*Table1[[#This Row],[skill_moves]] + 0.808787*Table1[[#This Row],[Defender]] + 0.472467*Table1[[#This Row],[Midfielder]] + 0.081427*Table1[[#This Row],[Finesse_Shot]]</f>
+        <v>13.483791036276017</v>
+      </c>
     </row>
-    <row r="7" spans="1:114" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:116" x14ac:dyDescent="0.2">
       <c r="A7">
         <v>211110</v>
       </c>
@@ -5565,8 +5629,16 @@
       <c r="DJ7" t="s">
         <v>321</v>
       </c>
+      <c r="DK7">
+        <f xml:space="preserve"> (Table1[[#This Row],[mentality_vision]]/100) + 0.809*(Table1[[#This Row],[skill_curve]]/100) + (0.75*(Table1[[#This Row],[attacking_short_passing]]/100) + 0.25*(Table1[[#This Row],[attacking_crossing]]/100)) + (0.625*(Table1[[#This Row],[skill_long_passing]]/100) + 0.1875*(Table1[[#This Row],[skill_fk_accuracy]]/100) + 0.1875*(Table1[[#This Row],[attacking_crossing]]/100)) - ((1 - ((0.75*(Table1[[#This Row],[attacking_short_passing]]/100) + 0.25*(Table1[[#This Row],[attacking_crossing]]/100) - (0.625*(Table1[[#This Row],[skill_long_passing]]/100) + 0.1875*(Table1[[#This Row],[skill_fk_accuracy]]/100) + 0.1875*(Table1[[#This Row],[attacking_crossing]]/100)))^2))  * ((1 - (Table1[[#This Row],[mentality_vision]]/100))^2))</f>
+        <v>3.2312435556249999</v>
+      </c>
+      <c r="DL7">
+        <f>1.585332 + 0.008219*Table1[[#This Row],[power_jumping]]+ 0.047559*Table1[[#This Row],[pace]] + 0.012348*Table1[[#This Row],[attacking_heading_accuracy]] + 0.362187*Table1[[#This Row],[develle_mcharo_passing]] + 0.015238*Table1[[#This Row],[dribbling]] + 0.189748*Table1[[#This Row],[weak_foot]] + 0.033917*Table1[[#This Row],[power_strength]] + 0.26019*Table1[[#This Row],[skill_moves]] + 0.808787*Table1[[#This Row],[Defender]] + 0.472467*Table1[[#This Row],[Midfielder]] + 0.081427*Table1[[#This Row],[Finesse_Shot]]</f>
+        <v>13.40172840968115</v>
+      </c>
     </row>
-    <row r="8" spans="1:114" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:116" x14ac:dyDescent="0.2">
       <c r="A8">
         <v>226268</v>
       </c>
@@ -5901,8 +5973,16 @@
       <c r="DJ8" t="s">
         <v>328</v>
       </c>
+      <c r="DK8">
+        <f xml:space="preserve"> (Table1[[#This Row],[mentality_vision]]/100) + 0.809*(Table1[[#This Row],[skill_curve]]/100) + (0.75*(Table1[[#This Row],[attacking_short_passing]]/100) + 0.25*(Table1[[#This Row],[attacking_crossing]]/100)) + (0.625*(Table1[[#This Row],[skill_long_passing]]/100) + 0.1875*(Table1[[#This Row],[skill_fk_accuracy]]/100) + 0.1875*(Table1[[#This Row],[attacking_crossing]]/100)) - ((1 - ((0.75*(Table1[[#This Row],[attacking_short_passing]]/100) + 0.25*(Table1[[#This Row],[attacking_crossing]]/100) - (0.625*(Table1[[#This Row],[skill_long_passing]]/100) + 0.1875*(Table1[[#This Row],[skill_fk_accuracy]]/100) + 0.1875*(Table1[[#This Row],[attacking_crossing]]/100)))^2))  * ((1 - (Table1[[#This Row],[mentality_vision]]/100))^2))</f>
+        <v>3.1569240000000001</v>
+      </c>
+      <c r="DL8">
+        <f>1.585332 + 0.008219*Table1[[#This Row],[power_jumping]]+ 0.047559*Table1[[#This Row],[pace]] + 0.012348*Table1[[#This Row],[attacking_heading_accuracy]] + 0.362187*Table1[[#This Row],[develle_mcharo_passing]] + 0.015238*Table1[[#This Row],[dribbling]] + 0.189748*Table1[[#This Row],[weak_foot]] + 0.033917*Table1[[#This Row],[power_strength]] + 0.26019*Table1[[#This Row],[skill_moves]] + 0.808787*Table1[[#This Row],[Defender]] + 0.472467*Table1[[#This Row],[Midfielder]] + 0.081427*Table1[[#This Row],[Finesse_Shot]]</f>
+        <v>14.172515832787997</v>
+      </c>
     </row>
-    <row r="9" spans="1:114" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:116" x14ac:dyDescent="0.2">
       <c r="A9">
         <v>237238</v>
       </c>
@@ -6234,8 +6314,16 @@
       <c r="DJ9" t="s">
         <v>336</v>
       </c>
+      <c r="DK9">
+        <f xml:space="preserve"> (Table1[[#This Row],[mentality_vision]]/100) + 0.809*(Table1[[#This Row],[skill_curve]]/100) + (0.75*(Table1[[#This Row],[attacking_short_passing]]/100) + 0.25*(Table1[[#This Row],[attacking_crossing]]/100)) + (0.625*(Table1[[#This Row],[skill_long_passing]]/100) + 0.1875*(Table1[[#This Row],[skill_fk_accuracy]]/100) + 0.1875*(Table1[[#This Row],[attacking_crossing]]/100)) - ((1 - ((0.75*(Table1[[#This Row],[attacking_short_passing]]/100) + 0.25*(Table1[[#This Row],[attacking_crossing]]/100) - (0.625*(Table1[[#This Row],[skill_long_passing]]/100) + 0.1875*(Table1[[#This Row],[skill_fk_accuracy]]/100) + 0.1875*(Table1[[#This Row],[attacking_crossing]]/100)))^2))  * ((1 - (Table1[[#This Row],[mentality_vision]]/100))^2))</f>
+        <v>2.841731550625</v>
+      </c>
+      <c r="DL9">
+        <f>1.585332 + 0.008219*Table1[[#This Row],[power_jumping]]+ 0.047559*Table1[[#This Row],[pace]] + 0.012348*Table1[[#This Row],[attacking_heading_accuracy]] + 0.362187*Table1[[#This Row],[develle_mcharo_passing]] + 0.015238*Table1[[#This Row],[dribbling]] + 0.189748*Table1[[#This Row],[weak_foot]] + 0.033917*Table1[[#This Row],[power_strength]] + 0.26019*Table1[[#This Row],[skill_moves]] + 0.808787*Table1[[#This Row],[Defender]] + 0.472467*Table1[[#This Row],[Midfielder]] + 0.081427*Table1[[#This Row],[Finesse_Shot]]</f>
+        <v>13.758591225126215</v>
+      </c>
     </row>
-    <row r="10" spans="1:114" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:116" x14ac:dyDescent="0.2">
       <c r="A10">
         <v>228093</v>
       </c>
@@ -6567,8 +6655,16 @@
       <c r="DJ10" t="s">
         <v>341</v>
       </c>
+      <c r="DK10">
+        <f xml:space="preserve"> (Table1[[#This Row],[mentality_vision]]/100) + 0.809*(Table1[[#This Row],[skill_curve]]/100) + (0.75*(Table1[[#This Row],[attacking_short_passing]]/100) + 0.25*(Table1[[#This Row],[attacking_crossing]]/100)) + (0.625*(Table1[[#This Row],[skill_long_passing]]/100) + 0.1875*(Table1[[#This Row],[skill_fk_accuracy]]/100) + 0.1875*(Table1[[#This Row],[attacking_crossing]]/100)) - ((1 - ((0.75*(Table1[[#This Row],[attacking_short_passing]]/100) + 0.25*(Table1[[#This Row],[attacking_crossing]]/100) - (0.625*(Table1[[#This Row],[skill_long_passing]]/100) + 0.1875*(Table1[[#This Row],[skill_fk_accuracy]]/100) + 0.1875*(Table1[[#This Row],[attacking_crossing]]/100)))^2))  * ((1 - (Table1[[#This Row],[mentality_vision]]/100))^2))</f>
+        <v>2.8014161756249996</v>
+      </c>
+      <c r="DL10">
+        <f>1.585332 + 0.008219*Table1[[#This Row],[power_jumping]]+ 0.047559*Table1[[#This Row],[pace]] + 0.012348*Table1[[#This Row],[attacking_heading_accuracy]] + 0.362187*Table1[[#This Row],[develle_mcharo_passing]] + 0.015238*Table1[[#This Row],[dribbling]] + 0.189748*Table1[[#This Row],[weak_foot]] + 0.033917*Table1[[#This Row],[power_strength]] + 0.26019*Table1[[#This Row],[skill_moves]] + 0.808787*Table1[[#This Row],[Defender]] + 0.472467*Table1[[#This Row],[Midfielder]] + 0.081427*Table1[[#This Row],[Finesse_Shot]]</f>
+        <v>13.943724520401091</v>
+      </c>
     </row>
-    <row r="11" spans="1:114" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:116" x14ac:dyDescent="0.2">
       <c r="A11">
         <v>239580</v>
       </c>
@@ -6891,8 +6987,16 @@
       <c r="DJ11" t="s">
         <v>347</v>
       </c>
+      <c r="DK11">
+        <f xml:space="preserve"> (Table1[[#This Row],[mentality_vision]]/100) + 0.809*(Table1[[#This Row],[skill_curve]]/100) + (0.75*(Table1[[#This Row],[attacking_short_passing]]/100) + 0.25*(Table1[[#This Row],[attacking_crossing]]/100)) + (0.625*(Table1[[#This Row],[skill_long_passing]]/100) + 0.1875*(Table1[[#This Row],[skill_fk_accuracy]]/100) + 0.1875*(Table1[[#This Row],[attacking_crossing]]/100)) - ((1 - ((0.75*(Table1[[#This Row],[attacking_short_passing]]/100) + 0.25*(Table1[[#This Row],[attacking_crossing]]/100) - (0.625*(Table1[[#This Row],[skill_long_passing]]/100) + 0.1875*(Table1[[#This Row],[skill_fk_accuracy]]/100) + 0.1875*(Table1[[#This Row],[attacking_crossing]]/100)))^2))  * ((1 - (Table1[[#This Row],[mentality_vision]]/100))^2))</f>
+        <v>1.7312805625000001</v>
+      </c>
+      <c r="DL11">
+        <f>1.585332 + 0.008219*Table1[[#This Row],[power_jumping]]+ 0.047559*Table1[[#This Row],[pace]] + 0.012348*Table1[[#This Row],[attacking_heading_accuracy]] + 0.362187*Table1[[#This Row],[develle_mcharo_passing]] + 0.015238*Table1[[#This Row],[dribbling]] + 0.189748*Table1[[#This Row],[weak_foot]] + 0.033917*Table1[[#This Row],[power_strength]] + 0.26019*Table1[[#This Row],[skill_moves]] + 0.808787*Table1[[#This Row],[Defender]] + 0.472467*Table1[[#This Row],[Midfielder]] + 0.081427*Table1[[#This Row],[Finesse_Shot]]</f>
+        <v>13.506040313090187</v>
+      </c>
     </row>
-    <row r="12" spans="1:114" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:116" x14ac:dyDescent="0.2">
       <c r="A12">
         <v>222077</v>
       </c>
@@ -7224,8 +7328,16 @@
       <c r="DJ12" t="s">
         <v>355</v>
       </c>
+      <c r="DK12">
+        <f xml:space="preserve"> (Table1[[#This Row],[mentality_vision]]/100) + 0.809*(Table1[[#This Row],[skill_curve]]/100) + (0.75*(Table1[[#This Row],[attacking_short_passing]]/100) + 0.25*(Table1[[#This Row],[attacking_crossing]]/100)) + (0.625*(Table1[[#This Row],[skill_long_passing]]/100) + 0.1875*(Table1[[#This Row],[skill_fk_accuracy]]/100) + 0.1875*(Table1[[#This Row],[attacking_crossing]]/100)) - ((1 - ((0.75*(Table1[[#This Row],[attacking_short_passing]]/100) + 0.25*(Table1[[#This Row],[attacking_crossing]]/100) - (0.625*(Table1[[#This Row],[skill_long_passing]]/100) + 0.1875*(Table1[[#This Row],[skill_fk_accuracy]]/100) + 0.1875*(Table1[[#This Row],[attacking_crossing]]/100)))^2))  * ((1 - (Table1[[#This Row],[mentality_vision]]/100))^2))</f>
+        <v>2.9800920939062494</v>
+      </c>
+      <c r="DL12">
+        <f>1.585332 + 0.008219*Table1[[#This Row],[power_jumping]]+ 0.047559*Table1[[#This Row],[pace]] + 0.012348*Table1[[#This Row],[attacking_heading_accuracy]] + 0.362187*Table1[[#This Row],[develle_mcharo_passing]] + 0.015238*Table1[[#This Row],[dribbling]] + 0.189748*Table1[[#This Row],[weak_foot]] + 0.033917*Table1[[#This Row],[power_strength]] + 0.26019*Table1[[#This Row],[skill_moves]] + 0.808787*Table1[[#This Row],[Defender]] + 0.472467*Table1[[#This Row],[Midfielder]] + 0.081427*Table1[[#This Row],[Finesse_Shot]]</f>
+        <v>12.670555615215621</v>
+      </c>
     </row>
-    <row r="13" spans="1:114" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:116" x14ac:dyDescent="0.2">
       <c r="A13">
         <v>233096</v>
       </c>
@@ -7557,8 +7669,16 @@
       <c r="DJ13" t="s">
         <v>361</v>
       </c>
+      <c r="DK13">
+        <f xml:space="preserve"> (Table1[[#This Row],[mentality_vision]]/100) + 0.809*(Table1[[#This Row],[skill_curve]]/100) + (0.75*(Table1[[#This Row],[attacking_short_passing]]/100) + 0.25*(Table1[[#This Row],[attacking_crossing]]/100)) + (0.625*(Table1[[#This Row],[skill_long_passing]]/100) + 0.1875*(Table1[[#This Row],[skill_fk_accuracy]]/100) + 0.1875*(Table1[[#This Row],[attacking_crossing]]/100)) - ((1 - ((0.75*(Table1[[#This Row],[attacking_short_passing]]/100) + 0.25*(Table1[[#This Row],[attacking_crossing]]/100) - (0.625*(Table1[[#This Row],[skill_long_passing]]/100) + 0.1875*(Table1[[#This Row],[skill_fk_accuracy]]/100) + 0.1875*(Table1[[#This Row],[attacking_crossing]]/100)))^2))  * ((1 - (Table1[[#This Row],[mentality_vision]]/100))^2))</f>
+        <v>2.6503913719140626</v>
+      </c>
+      <c r="DL13">
+        <f>1.585332 + 0.008219*Table1[[#This Row],[power_jumping]]+ 0.047559*Table1[[#This Row],[pace]] + 0.012348*Table1[[#This Row],[attacking_heading_accuracy]] + 0.362187*Table1[[#This Row],[develle_mcharo_passing]] + 0.015238*Table1[[#This Row],[dribbling]] + 0.189748*Table1[[#This Row],[weak_foot]] + 0.033917*Table1[[#This Row],[power_strength]] + 0.26019*Table1[[#This Row],[skill_moves]] + 0.808787*Table1[[#This Row],[Defender]] + 0.472467*Table1[[#This Row],[Midfielder]] + 0.081427*Table1[[#This Row],[Finesse_Shot]]</f>
+        <v>14.187224299819437</v>
+      </c>
     </row>
-    <row r="14" spans="1:114" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:116" x14ac:dyDescent="0.2">
       <c r="A14">
         <v>220502</v>
       </c>
@@ -7893,8 +8013,16 @@
       <c r="DJ14" t="s">
         <v>369</v>
       </c>
+      <c r="DK14">
+        <f xml:space="preserve"> (Table1[[#This Row],[mentality_vision]]/100) + 0.809*(Table1[[#This Row],[skill_curve]]/100) + (0.75*(Table1[[#This Row],[attacking_short_passing]]/100) + 0.25*(Table1[[#This Row],[attacking_crossing]]/100)) + (0.625*(Table1[[#This Row],[skill_long_passing]]/100) + 0.1875*(Table1[[#This Row],[skill_fk_accuracy]]/100) + 0.1875*(Table1[[#This Row],[attacking_crossing]]/100)) - ((1 - ((0.75*(Table1[[#This Row],[attacking_short_passing]]/100) + 0.25*(Table1[[#This Row],[attacking_crossing]]/100) - (0.625*(Table1[[#This Row],[skill_long_passing]]/100) + 0.1875*(Table1[[#This Row],[skill_fk_accuracy]]/100) + 0.1875*(Table1[[#This Row],[attacking_crossing]]/100)))^2))  * ((1 - (Table1[[#This Row],[mentality_vision]]/100))^2))</f>
+        <v>2.8547465806250001</v>
+      </c>
+      <c r="DL14">
+        <f>1.585332 + 0.008219*Table1[[#This Row],[power_jumping]]+ 0.047559*Table1[[#This Row],[pace]] + 0.012348*Table1[[#This Row],[attacking_heading_accuracy]] + 0.362187*Table1[[#This Row],[develle_mcharo_passing]] + 0.015238*Table1[[#This Row],[dribbling]] + 0.189748*Table1[[#This Row],[weak_foot]] + 0.033917*Table1[[#This Row],[power_strength]] + 0.26019*Table1[[#This Row],[skill_moves]] + 0.808787*Table1[[#This Row],[Defender]] + 0.472467*Table1[[#This Row],[Midfielder]] + 0.081427*Table1[[#This Row],[Finesse_Shot]]</f>
+        <v>13.460295099796827</v>
+      </c>
     </row>
-    <row r="15" spans="1:114" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:116" x14ac:dyDescent="0.2">
       <c r="A15">
         <v>227796</v>
       </c>
@@ -8229,8 +8357,16 @@
       <c r="DJ15" t="s">
         <v>377</v>
       </c>
+      <c r="DK15">
+        <f xml:space="preserve"> (Table1[[#This Row],[mentality_vision]]/100) + 0.809*(Table1[[#This Row],[skill_curve]]/100) + (0.75*(Table1[[#This Row],[attacking_short_passing]]/100) + 0.25*(Table1[[#This Row],[attacking_crossing]]/100)) + (0.625*(Table1[[#This Row],[skill_long_passing]]/100) + 0.1875*(Table1[[#This Row],[skill_fk_accuracy]]/100) + 0.1875*(Table1[[#This Row],[attacking_crossing]]/100)) - ((1 - ((0.75*(Table1[[#This Row],[attacking_short_passing]]/100) + 0.25*(Table1[[#This Row],[attacking_crossing]]/100) - (0.625*(Table1[[#This Row],[skill_long_passing]]/100) + 0.1875*(Table1[[#This Row],[skill_fk_accuracy]]/100) + 0.1875*(Table1[[#This Row],[attacking_crossing]]/100)))^2))  * ((1 - (Table1[[#This Row],[mentality_vision]]/100))^2))</f>
+        <v>3.0065276406250003</v>
+      </c>
+      <c r="DL15">
+        <f>1.585332 + 0.008219*Table1[[#This Row],[power_jumping]]+ 0.047559*Table1[[#This Row],[pace]] + 0.012348*Table1[[#This Row],[attacking_heading_accuracy]] + 0.362187*Table1[[#This Row],[develle_mcharo_passing]] + 0.015238*Table1[[#This Row],[dribbling]] + 0.189748*Table1[[#This Row],[weak_foot]] + 0.033917*Table1[[#This Row],[power_strength]] + 0.26019*Table1[[#This Row],[skill_moves]] + 0.808787*Table1[[#This Row],[Defender]] + 0.472467*Table1[[#This Row],[Midfielder]] + 0.081427*Table1[[#This Row],[Finesse_Shot]]</f>
+        <v>13.285416226575046</v>
+      </c>
     </row>
-    <row r="16" spans="1:114" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:116" x14ac:dyDescent="0.2">
       <c r="A16">
         <v>192505</v>
       </c>
@@ -8556,8 +8692,16 @@
       <c r="DJ16" t="s">
         <v>385</v>
       </c>
+      <c r="DK16">
+        <f xml:space="preserve"> (Table1[[#This Row],[mentality_vision]]/100) + 0.809*(Table1[[#This Row],[skill_curve]]/100) + (0.75*(Table1[[#This Row],[attacking_short_passing]]/100) + 0.25*(Table1[[#This Row],[attacking_crossing]]/100)) + (0.625*(Table1[[#This Row],[skill_long_passing]]/100) + 0.1875*(Table1[[#This Row],[skill_fk_accuracy]]/100) + 0.1875*(Table1[[#This Row],[attacking_crossing]]/100)) - ((1 - ((0.75*(Table1[[#This Row],[attacking_short_passing]]/100) + 0.25*(Table1[[#This Row],[attacking_crossing]]/100) - (0.625*(Table1[[#This Row],[skill_long_passing]]/100) + 0.1875*(Table1[[#This Row],[skill_fk_accuracy]]/100) + 0.1875*(Table1[[#This Row],[attacking_crossing]]/100)))^2))  * ((1 - (Table1[[#This Row],[mentality_vision]]/100))^2))</f>
+        <v>2.8340372224999997</v>
+      </c>
+      <c r="DL16">
+        <f>1.585332 + 0.008219*Table1[[#This Row],[power_jumping]]+ 0.047559*Table1[[#This Row],[pace]] + 0.012348*Table1[[#This Row],[attacking_heading_accuracy]] + 0.362187*Table1[[#This Row],[develle_mcharo_passing]] + 0.015238*Table1[[#This Row],[dribbling]] + 0.189748*Table1[[#This Row],[weak_foot]] + 0.033917*Table1[[#This Row],[power_strength]] + 0.26019*Table1[[#This Row],[skill_moves]] + 0.808787*Table1[[#This Row],[Defender]] + 0.472467*Table1[[#This Row],[Midfielder]] + 0.081427*Table1[[#This Row],[Finesse_Shot]]</f>
+        <v>14.020586439505607</v>
+      </c>
     </row>
-    <row r="17" spans="1:114" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:116" x14ac:dyDescent="0.2">
       <c r="A17">
         <v>241721</v>
       </c>
@@ -8892,8 +9036,16 @@
       <c r="DJ17" t="s">
         <v>392</v>
       </c>
+      <c r="DK17">
+        <f xml:space="preserve"> (Table1[[#This Row],[mentality_vision]]/100) + 0.809*(Table1[[#This Row],[skill_curve]]/100) + (0.75*(Table1[[#This Row],[attacking_short_passing]]/100) + 0.25*(Table1[[#This Row],[attacking_crossing]]/100)) + (0.625*(Table1[[#This Row],[skill_long_passing]]/100) + 0.1875*(Table1[[#This Row],[skill_fk_accuracy]]/100) + 0.1875*(Table1[[#This Row],[attacking_crossing]]/100)) - ((1 - ((0.75*(Table1[[#This Row],[attacking_short_passing]]/100) + 0.25*(Table1[[#This Row],[attacking_crossing]]/100) - (0.625*(Table1[[#This Row],[skill_long_passing]]/100) + 0.1875*(Table1[[#This Row],[skill_fk_accuracy]]/100) + 0.1875*(Table1[[#This Row],[attacking_crossing]]/100)))^2))  * ((1 - (Table1[[#This Row],[mentality_vision]]/100))^2))</f>
+        <v>2.9535740625</v>
+      </c>
+      <c r="DL17">
+        <f>1.585332 + 0.008219*Table1[[#This Row],[power_jumping]]+ 0.047559*Table1[[#This Row],[pace]] + 0.012348*Table1[[#This Row],[attacking_heading_accuracy]] + 0.362187*Table1[[#This Row],[develle_mcharo_passing]] + 0.015238*Table1[[#This Row],[dribbling]] + 0.189748*Table1[[#This Row],[weak_foot]] + 0.033917*Table1[[#This Row],[power_strength]] + 0.26019*Table1[[#This Row],[skill_moves]] + 0.808787*Table1[[#This Row],[Defender]] + 0.472467*Table1[[#This Row],[Midfielder]] + 0.081427*Table1[[#This Row],[Finesse_Shot]]</f>
+        <v>14.748465128974686</v>
+      </c>
     </row>
-    <row r="18" spans="1:114" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:116" x14ac:dyDescent="0.2">
       <c r="A18">
         <v>230899</v>
       </c>
@@ -9219,8 +9371,16 @@
       <c r="DJ18" t="s">
         <v>404</v>
       </c>
+      <c r="DK18">
+        <f xml:space="preserve"> (Table1[[#This Row],[mentality_vision]]/100) + 0.809*(Table1[[#This Row],[skill_curve]]/100) + (0.75*(Table1[[#This Row],[attacking_short_passing]]/100) + 0.25*(Table1[[#This Row],[attacking_crossing]]/100)) + (0.625*(Table1[[#This Row],[skill_long_passing]]/100) + 0.1875*(Table1[[#This Row],[skill_fk_accuracy]]/100) + 0.1875*(Table1[[#This Row],[attacking_crossing]]/100)) - ((1 - ((0.75*(Table1[[#This Row],[attacking_short_passing]]/100) + 0.25*(Table1[[#This Row],[attacking_crossing]]/100) - (0.625*(Table1[[#This Row],[skill_long_passing]]/100) + 0.1875*(Table1[[#This Row],[skill_fk_accuracy]]/100) + 0.1875*(Table1[[#This Row],[attacking_crossing]]/100)))^2))  * ((1 - (Table1[[#This Row],[mentality_vision]]/100))^2))</f>
+        <v>2.7246150625000003</v>
+      </c>
+      <c r="DL18">
+        <f>1.585332 + 0.008219*Table1[[#This Row],[power_jumping]]+ 0.047559*Table1[[#This Row],[pace]] + 0.012348*Table1[[#This Row],[attacking_heading_accuracy]] + 0.362187*Table1[[#This Row],[develle_mcharo_passing]] + 0.015238*Table1[[#This Row],[dribbling]] + 0.189748*Table1[[#This Row],[weak_foot]] + 0.033917*Table1[[#This Row],[power_strength]] + 0.26019*Table1[[#This Row],[skill_moves]] + 0.808787*Table1[[#This Row],[Defender]] + 0.472467*Table1[[#This Row],[Midfielder]] + 0.081427*Table1[[#This Row],[Finesse_Shot]]</f>
+        <v>13.490359155641686</v>
+      </c>
     </row>
-    <row r="19" spans="1:114" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:116" x14ac:dyDescent="0.2">
       <c r="A19">
         <v>199845</v>
       </c>
@@ -9546,8 +9706,16 @@
       <c r="DJ19" t="s">
         <v>409</v>
       </c>
+      <c r="DK19">
+        <f xml:space="preserve"> (Table1[[#This Row],[mentality_vision]]/100) + 0.809*(Table1[[#This Row],[skill_curve]]/100) + (0.75*(Table1[[#This Row],[attacking_short_passing]]/100) + 0.25*(Table1[[#This Row],[attacking_crossing]]/100)) + (0.625*(Table1[[#This Row],[skill_long_passing]]/100) + 0.1875*(Table1[[#This Row],[skill_fk_accuracy]]/100) + 0.1875*(Table1[[#This Row],[attacking_crossing]]/100)) - ((1 - ((0.75*(Table1[[#This Row],[attacking_short_passing]]/100) + 0.25*(Table1[[#This Row],[attacking_crossing]]/100) - (0.625*(Table1[[#This Row],[skill_long_passing]]/100) + 0.1875*(Table1[[#This Row],[skill_fk_accuracy]]/100) + 0.1875*(Table1[[#This Row],[attacking_crossing]]/100)))^2))  * ((1 - (Table1[[#This Row],[mentality_vision]]/100))^2))</f>
+        <v>2.35547172265625</v>
+      </c>
+      <c r="DL19">
+        <f>1.585332 + 0.008219*Table1[[#This Row],[power_jumping]]+ 0.047559*Table1[[#This Row],[pace]] + 0.012348*Table1[[#This Row],[attacking_heading_accuracy]] + 0.362187*Table1[[#This Row],[develle_mcharo_passing]] + 0.015238*Table1[[#This Row],[dribbling]] + 0.189748*Table1[[#This Row],[weak_foot]] + 0.033917*Table1[[#This Row],[power_strength]] + 0.26019*Table1[[#This Row],[skill_moves]] + 0.808787*Table1[[#This Row],[Defender]] + 0.472467*Table1[[#This Row],[Midfielder]] + 0.081427*Table1[[#This Row],[Finesse_Shot]]</f>
+        <v>12.883262236813698</v>
+      </c>
     </row>
-    <row r="20" spans="1:114" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:116" x14ac:dyDescent="0.2">
       <c r="A20">
         <v>198176</v>
       </c>
@@ -9879,8 +10047,16 @@
       <c r="DJ20" t="s">
         <v>414</v>
       </c>
+      <c r="DK20">
+        <f xml:space="preserve"> (Table1[[#This Row],[mentality_vision]]/100) + 0.809*(Table1[[#This Row],[skill_curve]]/100) + (0.75*(Table1[[#This Row],[attacking_short_passing]]/100) + 0.25*(Table1[[#This Row],[attacking_crossing]]/100)) + (0.625*(Table1[[#This Row],[skill_long_passing]]/100) + 0.1875*(Table1[[#This Row],[skill_fk_accuracy]]/100) + 0.1875*(Table1[[#This Row],[attacking_crossing]]/100)) - ((1 - ((0.75*(Table1[[#This Row],[attacking_short_passing]]/100) + 0.25*(Table1[[#This Row],[attacking_crossing]]/100) - (0.625*(Table1[[#This Row],[skill_long_passing]]/100) + 0.1875*(Table1[[#This Row],[skill_fk_accuracy]]/100) + 0.1875*(Table1[[#This Row],[attacking_crossing]]/100)))^2))  * ((1 - (Table1[[#This Row],[mentality_vision]]/100))^2))</f>
+        <v>2.3422893789062496</v>
+      </c>
+      <c r="DL20">
+        <f>1.585332 + 0.008219*Table1[[#This Row],[power_jumping]]+ 0.047559*Table1[[#This Row],[pace]] + 0.012348*Table1[[#This Row],[attacking_heading_accuracy]] + 0.362187*Table1[[#This Row],[develle_mcharo_passing]] + 0.015238*Table1[[#This Row],[dribbling]] + 0.189748*Table1[[#This Row],[weak_foot]] + 0.033917*Table1[[#This Row],[power_strength]] + 0.26019*Table1[[#This Row],[skill_moves]] + 0.808787*Table1[[#This Row],[Defender]] + 0.472467*Table1[[#This Row],[Midfielder]] + 0.081427*Table1[[#This Row],[Finesse_Shot]]</f>
+        <v>12.520302763277916</v>
+      </c>
     </row>
-    <row r="21" spans="1:114" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:116" x14ac:dyDescent="0.2">
       <c r="A21">
         <v>210008</v>
       </c>
@@ -10212,8 +10388,16 @@
       <c r="DJ21" t="s">
         <v>420</v>
       </c>
+      <c r="DK21">
+        <f xml:space="preserve"> (Table1[[#This Row],[mentality_vision]]/100) + 0.809*(Table1[[#This Row],[skill_curve]]/100) + (0.75*(Table1[[#This Row],[attacking_short_passing]]/100) + 0.25*(Table1[[#This Row],[attacking_crossing]]/100)) + (0.625*(Table1[[#This Row],[skill_long_passing]]/100) + 0.1875*(Table1[[#This Row],[skill_fk_accuracy]]/100) + 0.1875*(Table1[[#This Row],[attacking_crossing]]/100)) - ((1 - ((0.75*(Table1[[#This Row],[attacking_short_passing]]/100) + 0.25*(Table1[[#This Row],[attacking_crossing]]/100) - (0.625*(Table1[[#This Row],[skill_long_passing]]/100) + 0.1875*(Table1[[#This Row],[skill_fk_accuracy]]/100) + 0.1875*(Table1[[#This Row],[attacking_crossing]]/100)))^2))  * ((1 - (Table1[[#This Row],[mentality_vision]]/100))^2))</f>
+        <v>2.9944914099999997</v>
+      </c>
+      <c r="DL21">
+        <f>1.585332 + 0.008219*Table1[[#This Row],[power_jumping]]+ 0.047559*Table1[[#This Row],[pace]] + 0.012348*Table1[[#This Row],[attacking_heading_accuracy]] + 0.362187*Table1[[#This Row],[develle_mcharo_passing]] + 0.015238*Table1[[#This Row],[dribbling]] + 0.189748*Table1[[#This Row],[weak_foot]] + 0.033917*Table1[[#This Row],[power_strength]] + 0.26019*Table1[[#This Row],[skill_moves]] + 0.808787*Table1[[#This Row],[Defender]] + 0.472467*Table1[[#This Row],[Midfielder]] + 0.081427*Table1[[#This Row],[Finesse_Shot]]</f>
+        <v>14.109285860313671</v>
+      </c>
     </row>
-    <row r="22" spans="1:114" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:116" x14ac:dyDescent="0.2">
       <c r="A22">
         <v>192883</v>
       </c>
@@ -10536,8 +10720,16 @@
       <c r="DJ22" t="s">
         <v>427</v>
       </c>
+      <c r="DK22">
+        <f xml:space="preserve"> (Table1[[#This Row],[mentality_vision]]/100) + 0.809*(Table1[[#This Row],[skill_curve]]/100) + (0.75*(Table1[[#This Row],[attacking_short_passing]]/100) + 0.25*(Table1[[#This Row],[attacking_crossing]]/100)) + (0.625*(Table1[[#This Row],[skill_long_passing]]/100) + 0.1875*(Table1[[#This Row],[skill_fk_accuracy]]/100) + 0.1875*(Table1[[#This Row],[attacking_crossing]]/100)) - ((1 - ((0.75*(Table1[[#This Row],[attacking_short_passing]]/100) + 0.25*(Table1[[#This Row],[attacking_crossing]]/100) - (0.625*(Table1[[#This Row],[skill_long_passing]]/100) + 0.1875*(Table1[[#This Row],[skill_fk_accuracy]]/100) + 0.1875*(Table1[[#This Row],[attacking_crossing]]/100)))^2))  * ((1 - (Table1[[#This Row],[mentality_vision]]/100))^2))</f>
+        <v>3.0977926099999995</v>
+      </c>
+      <c r="DL22">
+        <f>1.585332 + 0.008219*Table1[[#This Row],[power_jumping]]+ 0.047559*Table1[[#This Row],[pace]] + 0.012348*Table1[[#This Row],[attacking_heading_accuracy]] + 0.362187*Table1[[#This Row],[develle_mcharo_passing]] + 0.015238*Table1[[#This Row],[dribbling]] + 0.189748*Table1[[#This Row],[weak_foot]] + 0.033917*Table1[[#This Row],[power_strength]] + 0.26019*Table1[[#This Row],[skill_moves]] + 0.808787*Table1[[#This Row],[Defender]] + 0.472467*Table1[[#This Row],[Midfielder]] + 0.081427*Table1[[#This Row],[Finesse_Shot]]</f>
+        <v>13.841042212038071</v>
+      </c>
     </row>
-    <row r="23" spans="1:114" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:116" x14ac:dyDescent="0.2">
       <c r="A23">
         <v>177003</v>
       </c>
@@ -10872,8 +11064,16 @@
       <c r="DJ23" t="s">
         <v>434</v>
       </c>
+      <c r="DK23">
+        <f xml:space="preserve"> (Table1[[#This Row],[mentality_vision]]/100) + 0.809*(Table1[[#This Row],[skill_curve]]/100) + (0.75*(Table1[[#This Row],[attacking_short_passing]]/100) + 0.25*(Table1[[#This Row],[attacking_crossing]]/100)) + (0.625*(Table1[[#This Row],[skill_long_passing]]/100) + 0.1875*(Table1[[#This Row],[skill_fk_accuracy]]/100) + 0.1875*(Table1[[#This Row],[attacking_crossing]]/100)) - ((1 - ((0.75*(Table1[[#This Row],[attacking_short_passing]]/100) + 0.25*(Table1[[#This Row],[attacking_crossing]]/100) - (0.625*(Table1[[#This Row],[skill_long_passing]]/100) + 0.1875*(Table1[[#This Row],[skill_fk_accuracy]]/100) + 0.1875*(Table1[[#This Row],[attacking_crossing]]/100)))^2))  * ((1 - (Table1[[#This Row],[mentality_vision]]/100))^2))</f>
+        <v>3.2657572899999998</v>
+      </c>
+      <c r="DL23">
+        <f>1.585332 + 0.008219*Table1[[#This Row],[power_jumping]]+ 0.047559*Table1[[#This Row],[pace]] + 0.012348*Table1[[#This Row],[attacking_heading_accuracy]] + 0.362187*Table1[[#This Row],[develle_mcharo_passing]] + 0.015238*Table1[[#This Row],[dribbling]] + 0.189748*Table1[[#This Row],[weak_foot]] + 0.033917*Table1[[#This Row],[power_strength]] + 0.26019*Table1[[#This Row],[skill_moves]] + 0.808787*Table1[[#This Row],[Defender]] + 0.472467*Table1[[#This Row],[Midfielder]] + 0.081427*Table1[[#This Row],[Finesse_Shot]]</f>
+        <v>12.773625835593229</v>
+      </c>
     </row>
-    <row r="24" spans="1:114" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:116" x14ac:dyDescent="0.2">
       <c r="A24">
         <v>217870</v>
       </c>
@@ -11205,8 +11405,16 @@
       <c r="DJ24" t="s">
         <v>439</v>
       </c>
+      <c r="DK24">
+        <f xml:space="preserve"> (Table1[[#This Row],[mentality_vision]]/100) + 0.809*(Table1[[#This Row],[skill_curve]]/100) + (0.75*(Table1[[#This Row],[attacking_short_passing]]/100) + 0.25*(Table1[[#This Row],[attacking_crossing]]/100)) + (0.625*(Table1[[#This Row],[skill_long_passing]]/100) + 0.1875*(Table1[[#This Row],[skill_fk_accuracy]]/100) + 0.1875*(Table1[[#This Row],[attacking_crossing]]/100)) - ((1 - ((0.75*(Table1[[#This Row],[attacking_short_passing]]/100) + 0.25*(Table1[[#This Row],[attacking_crossing]]/100) - (0.625*(Table1[[#This Row],[skill_long_passing]]/100) + 0.1875*(Table1[[#This Row],[skill_fk_accuracy]]/100) + 0.1875*(Table1[[#This Row],[attacking_crossing]]/100)))^2))  * ((1 - (Table1[[#This Row],[mentality_vision]]/100))^2))</f>
+        <v>2.6092181600000002</v>
+      </c>
+      <c r="DL24">
+        <f>1.585332 + 0.008219*Table1[[#This Row],[power_jumping]]+ 0.047559*Table1[[#This Row],[pace]] + 0.012348*Table1[[#This Row],[attacking_heading_accuracy]] + 0.362187*Table1[[#This Row],[develle_mcharo_passing]] + 0.015238*Table1[[#This Row],[dribbling]] + 0.189748*Table1[[#This Row],[weak_foot]] + 0.033917*Table1[[#This Row],[power_strength]] + 0.26019*Table1[[#This Row],[skill_moves]] + 0.808787*Table1[[#This Row],[Defender]] + 0.472467*Table1[[#This Row],[Midfielder]] + 0.081427*Table1[[#This Row],[Finesse_Shot]]</f>
+        <v>14.136297897715918</v>
+      </c>
     </row>
-    <row r="25" spans="1:114" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:116" x14ac:dyDescent="0.2">
       <c r="A25">
         <v>216435</v>
       </c>
@@ -11529,8 +11737,16 @@
       <c r="DJ25" t="s">
         <v>446</v>
       </c>
+      <c r="DK25">
+        <f xml:space="preserve"> (Table1[[#This Row],[mentality_vision]]/100) + 0.809*(Table1[[#This Row],[skill_curve]]/100) + (0.75*(Table1[[#This Row],[attacking_short_passing]]/100) + 0.25*(Table1[[#This Row],[attacking_crossing]]/100)) + (0.625*(Table1[[#This Row],[skill_long_passing]]/100) + 0.1875*(Table1[[#This Row],[skill_fk_accuracy]]/100) + 0.1875*(Table1[[#This Row],[attacking_crossing]]/100)) - ((1 - ((0.75*(Table1[[#This Row],[attacking_short_passing]]/100) + 0.25*(Table1[[#This Row],[attacking_crossing]]/100) - (0.625*(Table1[[#This Row],[skill_long_passing]]/100) + 0.1875*(Table1[[#This Row],[skill_fk_accuracy]]/100) + 0.1875*(Table1[[#This Row],[attacking_crossing]]/100)))^2))  * ((1 - (Table1[[#This Row],[mentality_vision]]/100))^2))</f>
+        <v>2.9944309999999996</v>
+      </c>
+      <c r="DL25">
+        <f>1.585332 + 0.008219*Table1[[#This Row],[power_jumping]]+ 0.047559*Table1[[#This Row],[pace]] + 0.012348*Table1[[#This Row],[attacking_heading_accuracy]] + 0.362187*Table1[[#This Row],[develle_mcharo_passing]] + 0.015238*Table1[[#This Row],[dribbling]] + 0.189748*Table1[[#This Row],[weak_foot]] + 0.033917*Table1[[#This Row],[power_strength]] + 0.26019*Table1[[#This Row],[skill_moves]] + 0.808787*Table1[[#This Row],[Defender]] + 0.472467*Table1[[#This Row],[Midfielder]] + 0.081427*Table1[[#This Row],[Finesse_Shot]]</f>
+        <v>12.466941980596998</v>
+      </c>
     </row>
-    <row r="26" spans="1:114" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:116" x14ac:dyDescent="0.2">
       <c r="A26">
         <v>243580</v>
       </c>
@@ -11853,8 +12069,16 @@
       <c r="DJ26" t="s">
         <v>454</v>
       </c>
+      <c r="DK26">
+        <f xml:space="preserve"> (Table1[[#This Row],[mentality_vision]]/100) + 0.809*(Table1[[#This Row],[skill_curve]]/100) + (0.75*(Table1[[#This Row],[attacking_short_passing]]/100) + 0.25*(Table1[[#This Row],[attacking_crossing]]/100)) + (0.625*(Table1[[#This Row],[skill_long_passing]]/100) + 0.1875*(Table1[[#This Row],[skill_fk_accuracy]]/100) + 0.1875*(Table1[[#This Row],[attacking_crossing]]/100)) - ((1 - ((0.75*(Table1[[#This Row],[attacking_short_passing]]/100) + 0.25*(Table1[[#This Row],[attacking_crossing]]/100) - (0.625*(Table1[[#This Row],[skill_long_passing]]/100) + 0.1875*(Table1[[#This Row],[skill_fk_accuracy]]/100) + 0.1875*(Table1[[#This Row],[attacking_crossing]]/100)))^2))  * ((1 - (Table1[[#This Row],[mentality_vision]]/100))^2))</f>
+        <v>2.4621568906250002</v>
+      </c>
+      <c r="DL26">
+        <f>1.585332 + 0.008219*Table1[[#This Row],[power_jumping]]+ 0.047559*Table1[[#This Row],[pace]] + 0.012348*Table1[[#This Row],[attacking_heading_accuracy]] + 0.362187*Table1[[#This Row],[develle_mcharo_passing]] + 0.015238*Table1[[#This Row],[dribbling]] + 0.189748*Table1[[#This Row],[weak_foot]] + 0.033917*Table1[[#This Row],[power_strength]] + 0.26019*Table1[[#This Row],[skill_moves]] + 0.808787*Table1[[#This Row],[Defender]] + 0.472467*Table1[[#This Row],[Midfielder]] + 0.081427*Table1[[#This Row],[Finesse_Shot]]</f>
+        <v>14.303684217744793</v>
+      </c>
     </row>
-    <row r="27" spans="1:114" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:116" x14ac:dyDescent="0.2">
       <c r="A27">
         <v>242458</v>
       </c>
@@ -12183,8 +12407,16 @@
       <c r="DJ27" t="s">
         <v>460</v>
       </c>
+      <c r="DK27">
+        <f xml:space="preserve"> (Table1[[#This Row],[mentality_vision]]/100) + 0.809*(Table1[[#This Row],[skill_curve]]/100) + (0.75*(Table1[[#This Row],[attacking_short_passing]]/100) + 0.25*(Table1[[#This Row],[attacking_crossing]]/100)) + (0.625*(Table1[[#This Row],[skill_long_passing]]/100) + 0.1875*(Table1[[#This Row],[skill_fk_accuracy]]/100) + 0.1875*(Table1[[#This Row],[attacking_crossing]]/100)) - ((1 - ((0.75*(Table1[[#This Row],[attacking_short_passing]]/100) + 0.25*(Table1[[#This Row],[attacking_crossing]]/100) - (0.625*(Table1[[#This Row],[skill_long_passing]]/100) + 0.1875*(Table1[[#This Row],[skill_fk_accuracy]]/100) + 0.1875*(Table1[[#This Row],[attacking_crossing]]/100)))^2))  * ((1 - (Table1[[#This Row],[mentality_vision]]/100))^2))</f>
+        <v>2.4943036099999998</v>
+      </c>
+      <c r="DL27">
+        <f>1.585332 + 0.008219*Table1[[#This Row],[power_jumping]]+ 0.047559*Table1[[#This Row],[pace]] + 0.012348*Table1[[#This Row],[attacking_heading_accuracy]] + 0.362187*Table1[[#This Row],[develle_mcharo_passing]] + 0.015238*Table1[[#This Row],[dribbling]] + 0.189748*Table1[[#This Row],[weak_foot]] + 0.033917*Table1[[#This Row],[power_strength]] + 0.26019*Table1[[#This Row],[skill_moves]] + 0.808787*Table1[[#This Row],[Defender]] + 0.472467*Table1[[#This Row],[Midfielder]] + 0.081427*Table1[[#This Row],[Finesse_Shot]]</f>
+        <v>13.67512834159507</v>
+      </c>
     </row>
-    <row r="28" spans="1:114" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:116" x14ac:dyDescent="0.2">
       <c r="A28">
         <v>236610</v>
       </c>
@@ -12516,8 +12748,16 @@
       <c r="DJ28" t="s">
         <v>466</v>
       </c>
+      <c r="DK28">
+        <f xml:space="preserve"> (Table1[[#This Row],[mentality_vision]]/100) + 0.809*(Table1[[#This Row],[skill_curve]]/100) + (0.75*(Table1[[#This Row],[attacking_short_passing]]/100) + 0.25*(Table1[[#This Row],[attacking_crossing]]/100)) + (0.625*(Table1[[#This Row],[skill_long_passing]]/100) + 0.1875*(Table1[[#This Row],[skill_fk_accuracy]]/100) + 0.1875*(Table1[[#This Row],[attacking_crossing]]/100)) - ((1 - ((0.75*(Table1[[#This Row],[attacking_short_passing]]/100) + 0.25*(Table1[[#This Row],[attacking_crossing]]/100) - (0.625*(Table1[[#This Row],[skill_long_passing]]/100) + 0.1875*(Table1[[#This Row],[skill_fk_accuracy]]/100) + 0.1875*(Table1[[#This Row],[attacking_crossing]]/100)))^2))  * ((1 - (Table1[[#This Row],[mentality_vision]]/100))^2))</f>
+        <v>2.0772011764062501</v>
+      </c>
+      <c r="DL28">
+        <f>1.585332 + 0.008219*Table1[[#This Row],[power_jumping]]+ 0.047559*Table1[[#This Row],[pace]] + 0.012348*Table1[[#This Row],[attacking_heading_accuracy]] + 0.362187*Table1[[#This Row],[develle_mcharo_passing]] + 0.015238*Table1[[#This Row],[dribbling]] + 0.189748*Table1[[#This Row],[weak_foot]] + 0.033917*Table1[[#This Row],[power_strength]] + 0.26019*Table1[[#This Row],[skill_moves]] + 0.808787*Table1[[#This Row],[Defender]] + 0.472467*Table1[[#This Row],[Midfielder]] + 0.081427*Table1[[#This Row],[Finesse_Shot]]</f>
+        <v>13.21023226247905</v>
+      </c>
     </row>
-    <row r="29" spans="1:114" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:116" x14ac:dyDescent="0.2">
       <c r="A29">
         <v>244263</v>
       </c>
@@ -12840,8 +13080,16 @@
       <c r="DJ29" t="s">
         <v>472</v>
       </c>
+      <c r="DK29">
+        <f xml:space="preserve"> (Table1[[#This Row],[mentality_vision]]/100) + 0.809*(Table1[[#This Row],[skill_curve]]/100) + (0.75*(Table1[[#This Row],[attacking_short_passing]]/100) + 0.25*(Table1[[#This Row],[attacking_crossing]]/100)) + (0.625*(Table1[[#This Row],[skill_long_passing]]/100) + 0.1875*(Table1[[#This Row],[skill_fk_accuracy]]/100) + 0.1875*(Table1[[#This Row],[attacking_crossing]]/100)) - ((1 - ((0.75*(Table1[[#This Row],[attacking_short_passing]]/100) + 0.25*(Table1[[#This Row],[attacking_crossing]]/100) - (0.625*(Table1[[#This Row],[skill_long_passing]]/100) + 0.1875*(Table1[[#This Row],[skill_fk_accuracy]]/100) + 0.1875*(Table1[[#This Row],[attacking_crossing]]/100)))^2))  * ((1 - (Table1[[#This Row],[mentality_vision]]/100))^2))</f>
+        <v>1.8791566025000002</v>
+      </c>
+      <c r="DL29">
+        <f>1.585332 + 0.008219*Table1[[#This Row],[power_jumping]]+ 0.047559*Table1[[#This Row],[pace]] + 0.012348*Table1[[#This Row],[attacking_heading_accuracy]] + 0.362187*Table1[[#This Row],[develle_mcharo_passing]] + 0.015238*Table1[[#This Row],[dribbling]] + 0.189748*Table1[[#This Row],[weak_foot]] + 0.033917*Table1[[#This Row],[power_strength]] + 0.26019*Table1[[#This Row],[skill_moves]] + 0.808787*Table1[[#This Row],[Defender]] + 0.472467*Table1[[#This Row],[Midfielder]] + 0.081427*Table1[[#This Row],[Finesse_Shot]]</f>
+        <v>12.974949092389668</v>
+      </c>
     </row>
-    <row r="30" spans="1:114" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:116" x14ac:dyDescent="0.2">
       <c r="A30">
         <v>229582</v>
       </c>
@@ -13173,8 +13421,16 @@
       <c r="DJ30" t="s">
         <v>477</v>
       </c>
+      <c r="DK30">
+        <f xml:space="preserve"> (Table1[[#This Row],[mentality_vision]]/100) + 0.809*(Table1[[#This Row],[skill_curve]]/100) + (0.75*(Table1[[#This Row],[attacking_short_passing]]/100) + 0.25*(Table1[[#This Row],[attacking_crossing]]/100)) + (0.625*(Table1[[#This Row],[skill_long_passing]]/100) + 0.1875*(Table1[[#This Row],[skill_fk_accuracy]]/100) + 0.1875*(Table1[[#This Row],[attacking_crossing]]/100)) - ((1 - ((0.75*(Table1[[#This Row],[attacking_short_passing]]/100) + 0.25*(Table1[[#This Row],[attacking_crossing]]/100) - (0.625*(Table1[[#This Row],[skill_long_passing]]/100) + 0.1875*(Table1[[#This Row],[skill_fk_accuracy]]/100) + 0.1875*(Table1[[#This Row],[attacking_crossing]]/100)))^2))  * ((1 - (Table1[[#This Row],[mentality_vision]]/100))^2))</f>
+        <v>1.8615244900000001</v>
+      </c>
+      <c r="DL30">
+        <f>1.585332 + 0.008219*Table1[[#This Row],[power_jumping]]+ 0.047559*Table1[[#This Row],[pace]] + 0.012348*Table1[[#This Row],[attacking_heading_accuracy]] + 0.362187*Table1[[#This Row],[develle_mcharo_passing]] + 0.015238*Table1[[#This Row],[dribbling]] + 0.189748*Table1[[#This Row],[weak_foot]] + 0.033917*Table1[[#This Row],[power_strength]] + 0.26019*Table1[[#This Row],[skill_moves]] + 0.808787*Table1[[#This Row],[Defender]] + 0.472467*Table1[[#This Row],[Midfielder]] + 0.081427*Table1[[#This Row],[Finesse_Shot]]</f>
+        <v>12.87761497045963</v>
+      </c>
     </row>
-    <row r="31" spans="1:114" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:116" x14ac:dyDescent="0.2">
       <c r="A31">
         <v>236496</v>
       </c>
@@ -13506,8 +13762,16 @@
       <c r="DJ31" t="s">
         <v>482</v>
       </c>
+      <c r="DK31">
+        <f xml:space="preserve"> (Table1[[#This Row],[mentality_vision]]/100) + 0.809*(Table1[[#This Row],[skill_curve]]/100) + (0.75*(Table1[[#This Row],[attacking_short_passing]]/100) + 0.25*(Table1[[#This Row],[attacking_crossing]]/100)) + (0.625*(Table1[[#This Row],[skill_long_passing]]/100) + 0.1875*(Table1[[#This Row],[skill_fk_accuracy]]/100) + 0.1875*(Table1[[#This Row],[attacking_crossing]]/100)) - ((1 - ((0.75*(Table1[[#This Row],[attacking_short_passing]]/100) + 0.25*(Table1[[#This Row],[attacking_crossing]]/100) - (0.625*(Table1[[#This Row],[skill_long_passing]]/100) + 0.1875*(Table1[[#This Row],[skill_fk_accuracy]]/100) + 0.1875*(Table1[[#This Row],[attacking_crossing]]/100)))^2))  * ((1 - (Table1[[#This Row],[mentality_vision]]/100))^2))</f>
+        <v>2.98792225</v>
+      </c>
+      <c r="DL31">
+        <f>1.585332 + 0.008219*Table1[[#This Row],[power_jumping]]+ 0.047559*Table1[[#This Row],[pace]] + 0.012348*Table1[[#This Row],[attacking_heading_accuracy]] + 0.362187*Table1[[#This Row],[develle_mcharo_passing]] + 0.015238*Table1[[#This Row],[dribbling]] + 0.189748*Table1[[#This Row],[weak_foot]] + 0.033917*Table1[[#This Row],[power_strength]] + 0.26019*Table1[[#This Row],[skill_moves]] + 0.808787*Table1[[#This Row],[Defender]] + 0.472467*Table1[[#This Row],[Midfielder]] + 0.081427*Table1[[#This Row],[Finesse_Shot]]</f>
+        <v>13.117715595960751</v>
+      </c>
     </row>
-    <row r="32" spans="1:114" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:116" x14ac:dyDescent="0.2">
       <c r="A32">
         <v>227236</v>
       </c>
@@ -13830,8 +14094,16 @@
       <c r="DJ32" t="s">
         <v>489</v>
       </c>
+      <c r="DK32">
+        <f xml:space="preserve"> (Table1[[#This Row],[mentality_vision]]/100) + 0.809*(Table1[[#This Row],[skill_curve]]/100) + (0.75*(Table1[[#This Row],[attacking_short_passing]]/100) + 0.25*(Table1[[#This Row],[attacking_crossing]]/100)) + (0.625*(Table1[[#This Row],[skill_long_passing]]/100) + 0.1875*(Table1[[#This Row],[skill_fk_accuracy]]/100) + 0.1875*(Table1[[#This Row],[attacking_crossing]]/100)) - ((1 - ((0.75*(Table1[[#This Row],[attacking_short_passing]]/100) + 0.25*(Table1[[#This Row],[attacking_crossing]]/100) - (0.625*(Table1[[#This Row],[skill_long_passing]]/100) + 0.1875*(Table1[[#This Row],[skill_fk_accuracy]]/100) + 0.1875*(Table1[[#This Row],[attacking_crossing]]/100)))^2))  * ((1 - (Table1[[#This Row],[mentality_vision]]/100))^2))</f>
+        <v>2.7361865624999999</v>
+      </c>
+      <c r="DL32">
+        <f>1.585332 + 0.008219*Table1[[#This Row],[power_jumping]]+ 0.047559*Table1[[#This Row],[pace]] + 0.012348*Table1[[#This Row],[attacking_heading_accuracy]] + 0.362187*Table1[[#This Row],[develle_mcharo_passing]] + 0.015238*Table1[[#This Row],[dribbling]] + 0.189748*Table1[[#This Row],[weak_foot]] + 0.033917*Table1[[#This Row],[power_strength]] + 0.26019*Table1[[#This Row],[skill_moves]] + 0.808787*Table1[[#This Row],[Defender]] + 0.472467*Table1[[#This Row],[Midfielder]] + 0.081427*Table1[[#This Row],[Finesse_Shot]]</f>
+        <v>13.604046202512189</v>
+      </c>
     </row>
-    <row r="33" spans="1:114" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:116" x14ac:dyDescent="0.2">
       <c r="A33">
         <v>266866</v>
       </c>
@@ -14154,8 +14426,16 @@
       <c r="DJ33" t="s">
         <v>494</v>
       </c>
+      <c r="DK33">
+        <f xml:space="preserve"> (Table1[[#This Row],[mentality_vision]]/100) + 0.809*(Table1[[#This Row],[skill_curve]]/100) + (0.75*(Table1[[#This Row],[attacking_short_passing]]/100) + 0.25*(Table1[[#This Row],[attacking_crossing]]/100)) + (0.625*(Table1[[#This Row],[skill_long_passing]]/100) + 0.1875*(Table1[[#This Row],[skill_fk_accuracy]]/100) + 0.1875*(Table1[[#This Row],[attacking_crossing]]/100)) - ((1 - ((0.75*(Table1[[#This Row],[attacking_short_passing]]/100) + 0.25*(Table1[[#This Row],[attacking_crossing]]/100) - (0.625*(Table1[[#This Row],[skill_long_passing]]/100) + 0.1875*(Table1[[#This Row],[skill_fk_accuracy]]/100) + 0.1875*(Table1[[#This Row],[attacking_crossing]]/100)))^2))  * ((1 - (Table1[[#This Row],[mentality_vision]]/100))^2))</f>
+        <v>2.8285322499999994</v>
+      </c>
+      <c r="DL33">
+        <f>1.585332 + 0.008219*Table1[[#This Row],[power_jumping]]+ 0.047559*Table1[[#This Row],[pace]] + 0.012348*Table1[[#This Row],[attacking_heading_accuracy]] + 0.362187*Table1[[#This Row],[develle_mcharo_passing]] + 0.015238*Table1[[#This Row],[dribbling]] + 0.189748*Table1[[#This Row],[weak_foot]] + 0.033917*Table1[[#This Row],[power_strength]] + 0.26019*Table1[[#This Row],[skill_moves]] + 0.808787*Table1[[#This Row],[Defender]] + 0.472467*Table1[[#This Row],[Midfielder]] + 0.081427*Table1[[#This Row],[Finesse_Shot]]</f>
+        <v>13.432461610030748</v>
+      </c>
     </row>
-    <row r="34" spans="1:114" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:116" x14ac:dyDescent="0.2">
       <c r="A34">
         <v>251470</v>
       </c>
@@ -14478,8 +14758,16 @@
       <c r="DJ34" t="s">
         <v>499</v>
       </c>
+      <c r="DK34">
+        <f xml:space="preserve"> (Table1[[#This Row],[mentality_vision]]/100) + 0.809*(Table1[[#This Row],[skill_curve]]/100) + (0.75*(Table1[[#This Row],[attacking_short_passing]]/100) + 0.25*(Table1[[#This Row],[attacking_crossing]]/100)) + (0.625*(Table1[[#This Row],[skill_long_passing]]/100) + 0.1875*(Table1[[#This Row],[skill_fk_accuracy]]/100) + 0.1875*(Table1[[#This Row],[attacking_crossing]]/100)) - ((1 - ((0.75*(Table1[[#This Row],[attacking_short_passing]]/100) + 0.25*(Table1[[#This Row],[attacking_crossing]]/100) - (0.625*(Table1[[#This Row],[skill_long_passing]]/100) + 0.1875*(Table1[[#This Row],[skill_fk_accuracy]]/100) + 0.1875*(Table1[[#This Row],[attacking_crossing]]/100)))^2))  * ((1 - (Table1[[#This Row],[mentality_vision]]/100))^2))</f>
+        <v>3.0221554025000001</v>
+      </c>
+      <c r="DL34">
+        <f>1.585332 + 0.008219*Table1[[#This Row],[power_jumping]]+ 0.047559*Table1[[#This Row],[pace]] + 0.012348*Table1[[#This Row],[attacking_heading_accuracy]] + 0.362187*Table1[[#This Row],[develle_mcharo_passing]] + 0.015238*Table1[[#This Row],[dribbling]] + 0.189748*Table1[[#This Row],[weak_foot]] + 0.033917*Table1[[#This Row],[power_strength]] + 0.26019*Table1[[#This Row],[skill_moves]] + 0.808787*Table1[[#This Row],[Defender]] + 0.472467*Table1[[#This Row],[Midfielder]] + 0.081427*Table1[[#This Row],[Finesse_Shot]]</f>
+        <v>12.757343398765267</v>
+      </c>
     </row>
-    <row r="35" spans="1:114" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:116" x14ac:dyDescent="0.2">
       <c r="A35">
         <v>233556</v>
       </c>
@@ -14811,8 +15099,16 @@
       <c r="DJ35" t="s">
         <v>505</v>
       </c>
+      <c r="DK35">
+        <f xml:space="preserve"> (Table1[[#This Row],[mentality_vision]]/100) + 0.809*(Table1[[#This Row],[skill_curve]]/100) + (0.75*(Table1[[#This Row],[attacking_short_passing]]/100) + 0.25*(Table1[[#This Row],[attacking_crossing]]/100)) + (0.625*(Table1[[#This Row],[skill_long_passing]]/100) + 0.1875*(Table1[[#This Row],[skill_fk_accuracy]]/100) + 0.1875*(Table1[[#This Row],[attacking_crossing]]/100)) - ((1 - ((0.75*(Table1[[#This Row],[attacking_short_passing]]/100) + 0.25*(Table1[[#This Row],[attacking_crossing]]/100) - (0.625*(Table1[[#This Row],[skill_long_passing]]/100) + 0.1875*(Table1[[#This Row],[skill_fk_accuracy]]/100) + 0.1875*(Table1[[#This Row],[attacking_crossing]]/100)))^2))  * ((1 - (Table1[[#This Row],[mentality_vision]]/100))^2))</f>
+        <v>2.9488123556249999</v>
+      </c>
+      <c r="DL35">
+        <f>1.585332 + 0.008219*Table1[[#This Row],[power_jumping]]+ 0.047559*Table1[[#This Row],[pace]] + 0.012348*Table1[[#This Row],[attacking_heading_accuracy]] + 0.362187*Table1[[#This Row],[develle_mcharo_passing]] + 0.015238*Table1[[#This Row],[dribbling]] + 0.189748*Table1[[#This Row],[weak_foot]] + 0.033917*Table1[[#This Row],[power_strength]] + 0.26019*Table1[[#This Row],[skill_moves]] + 0.808787*Table1[[#This Row],[Defender]] + 0.472467*Table1[[#This Row],[Midfielder]] + 0.081427*Table1[[#This Row],[Finesse_Shot]]</f>
+        <v>13.358864500646753</v>
+      </c>
     </row>
-    <row r="36" spans="1:114" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:116" x14ac:dyDescent="0.2">
       <c r="A36">
         <v>210935</v>
       </c>
@@ -15138,8 +15434,16 @@
       <c r="DJ36" t="s">
         <v>512</v>
       </c>
+      <c r="DK36">
+        <f xml:space="preserve"> (Table1[[#This Row],[mentality_vision]]/100) + 0.809*(Table1[[#This Row],[skill_curve]]/100) + (0.75*(Table1[[#This Row],[attacking_short_passing]]/100) + 0.25*(Table1[[#This Row],[attacking_crossing]]/100)) + (0.625*(Table1[[#This Row],[skill_long_passing]]/100) + 0.1875*(Table1[[#This Row],[skill_fk_accuracy]]/100) + 0.1875*(Table1[[#This Row],[attacking_crossing]]/100)) - ((1 - ((0.75*(Table1[[#This Row],[attacking_short_passing]]/100) + 0.25*(Table1[[#This Row],[attacking_crossing]]/100) - (0.625*(Table1[[#This Row],[skill_long_passing]]/100) + 0.1875*(Table1[[#This Row],[skill_fk_accuracy]]/100) + 0.1875*(Table1[[#This Row],[attacking_crossing]]/100)))^2))  * ((1 - (Table1[[#This Row],[mentality_vision]]/100))^2))</f>
+        <v>3.0133375625000003</v>
+      </c>
+      <c r="DL36">
+        <f>1.585332 + 0.008219*Table1[[#This Row],[power_jumping]]+ 0.047559*Table1[[#This Row],[pace]] + 0.012348*Table1[[#This Row],[attacking_heading_accuracy]] + 0.362187*Table1[[#This Row],[develle_mcharo_passing]] + 0.015238*Table1[[#This Row],[dribbling]] + 0.189748*Table1[[#This Row],[weak_foot]] + 0.033917*Table1[[#This Row],[power_strength]] + 0.26019*Table1[[#This Row],[skill_moves]] + 0.808787*Table1[[#This Row],[Defender]] + 0.472467*Table1[[#This Row],[Midfielder]] + 0.081427*Table1[[#This Row],[Finesse_Shot]]</f>
+        <v>12.880733691749187</v>
+      </c>
     </row>
-    <row r="37" spans="1:114" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:116" x14ac:dyDescent="0.2">
       <c r="A37">
         <v>246430</v>
       </c>
@@ -15465,8 +15769,16 @@
       <c r="DJ37" t="s">
         <v>518</v>
       </c>
+      <c r="DK37">
+        <f xml:space="preserve"> (Table1[[#This Row],[mentality_vision]]/100) + 0.809*(Table1[[#This Row],[skill_curve]]/100) + (0.75*(Table1[[#This Row],[attacking_short_passing]]/100) + 0.25*(Table1[[#This Row],[attacking_crossing]]/100)) + (0.625*(Table1[[#This Row],[skill_long_passing]]/100) + 0.1875*(Table1[[#This Row],[skill_fk_accuracy]]/100) + 0.1875*(Table1[[#This Row],[attacking_crossing]]/100)) - ((1 - ((0.75*(Table1[[#This Row],[attacking_short_passing]]/100) + 0.25*(Table1[[#This Row],[attacking_crossing]]/100) - (0.625*(Table1[[#This Row],[skill_long_passing]]/100) + 0.1875*(Table1[[#This Row],[skill_fk_accuracy]]/100) + 0.1875*(Table1[[#This Row],[attacking_crossing]]/100)))^2))  * ((1 - (Table1[[#This Row],[mentality_vision]]/100))^2))</f>
+        <v>2.6031447656249997</v>
+      </c>
+      <c r="DL37">
+        <f>1.585332 + 0.008219*Table1[[#This Row],[power_jumping]]+ 0.047559*Table1[[#This Row],[pace]] + 0.012348*Table1[[#This Row],[attacking_heading_accuracy]] + 0.362187*Table1[[#This Row],[develle_mcharo_passing]] + 0.015238*Table1[[#This Row],[dribbling]] + 0.189748*Table1[[#This Row],[weak_foot]] + 0.033917*Table1[[#This Row],[power_strength]] + 0.26019*Table1[[#This Row],[skill_moves]] + 0.808787*Table1[[#This Row],[Defender]] + 0.472467*Table1[[#This Row],[Midfielder]] + 0.081427*Table1[[#This Row],[Finesse_Shot]]</f>
+        <v>13.71762019322742</v>
+      </c>
     </row>
-    <row r="38" spans="1:114" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:116" x14ac:dyDescent="0.2">
       <c r="A38">
         <v>243630</v>
       </c>
@@ -15789,8 +16101,16 @@
       <c r="DJ38" t="s">
         <v>524</v>
       </c>
+      <c r="DK38">
+        <f xml:space="preserve"> (Table1[[#This Row],[mentality_vision]]/100) + 0.809*(Table1[[#This Row],[skill_curve]]/100) + (0.75*(Table1[[#This Row],[attacking_short_passing]]/100) + 0.25*(Table1[[#This Row],[attacking_crossing]]/100)) + (0.625*(Table1[[#This Row],[skill_long_passing]]/100) + 0.1875*(Table1[[#This Row],[skill_fk_accuracy]]/100) + 0.1875*(Table1[[#This Row],[attacking_crossing]]/100)) - ((1 - ((0.75*(Table1[[#This Row],[attacking_short_passing]]/100) + 0.25*(Table1[[#This Row],[attacking_crossing]]/100) - (0.625*(Table1[[#This Row],[skill_long_passing]]/100) + 0.1875*(Table1[[#This Row],[skill_fk_accuracy]]/100) + 0.1875*(Table1[[#This Row],[attacking_crossing]]/100)))^2))  * ((1 - (Table1[[#This Row],[mentality_vision]]/100))^2))</f>
+        <v>2.5531842226562498</v>
+      </c>
+      <c r="DL38">
+        <f>1.585332 + 0.008219*Table1[[#This Row],[power_jumping]]+ 0.047559*Table1[[#This Row],[pace]] + 0.012348*Table1[[#This Row],[attacking_heading_accuracy]] + 0.362187*Table1[[#This Row],[develle_mcharo_passing]] + 0.015238*Table1[[#This Row],[dribbling]] + 0.189748*Table1[[#This Row],[weak_foot]] + 0.033917*Table1[[#This Row],[power_strength]] + 0.26019*Table1[[#This Row],[skill_moves]] + 0.808787*Table1[[#This Row],[Defender]] + 0.472467*Table1[[#This Row],[Midfielder]] + 0.081427*Table1[[#This Row],[Finesse_Shot]]</f>
+        <v>13.5881491340512</v>
+      </c>
     </row>
-    <row r="39" spans="1:114" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:116" x14ac:dyDescent="0.2">
       <c r="A39">
         <v>229237</v>
       </c>
@@ -16110,8 +16430,16 @@
       <c r="DJ39" t="s">
         <v>529</v>
       </c>
+      <c r="DK39">
+        <f xml:space="preserve"> (Table1[[#This Row],[mentality_vision]]/100) + 0.809*(Table1[[#This Row],[skill_curve]]/100) + (0.75*(Table1[[#This Row],[attacking_short_passing]]/100) + 0.25*(Table1[[#This Row],[attacking_crossing]]/100)) + (0.625*(Table1[[#This Row],[skill_long_passing]]/100) + 0.1875*(Table1[[#This Row],[skill_fk_accuracy]]/100) + 0.1875*(Table1[[#This Row],[attacking_crossing]]/100)) - ((1 - ((0.75*(Table1[[#This Row],[attacking_short_passing]]/100) + 0.25*(Table1[[#This Row],[attacking_crossing]]/100) - (0.625*(Table1[[#This Row],[skill_long_passing]]/100) + 0.1875*(Table1[[#This Row],[skill_fk_accuracy]]/100) + 0.1875*(Table1[[#This Row],[attacking_crossing]]/100)))^2))  * ((1 - (Table1[[#This Row],[mentality_vision]]/100))^2))</f>
+        <v>2.3895100625000003</v>
+      </c>
+      <c r="DL39">
+        <f>1.585332 + 0.008219*Table1[[#This Row],[power_jumping]]+ 0.047559*Table1[[#This Row],[pace]] + 0.012348*Table1[[#This Row],[attacking_heading_accuracy]] + 0.362187*Table1[[#This Row],[develle_mcharo_passing]] + 0.015238*Table1[[#This Row],[dribbling]] + 0.189748*Table1[[#This Row],[weak_foot]] + 0.033917*Table1[[#This Row],[power_strength]] + 0.26019*Table1[[#This Row],[skill_moves]] + 0.808787*Table1[[#This Row],[Defender]] + 0.472467*Table1[[#This Row],[Midfielder]] + 0.081427*Table1[[#This Row],[Finesse_Shot]]</f>
+        <v>13.694856481006687</v>
+      </c>
     </row>
-    <row r="40" spans="1:114" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:116" x14ac:dyDescent="0.2">
       <c r="A40">
         <v>215333</v>
       </c>
@@ -16437,8 +16765,16 @@
       <c r="DJ40" t="s">
         <v>536</v>
       </c>
+      <c r="DK40">
+        <f xml:space="preserve"> (Table1[[#This Row],[mentality_vision]]/100) + 0.809*(Table1[[#This Row],[skill_curve]]/100) + (0.75*(Table1[[#This Row],[attacking_short_passing]]/100) + 0.25*(Table1[[#This Row],[attacking_crossing]]/100)) + (0.625*(Table1[[#This Row],[skill_long_passing]]/100) + 0.1875*(Table1[[#This Row],[skill_fk_accuracy]]/100) + 0.1875*(Table1[[#This Row],[attacking_crossing]]/100)) - ((1 - ((0.75*(Table1[[#This Row],[attacking_short_passing]]/100) + 0.25*(Table1[[#This Row],[attacking_crossing]]/100) - (0.625*(Table1[[#This Row],[skill_long_passing]]/100) + 0.1875*(Table1[[#This Row],[skill_fk_accuracy]]/100) + 0.1875*(Table1[[#This Row],[attacking_crossing]]/100)))^2))  * ((1 - (Table1[[#This Row],[mentality_vision]]/100))^2))</f>
+        <v>2.28920144140625</v>
+      </c>
+      <c r="DL40">
+        <f>1.585332 + 0.008219*Table1[[#This Row],[power_jumping]]+ 0.047559*Table1[[#This Row],[pace]] + 0.012348*Table1[[#This Row],[attacking_heading_accuracy]] + 0.362187*Table1[[#This Row],[develle_mcharo_passing]] + 0.015238*Table1[[#This Row],[dribbling]] + 0.189748*Table1[[#This Row],[weak_foot]] + 0.033917*Table1[[#This Row],[power_strength]] + 0.26019*Table1[[#This Row],[skill_moves]] + 0.808787*Table1[[#This Row],[Defender]] + 0.472467*Table1[[#This Row],[Midfielder]] + 0.081427*Table1[[#This Row],[Finesse_Shot]]</f>
+        <v>13.537878002458605</v>
+      </c>
     </row>
-    <row r="41" spans="1:114" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:116" x14ac:dyDescent="0.2">
       <c r="A41">
         <v>243241</v>
       </c>
@@ -16761,8 +17097,16 @@
       <c r="DJ41" t="s">
         <v>541</v>
       </c>
+      <c r="DK41">
+        <f xml:space="preserve"> (Table1[[#This Row],[mentality_vision]]/100) + 0.809*(Table1[[#This Row],[skill_curve]]/100) + (0.75*(Table1[[#This Row],[attacking_short_passing]]/100) + 0.25*(Table1[[#This Row],[attacking_crossing]]/100)) + (0.625*(Table1[[#This Row],[skill_long_passing]]/100) + 0.1875*(Table1[[#This Row],[skill_fk_accuracy]]/100) + 0.1875*(Table1[[#This Row],[attacking_crossing]]/100)) - ((1 - ((0.75*(Table1[[#This Row],[attacking_short_passing]]/100) + 0.25*(Table1[[#This Row],[attacking_crossing]]/100) - (0.625*(Table1[[#This Row],[skill_long_passing]]/100) + 0.1875*(Table1[[#This Row],[skill_fk_accuracy]]/100) + 0.1875*(Table1[[#This Row],[attacking_crossing]]/100)))^2))  * ((1 - (Table1[[#This Row],[mentality_vision]]/100))^2))</f>
+        <v>2.3145021056249999</v>
+      </c>
+      <c r="DL41">
+        <f>1.585332 + 0.008219*Table1[[#This Row],[power_jumping]]+ 0.047559*Table1[[#This Row],[pace]] + 0.012348*Table1[[#This Row],[attacking_heading_accuracy]] + 0.362187*Table1[[#This Row],[develle_mcharo_passing]] + 0.015238*Table1[[#This Row],[dribbling]] + 0.189748*Table1[[#This Row],[weak_foot]] + 0.033917*Table1[[#This Row],[power_strength]] + 0.26019*Table1[[#This Row],[skill_moves]] + 0.808787*Table1[[#This Row],[Defender]] + 0.472467*Table1[[#This Row],[Midfielder]] + 0.081427*Table1[[#This Row],[Finesse_Shot]]</f>
+        <v>12.909609574130002</v>
+      </c>
     </row>
-    <row r="42" spans="1:114" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:116" x14ac:dyDescent="0.2">
       <c r="A42">
         <v>210413</v>
       </c>
@@ -17085,8 +17429,16 @@
       <c r="DJ42" t="s">
         <v>546</v>
       </c>
+      <c r="DK42">
+        <f xml:space="preserve"> (Table1[[#This Row],[mentality_vision]]/100) + 0.809*(Table1[[#This Row],[skill_curve]]/100) + (0.75*(Table1[[#This Row],[attacking_short_passing]]/100) + 0.25*(Table1[[#This Row],[attacking_crossing]]/100)) + (0.625*(Table1[[#This Row],[skill_long_passing]]/100) + 0.1875*(Table1[[#This Row],[skill_fk_accuracy]]/100) + 0.1875*(Table1[[#This Row],[attacking_crossing]]/100)) - ((1 - ((0.75*(Table1[[#This Row],[attacking_short_passing]]/100) + 0.25*(Table1[[#This Row],[attacking_crossing]]/100) - (0.625*(Table1[[#This Row],[skill_long_passing]]/100) + 0.1875*(Table1[[#This Row],[skill_fk_accuracy]]/100) + 0.1875*(Table1[[#This Row],[attacking_crossing]]/100)))^2))  * ((1 - (Table1[[#This Row],[mentality_vision]]/100))^2))</f>
+        <v>1.6204660156249999</v>
+      </c>
+      <c r="DL42">
+        <f>1.585332 + 0.008219*Table1[[#This Row],[power_jumping]]+ 0.047559*Table1[[#This Row],[pace]] + 0.012348*Table1[[#This Row],[attacking_heading_accuracy]] + 0.362187*Table1[[#This Row],[develle_mcharo_passing]] + 0.015238*Table1[[#This Row],[dribbling]] + 0.189748*Table1[[#This Row],[weak_foot]] + 0.033917*Table1[[#This Row],[power_strength]] + 0.26019*Table1[[#This Row],[skill_moves]] + 0.808787*Table1[[#This Row],[Defender]] + 0.472467*Table1[[#This Row],[Midfielder]] + 0.081427*Table1[[#This Row],[Finesse_Shot]]</f>
+        <v>12.56979672480117</v>
+      </c>
     </row>
-    <row r="43" spans="1:114" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:116" x14ac:dyDescent="0.2">
       <c r="A43">
         <v>240679</v>
       </c>
@@ -17418,8 +17770,16 @@
       <c r="DJ43" t="s">
         <v>552</v>
       </c>
+      <c r="DK43">
+        <f xml:space="preserve"> (Table1[[#This Row],[mentality_vision]]/100) + 0.809*(Table1[[#This Row],[skill_curve]]/100) + (0.75*(Table1[[#This Row],[attacking_short_passing]]/100) + 0.25*(Table1[[#This Row],[attacking_crossing]]/100)) + (0.625*(Table1[[#This Row],[skill_long_passing]]/100) + 0.1875*(Table1[[#This Row],[skill_fk_accuracy]]/100) + 0.1875*(Table1[[#This Row],[attacking_crossing]]/100)) - ((1 - ((0.75*(Table1[[#This Row],[attacking_short_passing]]/100) + 0.25*(Table1[[#This Row],[attacking_crossing]]/100) - (0.625*(Table1[[#This Row],[skill_long_passing]]/100) + 0.1875*(Table1[[#This Row],[skill_fk_accuracy]]/100) + 0.1875*(Table1[[#This Row],[attacking_crossing]]/100)))^2))  * ((1 - (Table1[[#This Row],[mentality_vision]]/100))^2))</f>
+        <v>3.0711886100000001</v>
+      </c>
+      <c r="DL43">
+        <f>1.585332 + 0.008219*Table1[[#This Row],[power_jumping]]+ 0.047559*Table1[[#This Row],[pace]] + 0.012348*Table1[[#This Row],[attacking_heading_accuracy]] + 0.362187*Table1[[#This Row],[develle_mcharo_passing]] + 0.015238*Table1[[#This Row],[dribbling]] + 0.189748*Table1[[#This Row],[weak_foot]] + 0.033917*Table1[[#This Row],[power_strength]] + 0.26019*Table1[[#This Row],[skill_moves]] + 0.808787*Table1[[#This Row],[Defender]] + 0.472467*Table1[[#This Row],[Midfielder]] + 0.081427*Table1[[#This Row],[Finesse_Shot]]</f>
+        <v>12.79436758909007</v>
+      </c>
     </row>
-    <row r="44" spans="1:114" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:116" x14ac:dyDescent="0.2">
       <c r="A44">
         <v>208574</v>
       </c>
@@ -17745,8 +18105,16 @@
       <c r="DJ44" t="s">
         <v>558</v>
       </c>
+      <c r="DK44">
+        <f xml:space="preserve"> (Table1[[#This Row],[mentality_vision]]/100) + 0.809*(Table1[[#This Row],[skill_curve]]/100) + (0.75*(Table1[[#This Row],[attacking_short_passing]]/100) + 0.25*(Table1[[#This Row],[attacking_crossing]]/100)) + (0.625*(Table1[[#This Row],[skill_long_passing]]/100) + 0.1875*(Table1[[#This Row],[skill_fk_accuracy]]/100) + 0.1875*(Table1[[#This Row],[attacking_crossing]]/100)) - ((1 - ((0.75*(Table1[[#This Row],[attacking_short_passing]]/100) + 0.25*(Table1[[#This Row],[attacking_crossing]]/100) - (0.625*(Table1[[#This Row],[skill_long_passing]]/100) + 0.1875*(Table1[[#This Row],[skill_fk_accuracy]]/100) + 0.1875*(Table1[[#This Row],[attacking_crossing]]/100)))^2))  * ((1 - (Table1[[#This Row],[mentality_vision]]/100))^2))</f>
+        <v>3.0436304639062497</v>
+      </c>
+      <c r="DL44">
+        <f>1.585332 + 0.008219*Table1[[#This Row],[power_jumping]]+ 0.047559*Table1[[#This Row],[pace]] + 0.012348*Table1[[#This Row],[attacking_heading_accuracy]] + 0.362187*Table1[[#This Row],[develle_mcharo_passing]] + 0.015238*Table1[[#This Row],[dribbling]] + 0.189748*Table1[[#This Row],[weak_foot]] + 0.033917*Table1[[#This Row],[power_strength]] + 0.26019*Table1[[#This Row],[skill_moves]] + 0.808787*Table1[[#This Row],[Defender]] + 0.472467*Table1[[#This Row],[Midfielder]] + 0.081427*Table1[[#This Row],[Finesse_Shot]]</f>
+        <v>13.756649386830814</v>
+      </c>
     </row>
-    <row r="45" spans="1:114" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:116" x14ac:dyDescent="0.2">
       <c r="A45">
         <v>258648</v>
       </c>
@@ -18069,8 +18437,16 @@
       <c r="DJ45" t="s">
         <v>563</v>
       </c>
+      <c r="DK45">
+        <f xml:space="preserve"> (Table1[[#This Row],[mentality_vision]]/100) + 0.809*(Table1[[#This Row],[skill_curve]]/100) + (0.75*(Table1[[#This Row],[attacking_short_passing]]/100) + 0.25*(Table1[[#This Row],[attacking_crossing]]/100)) + (0.625*(Table1[[#This Row],[skill_long_passing]]/100) + 0.1875*(Table1[[#This Row],[skill_fk_accuracy]]/100) + 0.1875*(Table1[[#This Row],[attacking_crossing]]/100)) - ((1 - ((0.75*(Table1[[#This Row],[attacking_short_passing]]/100) + 0.25*(Table1[[#This Row],[attacking_crossing]]/100) - (0.625*(Table1[[#This Row],[skill_long_passing]]/100) + 0.1875*(Table1[[#This Row],[skill_fk_accuracy]]/100) + 0.1875*(Table1[[#This Row],[attacking_crossing]]/100)))^2))  * ((1 - (Table1[[#This Row],[mentality_vision]]/100))^2))</f>
+        <v>2.8572682024999998</v>
+      </c>
+      <c r="DL45">
+        <f>1.585332 + 0.008219*Table1[[#This Row],[power_jumping]]+ 0.047559*Table1[[#This Row],[pace]] + 0.012348*Table1[[#This Row],[attacking_heading_accuracy]] + 0.362187*Table1[[#This Row],[develle_mcharo_passing]] + 0.015238*Table1[[#This Row],[dribbling]] + 0.189748*Table1[[#This Row],[weak_foot]] + 0.033917*Table1[[#This Row],[power_strength]] + 0.26019*Table1[[#This Row],[skill_moves]] + 0.808787*Table1[[#This Row],[Defender]] + 0.472467*Table1[[#This Row],[Midfielder]] + 0.081427*Table1[[#This Row],[Finesse_Shot]]</f>
+        <v>13.581541398458869</v>
+      </c>
     </row>
-    <row r="46" spans="1:114" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:116" x14ac:dyDescent="0.2">
       <c r="A46">
         <v>247246</v>
       </c>
@@ -18393,8 +18769,16 @@
       <c r="DJ46" t="s">
         <v>568</v>
       </c>
+      <c r="DK46">
+        <f xml:space="preserve"> (Table1[[#This Row],[mentality_vision]]/100) + 0.809*(Table1[[#This Row],[skill_curve]]/100) + (0.75*(Table1[[#This Row],[attacking_short_passing]]/100) + 0.25*(Table1[[#This Row],[attacking_crossing]]/100)) + (0.625*(Table1[[#This Row],[skill_long_passing]]/100) + 0.1875*(Table1[[#This Row],[skill_fk_accuracy]]/100) + 0.1875*(Table1[[#This Row],[attacking_crossing]]/100)) - ((1 - ((0.75*(Table1[[#This Row],[attacking_short_passing]]/100) + 0.25*(Table1[[#This Row],[attacking_crossing]]/100) - (0.625*(Table1[[#This Row],[skill_long_passing]]/100) + 0.1875*(Table1[[#This Row],[skill_fk_accuracy]]/100) + 0.1875*(Table1[[#This Row],[attacking_crossing]]/100)))^2))  * ((1 - (Table1[[#This Row],[mentality_vision]]/100))^2))</f>
+        <v>2.8567690625000002</v>
+      </c>
+      <c r="DL46">
+        <f>1.585332 + 0.008219*Table1[[#This Row],[power_jumping]]+ 0.047559*Table1[[#This Row],[pace]] + 0.012348*Table1[[#This Row],[attacking_heading_accuracy]] + 0.362187*Table1[[#This Row],[develle_mcharo_passing]] + 0.015238*Table1[[#This Row],[dribbling]] + 0.189748*Table1[[#This Row],[weak_foot]] + 0.033917*Table1[[#This Row],[power_strength]] + 0.26019*Table1[[#This Row],[skill_moves]] + 0.808787*Table1[[#This Row],[Defender]] + 0.472467*Table1[[#This Row],[Midfielder]] + 0.081427*Table1[[#This Row],[Finesse_Shot]]</f>
+        <v>13.703883616439688</v>
+      </c>
     </row>
-    <row r="47" spans="1:114" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:116" x14ac:dyDescent="0.2">
       <c r="A47">
         <v>239807</v>
       </c>
@@ -18726,8 +19110,16 @@
       <c r="DJ47" t="s">
         <v>572</v>
       </c>
+      <c r="DK47">
+        <f xml:space="preserve"> (Table1[[#This Row],[mentality_vision]]/100) + 0.809*(Table1[[#This Row],[skill_curve]]/100) + (0.75*(Table1[[#This Row],[attacking_short_passing]]/100) + 0.25*(Table1[[#This Row],[attacking_crossing]]/100)) + (0.625*(Table1[[#This Row],[skill_long_passing]]/100) + 0.1875*(Table1[[#This Row],[skill_fk_accuracy]]/100) + 0.1875*(Table1[[#This Row],[attacking_crossing]]/100)) - ((1 - ((0.75*(Table1[[#This Row],[attacking_short_passing]]/100) + 0.25*(Table1[[#This Row],[attacking_crossing]]/100) - (0.625*(Table1[[#This Row],[skill_long_passing]]/100) + 0.1875*(Table1[[#This Row],[skill_fk_accuracy]]/100) + 0.1875*(Table1[[#This Row],[attacking_crossing]]/100)))^2))  * ((1 - (Table1[[#This Row],[mentality_vision]]/100))^2))</f>
+        <v>2.9143314414062496</v>
+      </c>
+      <c r="DL47">
+        <f>1.585332 + 0.008219*Table1[[#This Row],[power_jumping]]+ 0.047559*Table1[[#This Row],[pace]] + 0.012348*Table1[[#This Row],[attacking_heading_accuracy]] + 0.362187*Table1[[#This Row],[develle_mcharo_passing]] + 0.015238*Table1[[#This Row],[dribbling]] + 0.189748*Table1[[#This Row],[weak_foot]] + 0.033917*Table1[[#This Row],[power_strength]] + 0.26019*Table1[[#This Row],[skill_moves]] + 0.808787*Table1[[#This Row],[Defender]] + 0.472467*Table1[[#This Row],[Midfielder]] + 0.081427*Table1[[#This Row],[Finesse_Shot]]</f>
+        <v>13.515382961768603</v>
+      </c>
     </row>
-    <row r="48" spans="1:114" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:116" x14ac:dyDescent="0.2">
       <c r="A48">
         <v>261865</v>
       </c>
@@ -19050,8 +19442,16 @@
       <c r="DJ48" t="s">
         <v>577</v>
       </c>
+      <c r="DK48">
+        <f xml:space="preserve"> (Table1[[#This Row],[mentality_vision]]/100) + 0.809*(Table1[[#This Row],[skill_curve]]/100) + (0.75*(Table1[[#This Row],[attacking_short_passing]]/100) + 0.25*(Table1[[#This Row],[attacking_crossing]]/100)) + (0.625*(Table1[[#This Row],[skill_long_passing]]/100) + 0.1875*(Table1[[#This Row],[skill_fk_accuracy]]/100) + 0.1875*(Table1[[#This Row],[attacking_crossing]]/100)) - ((1 - ((0.75*(Table1[[#This Row],[attacking_short_passing]]/100) + 0.25*(Table1[[#This Row],[attacking_crossing]]/100) - (0.625*(Table1[[#This Row],[skill_long_passing]]/100) + 0.1875*(Table1[[#This Row],[skill_fk_accuracy]]/100) + 0.1875*(Table1[[#This Row],[attacking_crossing]]/100)))^2))  * ((1 - (Table1[[#This Row],[mentality_vision]]/100))^2))</f>
+        <v>2.9738126406250003</v>
+      </c>
+      <c r="DL48">
+        <f>1.585332 + 0.008219*Table1[[#This Row],[power_jumping]]+ 0.047559*Table1[[#This Row],[pace]] + 0.012348*Table1[[#This Row],[attacking_heading_accuracy]] + 0.362187*Table1[[#This Row],[develle_mcharo_passing]] + 0.015238*Table1[[#This Row],[dribbling]] + 0.189748*Table1[[#This Row],[weak_foot]] + 0.033917*Table1[[#This Row],[power_strength]] + 0.26019*Table1[[#This Row],[skill_moves]] + 0.808787*Table1[[#This Row],[Defender]] + 0.472467*Table1[[#This Row],[Midfielder]] + 0.081427*Table1[[#This Row],[Finesse_Shot]]</f>
+        <v>13.366644278870046</v>
+      </c>
     </row>
-    <row r="49" spans="1:114" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:116" x14ac:dyDescent="0.2">
       <c r="A49">
         <v>208461</v>
       </c>
@@ -19374,8 +19774,16 @@
       <c r="DJ49" t="s">
         <v>583</v>
       </c>
+      <c r="DK49">
+        <f xml:space="preserve"> (Table1[[#This Row],[mentality_vision]]/100) + 0.809*(Table1[[#This Row],[skill_curve]]/100) + (0.75*(Table1[[#This Row],[attacking_short_passing]]/100) + 0.25*(Table1[[#This Row],[attacking_crossing]]/100)) + (0.625*(Table1[[#This Row],[skill_long_passing]]/100) + 0.1875*(Table1[[#This Row],[skill_fk_accuracy]]/100) + 0.1875*(Table1[[#This Row],[attacking_crossing]]/100)) - ((1 - ((0.75*(Table1[[#This Row],[attacking_short_passing]]/100) + 0.25*(Table1[[#This Row],[attacking_crossing]]/100) - (0.625*(Table1[[#This Row],[skill_long_passing]]/100) + 0.1875*(Table1[[#This Row],[skill_fk_accuracy]]/100) + 0.1875*(Table1[[#This Row],[attacking_crossing]]/100)))^2))  * ((1 - (Table1[[#This Row],[mentality_vision]]/100))^2))</f>
+        <v>2.7360944899999997</v>
+      </c>
+      <c r="DL49">
+        <f>1.585332 + 0.008219*Table1[[#This Row],[power_jumping]]+ 0.047559*Table1[[#This Row],[pace]] + 0.012348*Table1[[#This Row],[attacking_heading_accuracy]] + 0.362187*Table1[[#This Row],[develle_mcharo_passing]] + 0.015238*Table1[[#This Row],[dribbling]] + 0.189748*Table1[[#This Row],[weak_foot]] + 0.033917*Table1[[#This Row],[power_strength]] + 0.26019*Table1[[#This Row],[skill_moves]] + 0.808787*Table1[[#This Row],[Defender]] + 0.472467*Table1[[#This Row],[Midfielder]] + 0.081427*Table1[[#This Row],[Finesse_Shot]]</f>
+        <v>12.468024855049629</v>
+      </c>
     </row>
-    <row r="50" spans="1:114" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:116" x14ac:dyDescent="0.2">
       <c r="A50">
         <v>216409</v>
       </c>
@@ -19710,8 +20118,16 @@
       <c r="DJ50" t="s">
         <v>588</v>
       </c>
+      <c r="DK50">
+        <f xml:space="preserve"> (Table1[[#This Row],[mentality_vision]]/100) + 0.809*(Table1[[#This Row],[skill_curve]]/100) + (0.75*(Table1[[#This Row],[attacking_short_passing]]/100) + 0.25*(Table1[[#This Row],[attacking_crossing]]/100)) + (0.625*(Table1[[#This Row],[skill_long_passing]]/100) + 0.1875*(Table1[[#This Row],[skill_fk_accuracy]]/100) + 0.1875*(Table1[[#This Row],[attacking_crossing]]/100)) - ((1 - ((0.75*(Table1[[#This Row],[attacking_short_passing]]/100) + 0.25*(Table1[[#This Row],[attacking_crossing]]/100) - (0.625*(Table1[[#This Row],[skill_long_passing]]/100) + 0.1875*(Table1[[#This Row],[skill_fk_accuracy]]/100) + 0.1875*(Table1[[#This Row],[attacking_crossing]]/100)))^2))  * ((1 - (Table1[[#This Row],[mentality_vision]]/100))^2))</f>
+        <v>2.9835682656250002</v>
+      </c>
+      <c r="DL50">
+        <f>1.585332 + 0.008219*Table1[[#This Row],[power_jumping]]+ 0.047559*Table1[[#This Row],[pace]] + 0.012348*Table1[[#This Row],[attacking_heading_accuracy]] + 0.362187*Table1[[#This Row],[develle_mcharo_passing]] + 0.015238*Table1[[#This Row],[dribbling]] + 0.189748*Table1[[#This Row],[weak_foot]] + 0.033917*Table1[[#This Row],[power_strength]] + 0.26019*Table1[[#This Row],[skill_moves]] + 0.808787*Table1[[#This Row],[Defender]] + 0.472467*Table1[[#This Row],[Midfielder]] + 0.081427*Table1[[#This Row],[Finesse_Shot]]</f>
+        <v>11.787457639421921</v>
+      </c>
     </row>
-    <row r="51" spans="1:114" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:116" x14ac:dyDescent="0.2">
       <c r="A51">
         <v>245630</v>
       </c>
@@ -20034,8 +20450,16 @@
       <c r="DJ51" t="s">
         <v>593</v>
       </c>
+      <c r="DK51">
+        <f xml:space="preserve"> (Table1[[#This Row],[mentality_vision]]/100) + 0.809*(Table1[[#This Row],[skill_curve]]/100) + (0.75*(Table1[[#This Row],[attacking_short_passing]]/100) + 0.25*(Table1[[#This Row],[attacking_crossing]]/100)) + (0.625*(Table1[[#This Row],[skill_long_passing]]/100) + 0.1875*(Table1[[#This Row],[skill_fk_accuracy]]/100) + 0.1875*(Table1[[#This Row],[attacking_crossing]]/100)) - ((1 - ((0.75*(Table1[[#This Row],[attacking_short_passing]]/100) + 0.25*(Table1[[#This Row],[attacking_crossing]]/100) - (0.625*(Table1[[#This Row],[skill_long_passing]]/100) + 0.1875*(Table1[[#This Row],[skill_fk_accuracy]]/100) + 0.1875*(Table1[[#This Row],[attacking_crossing]]/100)))^2))  * ((1 - (Table1[[#This Row],[mentality_vision]]/100))^2))</f>
+        <v>2.7606610000000003</v>
+      </c>
+      <c r="DL51">
+        <f>1.585332 + 0.008219*Table1[[#This Row],[power_jumping]]+ 0.047559*Table1[[#This Row],[pace]] + 0.012348*Table1[[#This Row],[attacking_heading_accuracy]] + 0.362187*Table1[[#This Row],[develle_mcharo_passing]] + 0.015238*Table1[[#This Row],[dribbling]] + 0.189748*Table1[[#This Row],[weak_foot]] + 0.033917*Table1[[#This Row],[power_strength]] + 0.26019*Table1[[#This Row],[skill_moves]] + 0.808787*Table1[[#This Row],[Defender]] + 0.472467*Table1[[#This Row],[Midfielder]] + 0.081427*Table1[[#This Row],[Finesse_Shot]]</f>
+        <v>12.683916525606998</v>
+      </c>
     </row>
-    <row r="52" spans="1:114" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:116" x14ac:dyDescent="0.2">
       <c r="A52">
         <v>184392</v>
       </c>
@@ -20355,8 +20779,16 @@
       <c r="DJ52" t="s">
         <v>597</v>
       </c>
+      <c r="DK52">
+        <f xml:space="preserve"> (Table1[[#This Row],[mentality_vision]]/100) + 0.809*(Table1[[#This Row],[skill_curve]]/100) + (0.75*(Table1[[#This Row],[attacking_short_passing]]/100) + 0.25*(Table1[[#This Row],[attacking_crossing]]/100)) + (0.625*(Table1[[#This Row],[skill_long_passing]]/100) + 0.1875*(Table1[[#This Row],[skill_fk_accuracy]]/100) + 0.1875*(Table1[[#This Row],[attacking_crossing]]/100)) - ((1 - ((0.75*(Table1[[#This Row],[attacking_short_passing]]/100) + 0.25*(Table1[[#This Row],[attacking_crossing]]/100) - (0.625*(Table1[[#This Row],[skill_long_passing]]/100) + 0.1875*(Table1[[#This Row],[skill_fk_accuracy]]/100) + 0.1875*(Table1[[#This Row],[attacking_crossing]]/100)))^2))  * ((1 - (Table1[[#This Row],[mentality_vision]]/100))^2))</f>
+        <v>2.6867162656249999</v>
+      </c>
+      <c r="DL52">
+        <f>1.585332 + 0.008219*Table1[[#This Row],[power_jumping]]+ 0.047559*Table1[[#This Row],[pace]] + 0.012348*Table1[[#This Row],[attacking_heading_accuracy]] + 0.362187*Table1[[#This Row],[develle_mcharo_passing]] + 0.015238*Table1[[#This Row],[dribbling]] + 0.189748*Table1[[#This Row],[weak_foot]] + 0.033917*Table1[[#This Row],[power_strength]] + 0.26019*Table1[[#This Row],[skill_moves]] + 0.808787*Table1[[#This Row],[Defender]] + 0.472467*Table1[[#This Row],[Midfielder]] + 0.081427*Table1[[#This Row],[Finesse_Shot]]</f>
+        <v>13.183550704097923</v>
+      </c>
     </row>
-    <row r="53" spans="1:114" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:116" x14ac:dyDescent="0.2">
       <c r="A53">
         <v>202024</v>
       </c>
@@ -20679,8 +21111,16 @@
       <c r="DJ53" t="s">
         <v>602</v>
       </c>
+      <c r="DK53">
+        <f xml:space="preserve"> (Table1[[#This Row],[mentality_vision]]/100) + 0.809*(Table1[[#This Row],[skill_curve]]/100) + (0.75*(Table1[[#This Row],[attacking_short_passing]]/100) + 0.25*(Table1[[#This Row],[attacking_crossing]]/100)) + (0.625*(Table1[[#This Row],[skill_long_passing]]/100) + 0.1875*(Table1[[#This Row],[skill_fk_accuracy]]/100) + 0.1875*(Table1[[#This Row],[attacking_crossing]]/100)) - ((1 - ((0.75*(Table1[[#This Row],[attacking_short_passing]]/100) + 0.25*(Table1[[#This Row],[attacking_crossing]]/100) - (0.625*(Table1[[#This Row],[skill_long_passing]]/100) + 0.1875*(Table1[[#This Row],[skill_fk_accuracy]]/100) + 0.1875*(Table1[[#This Row],[attacking_crossing]]/100)))^2))  * ((1 - (Table1[[#This Row],[mentality_vision]]/100))^2))</f>
+        <v>2.7508103064062501</v>
+      </c>
+      <c r="DL53">
+        <f>1.585332 + 0.008219*Table1[[#This Row],[power_jumping]]+ 0.047559*Table1[[#This Row],[pace]] + 0.012348*Table1[[#This Row],[attacking_heading_accuracy]] + 0.362187*Table1[[#This Row],[develle_mcharo_passing]] + 0.015238*Table1[[#This Row],[dribbling]] + 0.189748*Table1[[#This Row],[weak_foot]] + 0.033917*Table1[[#This Row],[power_strength]] + 0.26019*Table1[[#This Row],[skill_moves]] + 0.808787*Table1[[#This Row],[Defender]] + 0.472467*Table1[[#This Row],[Midfielder]] + 0.081427*Table1[[#This Row],[Finesse_Shot]]</f>
+        <v>11.970579732446362</v>
+      </c>
     </row>
-    <row r="54" spans="1:114" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:116" x14ac:dyDescent="0.2">
       <c r="A54">
         <v>232411</v>
       </c>
@@ -21003,8 +21443,16 @@
       <c r="DJ54" t="s">
         <v>608</v>
       </c>
+      <c r="DK54">
+        <f xml:space="preserve"> (Table1[[#This Row],[mentality_vision]]/100) + 0.809*(Table1[[#This Row],[skill_curve]]/100) + (0.75*(Table1[[#This Row],[attacking_short_passing]]/100) + 0.25*(Table1[[#This Row],[attacking_crossing]]/100)) + (0.625*(Table1[[#This Row],[skill_long_passing]]/100) + 0.1875*(Table1[[#This Row],[skill_fk_accuracy]]/100) + 0.1875*(Table1[[#This Row],[attacking_crossing]]/100)) - ((1 - ((0.75*(Table1[[#This Row],[attacking_short_passing]]/100) + 0.25*(Table1[[#This Row],[attacking_crossing]]/100) - (0.625*(Table1[[#This Row],[skill_long_passing]]/100) + 0.1875*(Table1[[#This Row],[skill_fk_accuracy]]/100) + 0.1875*(Table1[[#This Row],[attacking_crossing]]/100)))^2))  * ((1 - (Table1[[#This Row],[mentality_vision]]/100))^2))</f>
+        <v>2.9972360000000005</v>
+      </c>
+      <c r="DL54">
+        <f>1.585332 + 0.008219*Table1[[#This Row],[power_jumping]]+ 0.047559*Table1[[#This Row],[pace]] + 0.012348*Table1[[#This Row],[attacking_heading_accuracy]] + 0.362187*Table1[[#This Row],[develle_mcharo_passing]] + 0.015238*Table1[[#This Row],[dribbling]] + 0.189748*Table1[[#This Row],[weak_foot]] + 0.033917*Table1[[#This Row],[power_strength]] + 0.26019*Table1[[#This Row],[skill_moves]] + 0.808787*Table1[[#This Row],[Defender]] + 0.472467*Table1[[#This Row],[Midfielder]] + 0.081427*Table1[[#This Row],[Finesse_Shot]]</f>
+        <v>13.081668915131999</v>
+      </c>
     </row>
-    <row r="55" spans="1:114" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:116" x14ac:dyDescent="0.2">
       <c r="A55">
         <v>236632</v>
       </c>
@@ -21330,8 +21778,16 @@
       <c r="DJ55" t="s">
         <v>613</v>
       </c>
+      <c r="DK55">
+        <f xml:space="preserve"> (Table1[[#This Row],[mentality_vision]]/100) + 0.809*(Table1[[#This Row],[skill_curve]]/100) + (0.75*(Table1[[#This Row],[attacking_short_passing]]/100) + 0.25*(Table1[[#This Row],[attacking_crossing]]/100)) + (0.625*(Table1[[#This Row],[skill_long_passing]]/100) + 0.1875*(Table1[[#This Row],[skill_fk_accuracy]]/100) + 0.1875*(Table1[[#This Row],[attacking_crossing]]/100)) - ((1 - ((0.75*(Table1[[#This Row],[attacking_short_passing]]/100) + 0.25*(Table1[[#This Row],[attacking_crossing]]/100) - (0.625*(Table1[[#This Row],[skill_long_passing]]/100) + 0.1875*(Table1[[#This Row],[skill_fk_accuracy]]/100) + 0.1875*(Table1[[#This Row],[attacking_crossing]]/100)))^2))  * ((1 - (Table1[[#This Row],[mentality_vision]]/100))^2))</f>
+        <v>2.822973325625</v>
+      </c>
+      <c r="DL55">
+        <f>1.585332 + 0.008219*Table1[[#This Row],[power_jumping]]+ 0.047559*Table1[[#This Row],[pace]] + 0.012348*Table1[[#This Row],[attacking_heading_accuracy]] + 0.362187*Table1[[#This Row],[develle_mcharo_passing]] + 0.015238*Table1[[#This Row],[dribbling]] + 0.189748*Table1[[#This Row],[weak_foot]] + 0.033917*Table1[[#This Row],[power_strength]] + 0.26019*Table1[[#This Row],[skill_moves]] + 0.808787*Table1[[#This Row],[Defender]] + 0.472467*Table1[[#This Row],[Midfielder]] + 0.081427*Table1[[#This Row],[Finesse_Shot]]</f>
+        <v>12.985948239888142</v>
+      </c>
     </row>
-    <row r="56" spans="1:114" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:116" x14ac:dyDescent="0.2">
       <c r="A56">
         <v>201153</v>
       </c>
@@ -21660,8 +22116,16 @@
       <c r="DJ56" t="s">
         <v>620</v>
       </c>
+      <c r="DK56">
+        <f xml:space="preserve"> (Table1[[#This Row],[mentality_vision]]/100) + 0.809*(Table1[[#This Row],[skill_curve]]/100) + (0.75*(Table1[[#This Row],[attacking_short_passing]]/100) + 0.25*(Table1[[#This Row],[attacking_crossing]]/100)) + (0.625*(Table1[[#This Row],[skill_long_passing]]/100) + 0.1875*(Table1[[#This Row],[skill_fk_accuracy]]/100) + 0.1875*(Table1[[#This Row],[attacking_crossing]]/100)) - ((1 - ((0.75*(Table1[[#This Row],[attacking_short_passing]]/100) + 0.25*(Table1[[#This Row],[attacking_crossing]]/100) - (0.625*(Table1[[#This Row],[skill_long_passing]]/100) + 0.1875*(Table1[[#This Row],[skill_fk_accuracy]]/100) + 0.1875*(Table1[[#This Row],[attacking_crossing]]/100)))^2))  * ((1 - (Table1[[#This Row],[mentality_vision]]/100))^2))</f>
+        <v>2.7884175625000003</v>
+      </c>
+      <c r="DL56">
+        <f>1.585332 + 0.008219*Table1[[#This Row],[power_jumping]]+ 0.047559*Table1[[#This Row],[pace]] + 0.012348*Table1[[#This Row],[attacking_heading_accuracy]] + 0.362187*Table1[[#This Row],[develle_mcharo_passing]] + 0.015238*Table1[[#This Row],[dribbling]] + 0.189748*Table1[[#This Row],[weak_foot]] + 0.033917*Table1[[#This Row],[power_strength]] + 0.26019*Table1[[#This Row],[skill_moves]] + 0.808787*Table1[[#This Row],[Defender]] + 0.472467*Table1[[#This Row],[Midfielder]] + 0.081427*Table1[[#This Row],[Finesse_Shot]]</f>
+        <v>13.609495591709186</v>
+      </c>
     </row>
-    <row r="57" spans="1:114" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:116" x14ac:dyDescent="0.2">
       <c r="A57">
         <v>236403</v>
       </c>
@@ -21984,8 +22448,16 @@
       <c r="DJ57" t="s">
         <v>626</v>
       </c>
+      <c r="DK57">
+        <f xml:space="preserve"> (Table1[[#This Row],[mentality_vision]]/100) + 0.809*(Table1[[#This Row],[skill_curve]]/100) + (0.75*(Table1[[#This Row],[attacking_short_passing]]/100) + 0.25*(Table1[[#This Row],[attacking_crossing]]/100)) + (0.625*(Table1[[#This Row],[skill_long_passing]]/100) + 0.1875*(Table1[[#This Row],[skill_fk_accuracy]]/100) + 0.1875*(Table1[[#This Row],[attacking_crossing]]/100)) - ((1 - ((0.75*(Table1[[#This Row],[attacking_short_passing]]/100) + 0.25*(Table1[[#This Row],[attacking_crossing]]/100) - (0.625*(Table1[[#This Row],[skill_long_passing]]/100) + 0.1875*(Table1[[#This Row],[skill_fk_accuracy]]/100) + 0.1875*(Table1[[#This Row],[attacking_crossing]]/100)))^2))  * ((1 - (Table1[[#This Row],[mentality_vision]]/100))^2))</f>
+        <v>2.3904927224999999</v>
+      </c>
+      <c r="DL57">
+        <f>1.585332 + 0.008219*Table1[[#This Row],[power_jumping]]+ 0.047559*Table1[[#This Row],[pace]] + 0.012348*Table1[[#This Row],[attacking_heading_accuracy]] + 0.362187*Table1[[#This Row],[develle_mcharo_passing]] + 0.015238*Table1[[#This Row],[dribbling]] + 0.189748*Table1[[#This Row],[weak_foot]] + 0.033917*Table1[[#This Row],[power_strength]] + 0.26019*Table1[[#This Row],[skill_moves]] + 0.808787*Table1[[#This Row],[Defender]] + 0.472467*Table1[[#This Row],[Midfielder]] + 0.081427*Table1[[#This Row],[Finesse_Shot]]</f>
+        <v>13.341720387684108</v>
+      </c>
     </row>
-    <row r="58" spans="1:114" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:116" x14ac:dyDescent="0.2">
       <c r="A58">
         <v>180930</v>
       </c>
@@ -22308,8 +22780,16 @@
       <c r="DJ58" t="s">
         <v>632</v>
       </c>
+      <c r="DK58">
+        <f xml:space="preserve"> (Table1[[#This Row],[mentality_vision]]/100) + 0.809*(Table1[[#This Row],[skill_curve]]/100) + (0.75*(Table1[[#This Row],[attacking_short_passing]]/100) + 0.25*(Table1[[#This Row],[attacking_crossing]]/100)) + (0.625*(Table1[[#This Row],[skill_long_passing]]/100) + 0.1875*(Table1[[#This Row],[skill_fk_accuracy]]/100) + 0.1875*(Table1[[#This Row],[attacking_crossing]]/100)) - ((1 - ((0.75*(Table1[[#This Row],[attacking_short_passing]]/100) + 0.25*(Table1[[#This Row],[attacking_crossing]]/100) - (0.625*(Table1[[#This Row],[skill_long_passing]]/100) + 0.1875*(Table1[[#This Row],[skill_fk_accuracy]]/100) + 0.1875*(Table1[[#This Row],[attacking_crossing]]/100)))^2))  * ((1 - (Table1[[#This Row],[mentality_vision]]/100))^2))</f>
+        <v>2.7149742250390623</v>
+      </c>
+      <c r="DL58">
+        <f>1.585332 + 0.008219*Table1[[#This Row],[power_jumping]]+ 0.047559*Table1[[#This Row],[pace]] + 0.012348*Table1[[#This Row],[attacking_heading_accuracy]] + 0.362187*Table1[[#This Row],[develle_mcharo_passing]] + 0.015238*Table1[[#This Row],[dribbling]] + 0.189748*Table1[[#This Row],[weak_foot]] + 0.033917*Table1[[#This Row],[power_strength]] + 0.26019*Table1[[#This Row],[skill_moves]] + 0.808787*Table1[[#This Row],[Defender]] + 0.472467*Table1[[#This Row],[Midfielder]] + 0.081427*Table1[[#This Row],[Finesse_Shot]]</f>
+        <v>12.458430369644221</v>
+      </c>
     </row>
-    <row r="59" spans="1:114" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:116" x14ac:dyDescent="0.2">
       <c r="A59">
         <v>232756</v>
       </c>
@@ -22632,8 +23112,16 @@
       <c r="DJ59" t="s">
         <v>637</v>
       </c>
+      <c r="DK59">
+        <f xml:space="preserve"> (Table1[[#This Row],[mentality_vision]]/100) + 0.809*(Table1[[#This Row],[skill_curve]]/100) + (0.75*(Table1[[#This Row],[attacking_short_passing]]/100) + 0.25*(Table1[[#This Row],[attacking_crossing]]/100)) + (0.625*(Table1[[#This Row],[skill_long_passing]]/100) + 0.1875*(Table1[[#This Row],[skill_fk_accuracy]]/100) + 0.1875*(Table1[[#This Row],[attacking_crossing]]/100)) - ((1 - ((0.75*(Table1[[#This Row],[attacking_short_passing]]/100) + 0.25*(Table1[[#This Row],[attacking_crossing]]/100) - (0.625*(Table1[[#This Row],[skill_long_passing]]/100) + 0.1875*(Table1[[#This Row],[skill_fk_accuracy]]/100) + 0.1875*(Table1[[#This Row],[attacking_crossing]]/100)))^2))  * ((1 - (Table1[[#This Row],[mentality_vision]]/100))^2))</f>
+        <v>1.7961822756250001</v>
+      </c>
+      <c r="DL59">
+        <f>1.585332 + 0.008219*Table1[[#This Row],[power_jumping]]+ 0.047559*Table1[[#This Row],[pace]] + 0.012348*Table1[[#This Row],[attacking_heading_accuracy]] + 0.362187*Table1[[#This Row],[develle_mcharo_passing]] + 0.015238*Table1[[#This Row],[dribbling]] + 0.189748*Table1[[#This Row],[weak_foot]] + 0.033917*Table1[[#This Row],[power_strength]] + 0.26019*Table1[[#This Row],[skill_moves]] + 0.808787*Table1[[#This Row],[Defender]] + 0.472467*Table1[[#This Row],[Midfielder]] + 0.081427*Table1[[#This Row],[Finesse_Shot]]</f>
+        <v>13.486073869861793</v>
+      </c>
     </row>
-    <row r="60" spans="1:114" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:116" x14ac:dyDescent="0.2">
       <c r="A60">
         <v>228251</v>
       </c>
@@ -22965,8 +23453,16 @@
       <c r="DJ60" t="s">
         <v>642</v>
       </c>
+      <c r="DK60">
+        <f xml:space="preserve"> (Table1[[#This Row],[mentality_vision]]/100) + 0.809*(Table1[[#This Row],[skill_curve]]/100) + (0.75*(Table1[[#This Row],[attacking_short_passing]]/100) + 0.25*(Table1[[#This Row],[attacking_crossing]]/100)) + (0.625*(Table1[[#This Row],[skill_long_passing]]/100) + 0.1875*(Table1[[#This Row],[skill_fk_accuracy]]/100) + 0.1875*(Table1[[#This Row],[attacking_crossing]]/100)) - ((1 - ((0.75*(Table1[[#This Row],[attacking_short_passing]]/100) + 0.25*(Table1[[#This Row],[attacking_crossing]]/100) - (0.625*(Table1[[#This Row],[skill_long_passing]]/100) + 0.1875*(Table1[[#This Row],[skill_fk_accuracy]]/100) + 0.1875*(Table1[[#This Row],[attacking_crossing]]/100)))^2))  * ((1 - (Table1[[#This Row],[mentality_vision]]/100))^2))</f>
+        <v>3.0016578603515631</v>
+      </c>
+      <c r="DL60">
+        <f>1.585332 + 0.008219*Table1[[#This Row],[power_jumping]]+ 0.047559*Table1[[#This Row],[pace]] + 0.012348*Table1[[#This Row],[attacking_heading_accuracy]] + 0.362187*Table1[[#This Row],[develle_mcharo_passing]] + 0.015238*Table1[[#This Row],[dribbling]] + 0.189748*Table1[[#This Row],[weak_foot]] + 0.033917*Table1[[#This Row],[power_strength]] + 0.26019*Table1[[#This Row],[skill_moves]] + 0.808787*Table1[[#This Row],[Defender]] + 0.472467*Table1[[#This Row],[Midfielder]] + 0.081427*Table1[[#This Row],[Finesse_Shot]]</f>
+        <v>13.505595455467152</v>
+      </c>
     </row>
-    <row r="61" spans="1:114" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:116" x14ac:dyDescent="0.2">
       <c r="A61">
         <v>213666</v>
       </c>
@@ -23289,8 +23785,16 @@
       <c r="DJ61" t="s">
         <v>649</v>
       </c>
+      <c r="DK61">
+        <f xml:space="preserve"> (Table1[[#This Row],[mentality_vision]]/100) + 0.809*(Table1[[#This Row],[skill_curve]]/100) + (0.75*(Table1[[#This Row],[attacking_short_passing]]/100) + 0.25*(Table1[[#This Row],[attacking_crossing]]/100)) + (0.625*(Table1[[#This Row],[skill_long_passing]]/100) + 0.1875*(Table1[[#This Row],[skill_fk_accuracy]]/100) + 0.1875*(Table1[[#This Row],[attacking_crossing]]/100)) - ((1 - ((0.75*(Table1[[#This Row],[attacking_short_passing]]/100) + 0.25*(Table1[[#This Row],[attacking_crossing]]/100) - (0.625*(Table1[[#This Row],[skill_long_passing]]/100) + 0.1875*(Table1[[#This Row],[skill_fk_accuracy]]/100) + 0.1875*(Table1[[#This Row],[attacking_crossing]]/100)))^2))  * ((1 - (Table1[[#This Row],[mentality_vision]]/100))^2))</f>
+        <v>2.8774160900000001</v>
+      </c>
+      <c r="DL61">
+        <f>1.585332 + 0.008219*Table1[[#This Row],[power_jumping]]+ 0.047559*Table1[[#This Row],[pace]] + 0.012348*Table1[[#This Row],[attacking_heading_accuracy]] + 0.362187*Table1[[#This Row],[develle_mcharo_passing]] + 0.015238*Table1[[#This Row],[dribbling]] + 0.189748*Table1[[#This Row],[weak_foot]] + 0.033917*Table1[[#This Row],[power_strength]] + 0.26019*Table1[[#This Row],[skill_moves]] + 0.808787*Table1[[#This Row],[Defender]] + 0.472467*Table1[[#This Row],[Midfielder]] + 0.081427*Table1[[#This Row],[Finesse_Shot]]</f>
+        <v>14.676143701388828</v>
+      </c>
     </row>
-    <row r="62" spans="1:114" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:116" x14ac:dyDescent="0.2">
       <c r="A62">
         <v>223697</v>
       </c>
@@ -23610,8 +24114,16 @@
       <c r="DJ62" t="s">
         <v>654</v>
       </c>
+      <c r="DK62">
+        <f xml:space="preserve"> (Table1[[#This Row],[mentality_vision]]/100) + 0.809*(Table1[[#This Row],[skill_curve]]/100) + (0.75*(Table1[[#This Row],[attacking_short_passing]]/100) + 0.25*(Table1[[#This Row],[attacking_crossing]]/100)) + (0.625*(Table1[[#This Row],[skill_long_passing]]/100) + 0.1875*(Table1[[#This Row],[skill_fk_accuracy]]/100) + 0.1875*(Table1[[#This Row],[attacking_crossing]]/100)) - ((1 - ((0.75*(Table1[[#This Row],[attacking_short_passing]]/100) + 0.25*(Table1[[#This Row],[attacking_crossing]]/100) - (0.625*(Table1[[#This Row],[skill_long_passing]]/100) + 0.1875*(Table1[[#This Row],[skill_fk_accuracy]]/100) + 0.1875*(Table1[[#This Row],[attacking_crossing]]/100)))^2))  * ((1 - (Table1[[#This Row],[mentality_vision]]/100))^2))</f>
+        <v>2.6070557056250001</v>
+      </c>
+      <c r="DL62">
+        <f>1.585332 + 0.008219*Table1[[#This Row],[power_jumping]]+ 0.047559*Table1[[#This Row],[pace]] + 0.012348*Table1[[#This Row],[attacking_heading_accuracy]] + 0.362187*Table1[[#This Row],[develle_mcharo_passing]] + 0.015238*Table1[[#This Row],[dribbling]] + 0.189748*Table1[[#This Row],[weak_foot]] + 0.033917*Table1[[#This Row],[power_strength]] + 0.26019*Table1[[#This Row],[skill_moves]] + 0.808787*Table1[[#This Row],[Defender]] + 0.472467*Table1[[#This Row],[Midfielder]] + 0.081427*Table1[[#This Row],[Finesse_Shot]]</f>
+        <v>13.406206684853201</v>
+      </c>
     </row>
-    <row r="63" spans="1:114" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:116" x14ac:dyDescent="0.2">
       <c r="A63">
         <v>210406</v>
       </c>
@@ -23943,8 +24455,16 @@
       <c r="DJ63" t="s">
         <v>659</v>
       </c>
+      <c r="DK63">
+        <f xml:space="preserve"> (Table1[[#This Row],[mentality_vision]]/100) + 0.809*(Table1[[#This Row],[skill_curve]]/100) + (0.75*(Table1[[#This Row],[attacking_short_passing]]/100) + 0.25*(Table1[[#This Row],[attacking_crossing]]/100)) + (0.625*(Table1[[#This Row],[skill_long_passing]]/100) + 0.1875*(Table1[[#This Row],[skill_fk_accuracy]]/100) + 0.1875*(Table1[[#This Row],[attacking_crossing]]/100)) - ((1 - ((0.75*(Table1[[#This Row],[attacking_short_passing]]/100) + 0.25*(Table1[[#This Row],[attacking_crossing]]/100) - (0.625*(Table1[[#This Row],[skill_long_passing]]/100) + 0.1875*(Table1[[#This Row],[skill_fk_accuracy]]/100) + 0.1875*(Table1[[#This Row],[attacking_crossing]]/100)))^2))  * ((1 - (Table1[[#This Row],[mentality_vision]]/100))^2))</f>
+        <v>3.0391577600000002</v>
+      </c>
+      <c r="DL63">
+        <f>1.585332 + 0.008219*Table1[[#This Row],[power_jumping]]+ 0.047559*Table1[[#This Row],[pace]] + 0.012348*Table1[[#This Row],[attacking_heading_accuracy]] + 0.362187*Table1[[#This Row],[develle_mcharo_passing]] + 0.015238*Table1[[#This Row],[dribbling]] + 0.189748*Table1[[#This Row],[weak_foot]] + 0.033917*Table1[[#This Row],[power_strength]] + 0.26019*Table1[[#This Row],[skill_moves]] + 0.808787*Table1[[#This Row],[Defender]] + 0.472467*Table1[[#This Row],[Midfielder]] + 0.081427*Table1[[#This Row],[Finesse_Shot]]</f>
+        <v>12.646006431621119</v>
+      </c>
     </row>
-    <row r="64" spans="1:114" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:116" x14ac:dyDescent="0.2">
       <c r="A64">
         <v>223273</v>
       </c>
@@ -24276,8 +24796,16 @@
       <c r="DJ64" t="s">
         <v>664</v>
       </c>
+      <c r="DK64">
+        <f xml:space="preserve"> (Table1[[#This Row],[mentality_vision]]/100) + 0.809*(Table1[[#This Row],[skill_curve]]/100) + (0.75*(Table1[[#This Row],[attacking_short_passing]]/100) + 0.25*(Table1[[#This Row],[attacking_crossing]]/100)) + (0.625*(Table1[[#This Row],[skill_long_passing]]/100) + 0.1875*(Table1[[#This Row],[skill_fk_accuracy]]/100) + 0.1875*(Table1[[#This Row],[attacking_crossing]]/100)) - ((1 - ((0.75*(Table1[[#This Row],[attacking_short_passing]]/100) + 0.25*(Table1[[#This Row],[attacking_crossing]]/100) - (0.625*(Table1[[#This Row],[skill_long_passing]]/100) + 0.1875*(Table1[[#This Row],[skill_fk_accuracy]]/100) + 0.1875*(Table1[[#This Row],[attacking_crossing]]/100)))^2))  * ((1 - (Table1[[#This Row],[mentality_vision]]/100))^2))</f>
+        <v>2.8205781014062499</v>
+      </c>
+      <c r="DL64">
+        <f>1.585332 + 0.008219*Table1[[#This Row],[power_jumping]]+ 0.047559*Table1[[#This Row],[pace]] + 0.012348*Table1[[#This Row],[attacking_heading_accuracy]] + 0.362187*Table1[[#This Row],[develle_mcharo_passing]] + 0.015238*Table1[[#This Row],[dribbling]] + 0.189748*Table1[[#This Row],[weak_foot]] + 0.033917*Table1[[#This Row],[power_strength]] + 0.26019*Table1[[#This Row],[skill_moves]] + 0.808787*Table1[[#This Row],[Defender]] + 0.472467*Table1[[#This Row],[Midfielder]] + 0.081427*Table1[[#This Row],[Finesse_Shot]]</f>
+        <v>13.247826720814025</v>
+      </c>
     </row>
-    <row r="65" spans="1:114" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:116" x14ac:dyDescent="0.2">
       <c r="A65">
         <v>208268</v>
       </c>
@@ -24600,8 +25128,16 @@
       <c r="DJ65" t="s">
         <v>670</v>
       </c>
+      <c r="DK65">
+        <f xml:space="preserve"> (Table1[[#This Row],[mentality_vision]]/100) + 0.809*(Table1[[#This Row],[skill_curve]]/100) + (0.75*(Table1[[#This Row],[attacking_short_passing]]/100) + 0.25*(Table1[[#This Row],[attacking_crossing]]/100)) + (0.625*(Table1[[#This Row],[skill_long_passing]]/100) + 0.1875*(Table1[[#This Row],[skill_fk_accuracy]]/100) + 0.1875*(Table1[[#This Row],[attacking_crossing]]/100)) - ((1 - ((0.75*(Table1[[#This Row],[attacking_short_passing]]/100) + 0.25*(Table1[[#This Row],[attacking_crossing]]/100) - (0.625*(Table1[[#This Row],[skill_long_passing]]/100) + 0.1875*(Table1[[#This Row],[skill_fk_accuracy]]/100) + 0.1875*(Table1[[#This Row],[attacking_crossing]]/100)))^2))  * ((1 - (Table1[[#This Row],[mentality_vision]]/100))^2))</f>
+        <v>2.8738805625000001</v>
+      </c>
+      <c r="DL65">
+        <f>1.585332 + 0.008219*Table1[[#This Row],[power_jumping]]+ 0.047559*Table1[[#This Row],[pace]] + 0.012348*Table1[[#This Row],[attacking_heading_accuracy]] + 0.362187*Table1[[#This Row],[develle_mcharo_passing]] + 0.015238*Table1[[#This Row],[dribbling]] + 0.189748*Table1[[#This Row],[weak_foot]] + 0.033917*Table1[[#This Row],[power_strength]] + 0.26019*Table1[[#This Row],[skill_moves]] + 0.808787*Table1[[#This Row],[Defender]] + 0.472467*Table1[[#This Row],[Midfielder]] + 0.081427*Table1[[#This Row],[Finesse_Shot]]</f>
+        <v>12.479217179290186</v>
+      </c>
     </row>
-    <row r="66" spans="1:114" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:116" x14ac:dyDescent="0.2">
       <c r="A66">
         <v>239380</v>
       </c>
@@ -24936,8 +25472,16 @@
       <c r="DJ66" t="s">
         <v>675</v>
       </c>
+      <c r="DK66">
+        <f xml:space="preserve"> (Table1[[#This Row],[mentality_vision]]/100) + 0.809*(Table1[[#This Row],[skill_curve]]/100) + (0.75*(Table1[[#This Row],[attacking_short_passing]]/100) + 0.25*(Table1[[#This Row],[attacking_crossing]]/100)) + (0.625*(Table1[[#This Row],[skill_long_passing]]/100) + 0.1875*(Table1[[#This Row],[skill_fk_accuracy]]/100) + 0.1875*(Table1[[#This Row],[attacking_crossing]]/100)) - ((1 - ((0.75*(Table1[[#This Row],[attacking_short_passing]]/100) + 0.25*(Table1[[#This Row],[attacking_crossing]]/100) - (0.625*(Table1[[#This Row],[skill_long_passing]]/100) + 0.1875*(Table1[[#This Row],[skill_fk_accuracy]]/100) + 0.1875*(Table1[[#This Row],[attacking_crossing]]/100)))^2))  * ((1 - (Table1[[#This Row],[mentality_vision]]/100))^2))</f>
+        <v>2.7355166701562501</v>
+      </c>
+      <c r="DL66">
+        <f>1.585332 + 0.008219*Table1[[#This Row],[power_jumping]]+ 0.047559*Table1[[#This Row],[pace]] + 0.012348*Table1[[#This Row],[attacking_heading_accuracy]] + 0.362187*Table1[[#This Row],[develle_mcharo_passing]] + 0.015238*Table1[[#This Row],[dribbling]] + 0.189748*Table1[[#This Row],[weak_foot]] + 0.033917*Table1[[#This Row],[power_strength]] + 0.26019*Table1[[#This Row],[skill_moves]] + 0.808787*Table1[[#This Row],[Defender]] + 0.472467*Table1[[#This Row],[Midfielder]] + 0.081427*Table1[[#This Row],[Finesse_Shot]]</f>
+        <v>12.72997057621388</v>
+      </c>
     </row>
-    <row r="67" spans="1:114" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:116" x14ac:dyDescent="0.2">
       <c r="A67">
         <v>237712</v>
       </c>
@@ -25260,8 +25804,16 @@
       <c r="DJ67" t="s">
         <v>680</v>
       </c>
+      <c r="DK67">
+        <f xml:space="preserve"> (Table1[[#This Row],[mentality_vision]]/100) + 0.809*(Table1[[#This Row],[skill_curve]]/100) + (0.75*(Table1[[#This Row],[attacking_short_passing]]/100) + 0.25*(Table1[[#This Row],[attacking_crossing]]/100)) + (0.625*(Table1[[#This Row],[skill_long_passing]]/100) + 0.1875*(Table1[[#This Row],[skill_fk_accuracy]]/100) + 0.1875*(Table1[[#This Row],[attacking_crossing]]/100)) - ((1 - ((0.75*(Table1[[#This Row],[attacking_short_passing]]/100) + 0.25*(Table1[[#This Row],[attacking_crossing]]/100) - (0.625*(Table1[[#This Row],[skill_long_passing]]/100) + 0.1875*(Table1[[#This Row],[skill_fk_accuracy]]/100) + 0.1875*(Table1[[#This Row],[attacking_crossing]]/100)))^2))  * ((1 - (Table1[[#This Row],[mentality_vision]]/100))^2))</f>
+        <v>2.6527677828515626</v>
+      </c>
+      <c r="DL67">
+        <f>1.585332 + 0.008219*Table1[[#This Row],[power_jumping]]+ 0.047559*Table1[[#This Row],[pace]] + 0.012348*Table1[[#This Row],[attacking_heading_accuracy]] + 0.362187*Table1[[#This Row],[develle_mcharo_passing]] + 0.015238*Table1[[#This Row],[dribbling]] + 0.189748*Table1[[#This Row],[weak_foot]] + 0.033917*Table1[[#This Row],[power_strength]] + 0.26019*Table1[[#This Row],[skill_moves]] + 0.808787*Table1[[#This Row],[Defender]] + 0.472467*Table1[[#This Row],[Midfielder]] + 0.081427*Table1[[#This Row],[Finesse_Shot]]</f>
+        <v>12.706678004967658</v>
+      </c>
     </row>
-    <row r="68" spans="1:114" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:116" x14ac:dyDescent="0.2">
       <c r="A68">
         <v>243593</v>
       </c>
@@ -25587,8 +26139,16 @@
       <c r="DJ68" t="s">
         <v>686</v>
       </c>
+      <c r="DK68">
+        <f xml:space="preserve"> (Table1[[#This Row],[mentality_vision]]/100) + 0.809*(Table1[[#This Row],[skill_curve]]/100) + (0.75*(Table1[[#This Row],[attacking_short_passing]]/100) + 0.25*(Table1[[#This Row],[attacking_crossing]]/100)) + (0.625*(Table1[[#This Row],[skill_long_passing]]/100) + 0.1875*(Table1[[#This Row],[skill_fk_accuracy]]/100) + 0.1875*(Table1[[#This Row],[attacking_crossing]]/100)) - ((1 - ((0.75*(Table1[[#This Row],[attacking_short_passing]]/100) + 0.25*(Table1[[#This Row],[attacking_crossing]]/100) - (0.625*(Table1[[#This Row],[skill_long_passing]]/100) + 0.1875*(Table1[[#This Row],[skill_fk_accuracy]]/100) + 0.1875*(Table1[[#This Row],[attacking_crossing]]/100)))^2))  * ((1 - (Table1[[#This Row],[mentality_vision]]/100))^2))</f>
+        <v>2.7934481139062504</v>
+      </c>
+      <c r="DL68">
+        <f>1.585332 + 0.008219*Table1[[#This Row],[power_jumping]]+ 0.047559*Table1[[#This Row],[pace]] + 0.012348*Table1[[#This Row],[attacking_heading_accuracy]] + 0.362187*Table1[[#This Row],[develle_mcharo_passing]] + 0.015238*Table1[[#This Row],[dribbling]] + 0.189748*Table1[[#This Row],[weak_foot]] + 0.033917*Table1[[#This Row],[power_strength]] + 0.26019*Table1[[#This Row],[skill_moves]] + 0.808787*Table1[[#This Row],[Defender]] + 0.472467*Table1[[#This Row],[Midfielder]] + 0.081427*Table1[[#This Row],[Finesse_Shot]]</f>
+        <v>12.590828592031363</v>
+      </c>
     </row>
-    <row r="69" spans="1:114" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:116" x14ac:dyDescent="0.2">
       <c r="A69">
         <v>255654</v>
       </c>
@@ -25911,8 +26471,16 @@
       <c r="DJ69" t="s">
         <v>692</v>
       </c>
+      <c r="DK69">
+        <f xml:space="preserve"> (Table1[[#This Row],[mentality_vision]]/100) + 0.809*(Table1[[#This Row],[skill_curve]]/100) + (0.75*(Table1[[#This Row],[attacking_short_passing]]/100) + 0.25*(Table1[[#This Row],[attacking_crossing]]/100)) + (0.625*(Table1[[#This Row],[skill_long_passing]]/100) + 0.1875*(Table1[[#This Row],[skill_fk_accuracy]]/100) + 0.1875*(Table1[[#This Row],[attacking_crossing]]/100)) - ((1 - ((0.75*(Table1[[#This Row],[attacking_short_passing]]/100) + 0.25*(Table1[[#This Row],[attacking_crossing]]/100) - (0.625*(Table1[[#This Row],[skill_long_passing]]/100) + 0.1875*(Table1[[#This Row],[skill_fk_accuracy]]/100) + 0.1875*(Table1[[#This Row],[attacking_crossing]]/100)))^2))  * ((1 - (Table1[[#This Row],[mentality_vision]]/100))^2))</f>
+        <v>2.3232012056250002</v>
+      </c>
+      <c r="DL69">
+        <f>1.585332 + 0.008219*Table1[[#This Row],[power_jumping]]+ 0.047559*Table1[[#This Row],[pace]] + 0.012348*Table1[[#This Row],[attacking_heading_accuracy]] + 0.362187*Table1[[#This Row],[develle_mcharo_passing]] + 0.015238*Table1[[#This Row],[dribbling]] + 0.189748*Table1[[#This Row],[weak_foot]] + 0.033917*Table1[[#This Row],[power_strength]] + 0.26019*Table1[[#This Row],[skill_moves]] + 0.808787*Table1[[#This Row],[Defender]] + 0.472467*Table1[[#This Row],[Midfielder]] + 0.081427*Table1[[#This Row],[Finesse_Shot]]</f>
+        <v>13.280774275061702</v>
+      </c>
     </row>
-    <row r="70" spans="1:114" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:116" x14ac:dyDescent="0.2">
       <c r="A70">
         <v>246242</v>
       </c>
@@ -26235,8 +26803,16 @@
       <c r="DJ70" t="s">
         <v>697</v>
       </c>
+      <c r="DK70">
+        <f xml:space="preserve"> (Table1[[#This Row],[mentality_vision]]/100) + 0.809*(Table1[[#This Row],[skill_curve]]/100) + (0.75*(Table1[[#This Row],[attacking_short_passing]]/100) + 0.25*(Table1[[#This Row],[attacking_crossing]]/100)) + (0.625*(Table1[[#This Row],[skill_long_passing]]/100) + 0.1875*(Table1[[#This Row],[skill_fk_accuracy]]/100) + 0.1875*(Table1[[#This Row],[attacking_crossing]]/100)) - ((1 - ((0.75*(Table1[[#This Row],[attacking_short_passing]]/100) + 0.25*(Table1[[#This Row],[attacking_crossing]]/100) - (0.625*(Table1[[#This Row],[skill_long_passing]]/100) + 0.1875*(Table1[[#This Row],[skill_fk_accuracy]]/100) + 0.1875*(Table1[[#This Row],[attacking_crossing]]/100)))^2))  * ((1 - (Table1[[#This Row],[mentality_vision]]/100))^2))</f>
+        <v>2.3905043600000004</v>
+      </c>
+      <c r="DL70">
+        <f>1.585332 + 0.008219*Table1[[#This Row],[power_jumping]]+ 0.047559*Table1[[#This Row],[pace]] + 0.012348*Table1[[#This Row],[attacking_heading_accuracy]] + 0.362187*Table1[[#This Row],[develle_mcharo_passing]] + 0.015238*Table1[[#This Row],[dribbling]] + 0.189748*Table1[[#This Row],[weak_foot]] + 0.033917*Table1[[#This Row],[power_strength]] + 0.26019*Table1[[#This Row],[skill_moves]] + 0.808787*Table1[[#This Row],[Defender]] + 0.472467*Table1[[#This Row],[Midfielder]] + 0.081427*Table1[[#This Row],[Finesse_Shot]]</f>
+        <v>13.337582602635319</v>
+      </c>
     </row>
-    <row r="71" spans="1:114" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:116" x14ac:dyDescent="0.2">
       <c r="A71">
         <v>229668</v>
       </c>
@@ -26559,8 +27135,16 @@
       <c r="DJ71" t="s">
         <v>701</v>
       </c>
+      <c r="DK71">
+        <f xml:space="preserve"> (Table1[[#This Row],[mentality_vision]]/100) + 0.809*(Table1[[#This Row],[skill_curve]]/100) + (0.75*(Table1[[#This Row],[attacking_short_passing]]/100) + 0.25*(Table1[[#This Row],[attacking_crossing]]/100)) + (0.625*(Table1[[#This Row],[skill_long_passing]]/100) + 0.1875*(Table1[[#This Row],[skill_fk_accuracy]]/100) + 0.1875*(Table1[[#This Row],[attacking_crossing]]/100)) - ((1 - ((0.75*(Table1[[#This Row],[attacking_short_passing]]/100) + 0.25*(Table1[[#This Row],[attacking_crossing]]/100) - (0.625*(Table1[[#This Row],[skill_long_passing]]/100) + 0.1875*(Table1[[#This Row],[skill_fk_accuracy]]/100) + 0.1875*(Table1[[#This Row],[attacking_crossing]]/100)))^2))  * ((1 - (Table1[[#This Row],[mentality_vision]]/100))^2))</f>
+        <v>2.5761690006250002</v>
+      </c>
+      <c r="DL71">
+        <f>1.585332 + 0.008219*Table1[[#This Row],[power_jumping]]+ 0.047559*Table1[[#This Row],[pace]] + 0.012348*Table1[[#This Row],[attacking_heading_accuracy]] + 0.362187*Table1[[#This Row],[develle_mcharo_passing]] + 0.015238*Table1[[#This Row],[dribbling]] + 0.189748*Table1[[#This Row],[weak_foot]] + 0.033917*Table1[[#This Row],[power_strength]] + 0.26019*Table1[[#This Row],[skill_moves]] + 0.808787*Table1[[#This Row],[Defender]] + 0.472467*Table1[[#This Row],[Midfielder]] + 0.081427*Table1[[#This Row],[Finesse_Shot]]</f>
+        <v>13.384459921829366</v>
+      </c>
     </row>
-    <row r="72" spans="1:114" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:116" x14ac:dyDescent="0.2">
       <c r="A72">
         <v>266872</v>
       </c>
@@ -26892,8 +27476,16 @@
       <c r="DJ72" t="s">
         <v>706</v>
       </c>
+      <c r="DK72">
+        <f xml:space="preserve"> (Table1[[#This Row],[mentality_vision]]/100) + 0.809*(Table1[[#This Row],[skill_curve]]/100) + (0.75*(Table1[[#This Row],[attacking_short_passing]]/100) + 0.25*(Table1[[#This Row],[attacking_crossing]]/100)) + (0.625*(Table1[[#This Row],[skill_long_passing]]/100) + 0.1875*(Table1[[#This Row],[skill_fk_accuracy]]/100) + 0.1875*(Table1[[#This Row],[attacking_crossing]]/100)) - ((1 - ((0.75*(Table1[[#This Row],[attacking_short_passing]]/100) + 0.25*(Table1[[#This Row],[attacking_crossing]]/100) - (0.625*(Table1[[#This Row],[skill_long_passing]]/100) + 0.1875*(Table1[[#This Row],[skill_fk_accuracy]]/100) + 0.1875*(Table1[[#This Row],[attacking_crossing]]/100)))^2))  * ((1 - (Table1[[#This Row],[mentality_vision]]/100))^2))</f>
+        <v>1.4927500624999999</v>
+      </c>
+      <c r="DL72">
+        <f>1.585332 + 0.008219*Table1[[#This Row],[power_jumping]]+ 0.047559*Table1[[#This Row],[pace]] + 0.012348*Table1[[#This Row],[attacking_heading_accuracy]] + 0.362187*Table1[[#This Row],[develle_mcharo_passing]] + 0.015238*Table1[[#This Row],[dribbling]] + 0.189748*Table1[[#This Row],[weak_foot]] + 0.033917*Table1[[#This Row],[power_strength]] + 0.26019*Table1[[#This Row],[skill_moves]] + 0.808787*Table1[[#This Row],[Defender]] + 0.472467*Table1[[#This Row],[Midfielder]] + 0.081427*Table1[[#This Row],[Finesse_Shot]]</f>
+        <v>13.087740666886686</v>
+      </c>
     </row>
-    <row r="73" spans="1:114" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:116" x14ac:dyDescent="0.2">
       <c r="A73">
         <v>246875</v>
       </c>
@@ -27213,8 +27805,16 @@
       <c r="DJ73" t="s">
         <v>711</v>
       </c>
+      <c r="DK73">
+        <f xml:space="preserve"> (Table1[[#This Row],[mentality_vision]]/100) + 0.809*(Table1[[#This Row],[skill_curve]]/100) + (0.75*(Table1[[#This Row],[attacking_short_passing]]/100) + 0.25*(Table1[[#This Row],[attacking_crossing]]/100)) + (0.625*(Table1[[#This Row],[skill_long_passing]]/100) + 0.1875*(Table1[[#This Row],[skill_fk_accuracy]]/100) + 0.1875*(Table1[[#This Row],[attacking_crossing]]/100)) - ((1 - ((0.75*(Table1[[#This Row],[attacking_short_passing]]/100) + 0.25*(Table1[[#This Row],[attacking_crossing]]/100) - (0.625*(Table1[[#This Row],[skill_long_passing]]/100) + 0.1875*(Table1[[#This Row],[skill_fk_accuracy]]/100) + 0.1875*(Table1[[#This Row],[attacking_crossing]]/100)))^2))  * ((1 - (Table1[[#This Row],[mentality_vision]]/100))^2))</f>
+        <v>1.9833171847265627</v>
+      </c>
+      <c r="DL73">
+        <f>1.585332 + 0.008219*Table1[[#This Row],[power_jumping]]+ 0.047559*Table1[[#This Row],[pace]] + 0.012348*Table1[[#This Row],[attacking_heading_accuracy]] + 0.362187*Table1[[#This Row],[develle_mcharo_passing]] + 0.015238*Table1[[#This Row],[dribbling]] + 0.189748*Table1[[#This Row],[weak_foot]] + 0.033917*Table1[[#This Row],[power_strength]] + 0.26019*Table1[[#This Row],[skill_moves]] + 0.808787*Table1[[#This Row],[Defender]] + 0.472467*Table1[[#This Row],[Midfielder]] + 0.081427*Table1[[#This Row],[Finesse_Shot]]</f>
+        <v>13.340195701184557</v>
+      </c>
     </row>
-    <row r="74" spans="1:114" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:116" x14ac:dyDescent="0.2">
       <c r="A74">
         <v>220651</v>
       </c>
@@ -27540,8 +28140,16 @@
       <c r="DJ74" t="s">
         <v>716</v>
       </c>
+      <c r="DK74">
+        <f xml:space="preserve"> (Table1[[#This Row],[mentality_vision]]/100) + 0.809*(Table1[[#This Row],[skill_curve]]/100) + (0.75*(Table1[[#This Row],[attacking_short_passing]]/100) + 0.25*(Table1[[#This Row],[attacking_crossing]]/100)) + (0.625*(Table1[[#This Row],[skill_long_passing]]/100) + 0.1875*(Table1[[#This Row],[skill_fk_accuracy]]/100) + 0.1875*(Table1[[#This Row],[attacking_crossing]]/100)) - ((1 - ((0.75*(Table1[[#This Row],[attacking_short_passing]]/100) + 0.25*(Table1[[#This Row],[attacking_crossing]]/100) - (0.625*(Table1[[#This Row],[skill_long_passing]]/100) + 0.1875*(Table1[[#This Row],[skill_fk_accuracy]]/100) + 0.1875*(Table1[[#This Row],[attacking_crossing]]/100)))^2))  * ((1 - (Table1[[#This Row],[mentality_vision]]/100))^2))</f>
+        <v>3.0368533506249999</v>
+      </c>
+      <c r="DL74">
+        <f>1.585332 + 0.008219*Table1[[#This Row],[power_jumping]]+ 0.047559*Table1[[#This Row],[pace]] + 0.012348*Table1[[#This Row],[attacking_heading_accuracy]] + 0.362187*Table1[[#This Row],[develle_mcharo_passing]] + 0.015238*Table1[[#This Row],[dribbling]] + 0.189748*Table1[[#This Row],[weak_foot]] + 0.033917*Table1[[#This Row],[power_strength]] + 0.26019*Table1[[#This Row],[skill_moves]] + 0.808787*Table1[[#This Row],[Defender]] + 0.472467*Table1[[#This Row],[Midfielder]] + 0.081427*Table1[[#This Row],[Finesse_Shot]]</f>
+        <v>12.865467804502817</v>
+      </c>
     </row>
-    <row r="75" spans="1:114" x14ac:dyDescent="0.2">
+    <row r="75" spans="1:116" x14ac:dyDescent="0.2">
       <c r="A75">
         <v>250723</v>
       </c>
@@ -27873,8 +28481,16 @@
       <c r="DJ75" t="s">
         <v>721</v>
       </c>
+      <c r="DK75">
+        <f xml:space="preserve"> (Table1[[#This Row],[mentality_vision]]/100) + 0.809*(Table1[[#This Row],[skill_curve]]/100) + (0.75*(Table1[[#This Row],[attacking_short_passing]]/100) + 0.25*(Table1[[#This Row],[attacking_crossing]]/100)) + (0.625*(Table1[[#This Row],[skill_long_passing]]/100) + 0.1875*(Table1[[#This Row],[skill_fk_accuracy]]/100) + 0.1875*(Table1[[#This Row],[attacking_crossing]]/100)) - ((1 - ((0.75*(Table1[[#This Row],[attacking_short_passing]]/100) + 0.25*(Table1[[#This Row],[attacking_crossing]]/100) - (0.625*(Table1[[#This Row],[skill_long_passing]]/100) + 0.1875*(Table1[[#This Row],[skill_fk_accuracy]]/100) + 0.1875*(Table1[[#This Row],[attacking_crossing]]/100)))^2))  * ((1 - (Table1[[#This Row],[mentality_vision]]/100))^2))</f>
+        <v>2.7347258056640626</v>
+      </c>
+      <c r="DL75">
+        <f>1.585332 + 0.008219*Table1[[#This Row],[power_jumping]]+ 0.047559*Table1[[#This Row],[pace]] + 0.012348*Table1[[#This Row],[attacking_heading_accuracy]] + 0.362187*Table1[[#This Row],[develle_mcharo_passing]] + 0.015238*Table1[[#This Row],[dribbling]] + 0.189748*Table1[[#This Row],[weak_foot]] + 0.033917*Table1[[#This Row],[power_strength]] + 0.26019*Table1[[#This Row],[skill_moves]] + 0.808787*Table1[[#This Row],[Defender]] + 0.472467*Table1[[#This Row],[Midfielder]] + 0.081427*Table1[[#This Row],[Finesse_Shot]]</f>
+        <v>13.71496413537605</v>
+      </c>
     </row>
-    <row r="76" spans="1:114" x14ac:dyDescent="0.2">
+    <row r="76" spans="1:116" x14ac:dyDescent="0.2">
       <c r="A76">
         <v>216150</v>
       </c>
@@ -28197,8 +28813,16 @@
       <c r="DJ76" t="s">
         <v>727</v>
       </c>
+      <c r="DK76">
+        <f xml:space="preserve"> (Table1[[#This Row],[mentality_vision]]/100) + 0.809*(Table1[[#This Row],[skill_curve]]/100) + (0.75*(Table1[[#This Row],[attacking_short_passing]]/100) + 0.25*(Table1[[#This Row],[attacking_crossing]]/100)) + (0.625*(Table1[[#This Row],[skill_long_passing]]/100) + 0.1875*(Table1[[#This Row],[skill_fk_accuracy]]/100) + 0.1875*(Table1[[#This Row],[attacking_crossing]]/100)) - ((1 - ((0.75*(Table1[[#This Row],[attacking_short_passing]]/100) + 0.25*(Table1[[#This Row],[attacking_crossing]]/100) - (0.625*(Table1[[#This Row],[skill_long_passing]]/100) + 0.1875*(Table1[[#This Row],[skill_fk_accuracy]]/100) + 0.1875*(Table1[[#This Row],[attacking_crossing]]/100)))^2))  * ((1 - (Table1[[#This Row],[mentality_vision]]/100))^2))</f>
+        <v>2.7807825976562497</v>
+      </c>
+      <c r="DL76">
+        <f>1.585332 + 0.008219*Table1[[#This Row],[power_jumping]]+ 0.047559*Table1[[#This Row],[pace]] + 0.012348*Table1[[#This Row],[attacking_heading_accuracy]] + 0.362187*Table1[[#This Row],[develle_mcharo_passing]] + 0.015238*Table1[[#This Row],[dribbling]] + 0.189748*Table1[[#This Row],[weak_foot]] + 0.033917*Table1[[#This Row],[power_strength]] + 0.26019*Table1[[#This Row],[skill_moves]] + 0.808787*Table1[[#This Row],[Defender]] + 0.472467*Table1[[#This Row],[Midfielder]] + 0.081427*Table1[[#This Row],[Finesse_Shot]]</f>
+        <v>13.076280306697322</v>
+      </c>
     </row>
-    <row r="77" spans="1:114" x14ac:dyDescent="0.2">
+    <row r="77" spans="1:116" x14ac:dyDescent="0.2">
       <c r="A77">
         <v>258966</v>
       </c>
@@ -28530,8 +29154,16 @@
       <c r="DJ77" t="s">
         <v>733</v>
       </c>
+      <c r="DK77">
+        <f xml:space="preserve"> (Table1[[#This Row],[mentality_vision]]/100) + 0.809*(Table1[[#This Row],[skill_curve]]/100) + (0.75*(Table1[[#This Row],[attacking_short_passing]]/100) + 0.25*(Table1[[#This Row],[attacking_crossing]]/100)) + (0.625*(Table1[[#This Row],[skill_long_passing]]/100) + 0.1875*(Table1[[#This Row],[skill_fk_accuracy]]/100) + 0.1875*(Table1[[#This Row],[attacking_crossing]]/100)) - ((1 - ((0.75*(Table1[[#This Row],[attacking_short_passing]]/100) + 0.25*(Table1[[#This Row],[attacking_crossing]]/100) - (0.625*(Table1[[#This Row],[skill_long_passing]]/100) + 0.1875*(Table1[[#This Row],[skill_fk_accuracy]]/100) + 0.1875*(Table1[[#This Row],[attacking_crossing]]/100)))^2))  * ((1 - (Table1[[#This Row],[mentality_vision]]/100))^2))</f>
+        <v>2.8802770847265626</v>
+      </c>
+      <c r="DL77">
+        <f>1.585332 + 0.008219*Table1[[#This Row],[power_jumping]]+ 0.047559*Table1[[#This Row],[pace]] + 0.012348*Table1[[#This Row],[attacking_heading_accuracy]] + 0.362187*Table1[[#This Row],[develle_mcharo_passing]] + 0.015238*Table1[[#This Row],[dribbling]] + 0.189748*Table1[[#This Row],[weak_foot]] + 0.033917*Table1[[#This Row],[power_strength]] + 0.26019*Table1[[#This Row],[skill_moves]] + 0.808787*Table1[[#This Row],[Defender]] + 0.472467*Table1[[#This Row],[Midfielder]] + 0.081427*Table1[[#This Row],[Finesse_Shot]]</f>
+        <v>13.700554916485858</v>
+      </c>
     </row>
-    <row r="78" spans="1:114" x14ac:dyDescent="0.2">
+    <row r="78" spans="1:116" x14ac:dyDescent="0.2">
       <c r="A78">
         <v>255001</v>
       </c>
@@ -28863,8 +29495,16 @@
       <c r="DJ78" t="s">
         <v>738</v>
       </c>
+      <c r="DK78">
+        <f xml:space="preserve"> (Table1[[#This Row],[mentality_vision]]/100) + 0.809*(Table1[[#This Row],[skill_curve]]/100) + (0.75*(Table1[[#This Row],[attacking_short_passing]]/100) + 0.25*(Table1[[#This Row],[attacking_crossing]]/100)) + (0.625*(Table1[[#This Row],[skill_long_passing]]/100) + 0.1875*(Table1[[#This Row],[skill_fk_accuracy]]/100) + 0.1875*(Table1[[#This Row],[attacking_crossing]]/100)) - ((1 - ((0.75*(Table1[[#This Row],[attacking_short_passing]]/100) + 0.25*(Table1[[#This Row],[attacking_crossing]]/100) - (0.625*(Table1[[#This Row],[skill_long_passing]]/100) + 0.1875*(Table1[[#This Row],[skill_fk_accuracy]]/100) + 0.1875*(Table1[[#This Row],[attacking_crossing]]/100)))^2))  * ((1 - (Table1[[#This Row],[mentality_vision]]/100))^2))</f>
+        <v>2.8858348751562506</v>
+      </c>
+      <c r="DL78">
+        <f>1.585332 + 0.008219*Table1[[#This Row],[power_jumping]]+ 0.047559*Table1[[#This Row],[pace]] + 0.012348*Table1[[#This Row],[attacking_heading_accuracy]] + 0.362187*Table1[[#This Row],[develle_mcharo_passing]] + 0.015238*Table1[[#This Row],[dribbling]] + 0.189748*Table1[[#This Row],[weak_foot]] + 0.033917*Table1[[#This Row],[power_strength]] + 0.26019*Table1[[#This Row],[skill_moves]] + 0.808787*Table1[[#This Row],[Defender]] + 0.472467*Table1[[#This Row],[Midfielder]] + 0.081427*Table1[[#This Row],[Finesse_Shot]]</f>
+        <v>12.905818875928217</v>
+      </c>
     </row>
-    <row r="79" spans="1:114" x14ac:dyDescent="0.2">
+    <row r="79" spans="1:116" x14ac:dyDescent="0.2">
       <c r="A79">
         <v>237942</v>
       </c>
@@ -29184,8 +29824,16 @@
       <c r="DJ79" t="s">
         <v>743</v>
       </c>
+      <c r="DK79">
+        <f xml:space="preserve"> (Table1[[#This Row],[mentality_vision]]/100) + 0.809*(Table1[[#This Row],[skill_curve]]/100) + (0.75*(Table1[[#This Row],[attacking_short_passing]]/100) + 0.25*(Table1[[#This Row],[attacking_crossing]]/100)) + (0.625*(Table1[[#This Row],[skill_long_passing]]/100) + 0.1875*(Table1[[#This Row],[skill_fk_accuracy]]/100) + 0.1875*(Table1[[#This Row],[attacking_crossing]]/100)) - ((1 - ((0.75*(Table1[[#This Row],[attacking_short_passing]]/100) + 0.25*(Table1[[#This Row],[attacking_crossing]]/100) - (0.625*(Table1[[#This Row],[skill_long_passing]]/100) + 0.1875*(Table1[[#This Row],[skill_fk_accuracy]]/100) + 0.1875*(Table1[[#This Row],[attacking_crossing]]/100)))^2))  * ((1 - (Table1[[#This Row],[mentality_vision]]/100))^2))</f>
+        <v>2.8090200625000001</v>
+      </c>
+      <c r="DL79">
+        <f>1.585332 + 0.008219*Table1[[#This Row],[power_jumping]]+ 0.047559*Table1[[#This Row],[pace]] + 0.012348*Table1[[#This Row],[attacking_heading_accuracy]] + 0.362187*Table1[[#This Row],[develle_mcharo_passing]] + 0.015238*Table1[[#This Row],[dribbling]] + 0.189748*Table1[[#This Row],[weak_foot]] + 0.033917*Table1[[#This Row],[power_strength]] + 0.26019*Table1[[#This Row],[skill_moves]] + 0.808787*Table1[[#This Row],[Defender]] + 0.472467*Table1[[#This Row],[Midfielder]] + 0.081427*Table1[[#This Row],[Finesse_Shot]]</f>
+        <v>13.367950549376689</v>
+      </c>
     </row>
-    <row r="80" spans="1:114" x14ac:dyDescent="0.2">
+    <row r="80" spans="1:116" x14ac:dyDescent="0.2">
       <c r="A80">
         <v>241095</v>
       </c>
@@ -29517,8 +30165,16 @@
       <c r="DJ80" t="s">
         <v>749</v>
       </c>
+      <c r="DK80">
+        <f xml:space="preserve"> (Table1[[#This Row],[mentality_vision]]/100) + 0.809*(Table1[[#This Row],[skill_curve]]/100) + (0.75*(Table1[[#This Row],[attacking_short_passing]]/100) + 0.25*(Table1[[#This Row],[attacking_crossing]]/100)) + (0.625*(Table1[[#This Row],[skill_long_passing]]/100) + 0.1875*(Table1[[#This Row],[skill_fk_accuracy]]/100) + 0.1875*(Table1[[#This Row],[attacking_crossing]]/100)) - ((1 - ((0.75*(Table1[[#This Row],[attacking_short_passing]]/100) + 0.25*(Table1[[#This Row],[attacking_crossing]]/100) - (0.625*(Table1[[#This Row],[skill_long_passing]]/100) + 0.1875*(Table1[[#This Row],[skill_fk_accuracy]]/100) + 0.1875*(Table1[[#This Row],[attacking_crossing]]/100)))^2))  * ((1 - (Table1[[#This Row],[mentality_vision]]/100))^2))</f>
+        <v>2.8061313476562502</v>
+      </c>
+      <c r="DL80">
+        <f>1.585332 + 0.008219*Table1[[#This Row],[power_jumping]]+ 0.047559*Table1[[#This Row],[pace]] + 0.012348*Table1[[#This Row],[attacking_heading_accuracy]] + 0.362187*Table1[[#This Row],[develle_mcharo_passing]] + 0.015238*Table1[[#This Row],[dribbling]] + 0.189748*Table1[[#This Row],[weak_foot]] + 0.033917*Table1[[#This Row],[power_strength]] + 0.26019*Table1[[#This Row],[skill_moves]] + 0.808787*Table1[[#This Row],[Defender]] + 0.472467*Table1[[#This Row],[Midfielder]] + 0.081427*Table1[[#This Row],[Finesse_Shot]]</f>
+        <v>12.518532294413575</v>
+      </c>
     </row>
-    <row r="81" spans="1:114" x14ac:dyDescent="0.2">
+    <row r="81" spans="1:116" x14ac:dyDescent="0.2">
       <c r="A81">
         <v>242664</v>
       </c>
@@ -29841,8 +30497,16 @@
       <c r="DJ81" t="s">
         <v>755</v>
       </c>
+      <c r="DK81">
+        <f xml:space="preserve"> (Table1[[#This Row],[mentality_vision]]/100) + 0.809*(Table1[[#This Row],[skill_curve]]/100) + (0.75*(Table1[[#This Row],[attacking_short_passing]]/100) + 0.25*(Table1[[#This Row],[attacking_crossing]]/100)) + (0.625*(Table1[[#This Row],[skill_long_passing]]/100) + 0.1875*(Table1[[#This Row],[skill_fk_accuracy]]/100) + 0.1875*(Table1[[#This Row],[attacking_crossing]]/100)) - ((1 - ((0.75*(Table1[[#This Row],[attacking_short_passing]]/100) + 0.25*(Table1[[#This Row],[attacking_crossing]]/100) - (0.625*(Table1[[#This Row],[skill_long_passing]]/100) + 0.1875*(Table1[[#This Row],[skill_fk_accuracy]]/100) + 0.1875*(Table1[[#This Row],[attacking_crossing]]/100)))^2))  * ((1 - (Table1[[#This Row],[mentality_vision]]/100))^2))</f>
+        <v>2.7317135222265621</v>
+      </c>
+      <c r="DL81">
+        <f>1.585332 + 0.008219*Table1[[#This Row],[power_jumping]]+ 0.047559*Table1[[#This Row],[pace]] + 0.012348*Table1[[#This Row],[attacking_heading_accuracy]] + 0.362187*Table1[[#This Row],[develle_mcharo_passing]] + 0.015238*Table1[[#This Row],[dribbling]] + 0.189748*Table1[[#This Row],[weak_foot]] + 0.033917*Table1[[#This Row],[power_strength]] + 0.26019*Table1[[#This Row],[skill_moves]] + 0.808787*Table1[[#This Row],[Defender]] + 0.472467*Table1[[#This Row],[Midfielder]] + 0.081427*Table1[[#This Row],[Finesse_Shot]]</f>
+        <v>12.318448125474672</v>
+      </c>
     </row>
-    <row r="82" spans="1:114" x14ac:dyDescent="0.2">
+    <row r="82" spans="1:116" x14ac:dyDescent="0.2">
       <c r="A82">
         <v>268804</v>
       </c>
@@ -30165,8 +30829,16 @@
       <c r="DJ82" t="s">
         <v>760</v>
       </c>
+      <c r="DK82">
+        <f xml:space="preserve"> (Table1[[#This Row],[mentality_vision]]/100) + 0.809*(Table1[[#This Row],[skill_curve]]/100) + (0.75*(Table1[[#This Row],[attacking_short_passing]]/100) + 0.25*(Table1[[#This Row],[attacking_crossing]]/100)) + (0.625*(Table1[[#This Row],[skill_long_passing]]/100) + 0.1875*(Table1[[#This Row],[skill_fk_accuracy]]/100) + 0.1875*(Table1[[#This Row],[attacking_crossing]]/100)) - ((1 - ((0.75*(Table1[[#This Row],[attacking_short_passing]]/100) + 0.25*(Table1[[#This Row],[attacking_crossing]]/100) - (0.625*(Table1[[#This Row],[skill_long_passing]]/100) + 0.1875*(Table1[[#This Row],[skill_fk_accuracy]]/100) + 0.1875*(Table1[[#This Row],[attacking_crossing]]/100)))^2))  * ((1 - (Table1[[#This Row],[mentality_vision]]/100))^2))</f>
+        <v>2.3320955225</v>
+      </c>
+      <c r="DL82">
+        <f>1.585332 + 0.008219*Table1[[#This Row],[power_jumping]]+ 0.047559*Table1[[#This Row],[pace]] + 0.012348*Table1[[#This Row],[attacking_heading_accuracy]] + 0.362187*Table1[[#This Row],[develle_mcharo_passing]] + 0.015238*Table1[[#This Row],[dribbling]] + 0.189748*Table1[[#This Row],[weak_foot]] + 0.033917*Table1[[#This Row],[power_strength]] + 0.26019*Table1[[#This Row],[skill_moves]] + 0.808787*Table1[[#This Row],[Defender]] + 0.472467*Table1[[#This Row],[Midfielder]] + 0.081427*Table1[[#This Row],[Finesse_Shot]]</f>
+        <v>13.810381681007707</v>
+      </c>
     </row>
-    <row r="83" spans="1:114" x14ac:dyDescent="0.2">
+    <row r="83" spans="1:116" x14ac:dyDescent="0.2">
       <c r="A83">
         <v>190813</v>
       </c>
@@ -30489,8 +31161,16 @@
       <c r="DJ83" t="s">
         <v>765</v>
       </c>
+      <c r="DK83">
+        <f xml:space="preserve"> (Table1[[#This Row],[mentality_vision]]/100) + 0.809*(Table1[[#This Row],[skill_curve]]/100) + (0.75*(Table1[[#This Row],[attacking_short_passing]]/100) + 0.25*(Table1[[#This Row],[attacking_crossing]]/100)) + (0.625*(Table1[[#This Row],[skill_long_passing]]/100) + 0.1875*(Table1[[#This Row],[skill_fk_accuracy]]/100) + 0.1875*(Table1[[#This Row],[attacking_crossing]]/100)) - ((1 - ((0.75*(Table1[[#This Row],[attacking_short_passing]]/100) + 0.25*(Table1[[#This Row],[attacking_crossing]]/100) - (0.625*(Table1[[#This Row],[skill_long_passing]]/100) + 0.1875*(Table1[[#This Row],[skill_fk_accuracy]]/100) + 0.1875*(Table1[[#This Row],[attacking_crossing]]/100)))^2))  * ((1 - (Table1[[#This Row],[mentality_vision]]/100))^2))</f>
+        <v>2.9018834024999998</v>
+      </c>
+      <c r="DL83">
+        <f>1.585332 + 0.008219*Table1[[#This Row],[power_jumping]]+ 0.047559*Table1[[#This Row],[pace]] + 0.012348*Table1[[#This Row],[attacking_heading_accuracy]] + 0.362187*Table1[[#This Row],[develle_mcharo_passing]] + 0.015238*Table1[[#This Row],[dribbling]] + 0.189748*Table1[[#This Row],[weak_foot]] + 0.033917*Table1[[#This Row],[power_strength]] + 0.26019*Table1[[#This Row],[skill_moves]] + 0.808787*Table1[[#This Row],[Defender]] + 0.472467*Table1[[#This Row],[Midfielder]] + 0.081427*Table1[[#This Row],[Finesse_Shot]]</f>
+        <v>12.674781443901265</v>
+      </c>
     </row>
-    <row r="84" spans="1:114" x14ac:dyDescent="0.2">
+    <row r="84" spans="1:116" x14ac:dyDescent="0.2">
       <c r="A84">
         <v>277954</v>
       </c>
@@ -30813,8 +31493,16 @@
       <c r="DJ84" t="s">
         <v>770</v>
       </c>
+      <c r="DK84">
+        <f xml:space="preserve"> (Table1[[#This Row],[mentality_vision]]/100) + 0.809*(Table1[[#This Row],[skill_curve]]/100) + (0.75*(Table1[[#This Row],[attacking_short_passing]]/100) + 0.25*(Table1[[#This Row],[attacking_crossing]]/100)) + (0.625*(Table1[[#This Row],[skill_long_passing]]/100) + 0.1875*(Table1[[#This Row],[skill_fk_accuracy]]/100) + 0.1875*(Table1[[#This Row],[attacking_crossing]]/100)) - ((1 - ((0.75*(Table1[[#This Row],[attacking_short_passing]]/100) + 0.25*(Table1[[#This Row],[attacking_crossing]]/100) - (0.625*(Table1[[#This Row],[skill_long_passing]]/100) + 0.1875*(Table1[[#This Row],[skill_fk_accuracy]]/100) + 0.1875*(Table1[[#This Row],[attacking_crossing]]/100)))^2))  * ((1 - (Table1[[#This Row],[mentality_vision]]/100))^2))</f>
+        <v>2.8137851187890628</v>
+      </c>
+      <c r="DL84">
+        <f>1.585332 + 0.008219*Table1[[#This Row],[power_jumping]]+ 0.047559*Table1[[#This Row],[pace]] + 0.012348*Table1[[#This Row],[attacking_heading_accuracy]] + 0.362187*Table1[[#This Row],[develle_mcharo_passing]] + 0.015238*Table1[[#This Row],[dribbling]] + 0.189748*Table1[[#This Row],[weak_foot]] + 0.033917*Table1[[#This Row],[power_strength]] + 0.26019*Table1[[#This Row],[skill_moves]] + 0.808787*Table1[[#This Row],[Defender]] + 0.472467*Table1[[#This Row],[Midfielder]] + 0.081427*Table1[[#This Row],[Finesse_Shot]]</f>
+        <v>13.635629390818856</v>
+      </c>
     </row>
-    <row r="85" spans="1:114" x14ac:dyDescent="0.2">
+    <row r="85" spans="1:116" x14ac:dyDescent="0.2">
       <c r="A85">
         <v>245152</v>
       </c>
@@ -31146,8 +31834,16 @@
       <c r="DJ85" t="s">
         <v>775</v>
       </c>
+      <c r="DK85">
+        <f xml:space="preserve"> (Table1[[#This Row],[mentality_vision]]/100) + 0.809*(Table1[[#This Row],[skill_curve]]/100) + (0.75*(Table1[[#This Row],[attacking_short_passing]]/100) + 0.25*(Table1[[#This Row],[attacking_crossing]]/100)) + (0.625*(Table1[[#This Row],[skill_long_passing]]/100) + 0.1875*(Table1[[#This Row],[skill_fk_accuracy]]/100) + 0.1875*(Table1[[#This Row],[attacking_crossing]]/100)) - ((1 - ((0.75*(Table1[[#This Row],[attacking_short_passing]]/100) + 0.25*(Table1[[#This Row],[attacking_crossing]]/100) - (0.625*(Table1[[#This Row],[skill_long_passing]]/100) + 0.1875*(Table1[[#This Row],[skill_fk_accuracy]]/100) + 0.1875*(Table1[[#This Row],[attacking_crossing]]/100)))^2))  * ((1 - (Table1[[#This Row],[mentality_vision]]/100))^2))</f>
+        <v>2.6340043164062501</v>
+      </c>
+      <c r="DL85">
+        <f>1.585332 + 0.008219*Table1[[#This Row],[power_jumping]]+ 0.047559*Table1[[#This Row],[pace]] + 0.012348*Table1[[#This Row],[attacking_heading_accuracy]] + 0.362187*Table1[[#This Row],[develle_mcharo_passing]] + 0.015238*Table1[[#This Row],[dribbling]] + 0.189748*Table1[[#This Row],[weak_foot]] + 0.033917*Table1[[#This Row],[power_strength]] + 0.26019*Table1[[#This Row],[skill_moves]] + 0.808787*Table1[[#This Row],[Defender]] + 0.472467*Table1[[#This Row],[Midfielder]] + 0.081427*Table1[[#This Row],[Finesse_Shot]]</f>
+        <v>12.888883121346229</v>
+      </c>
     </row>
-    <row r="86" spans="1:114" x14ac:dyDescent="0.2">
+    <row r="86" spans="1:116" x14ac:dyDescent="0.2">
       <c r="A86">
         <v>229906</v>
       </c>
@@ -31470,8 +32166,16 @@
       <c r="DJ86" t="s">
         <v>782</v>
       </c>
+      <c r="DK86">
+        <f xml:space="preserve"> (Table1[[#This Row],[mentality_vision]]/100) + 0.809*(Table1[[#This Row],[skill_curve]]/100) + (0.75*(Table1[[#This Row],[attacking_short_passing]]/100) + 0.25*(Table1[[#This Row],[attacking_crossing]]/100)) + (0.625*(Table1[[#This Row],[skill_long_passing]]/100) + 0.1875*(Table1[[#This Row],[skill_fk_accuracy]]/100) + 0.1875*(Table1[[#This Row],[attacking_crossing]]/100)) - ((1 - ((0.75*(Table1[[#This Row],[attacking_short_passing]]/100) + 0.25*(Table1[[#This Row],[attacking_crossing]]/100) - (0.625*(Table1[[#This Row],[skill_long_passing]]/100) + 0.1875*(Table1[[#This Row],[skill_fk_accuracy]]/100) + 0.1875*(Table1[[#This Row],[attacking_crossing]]/100)))^2))  * ((1 - (Table1[[#This Row],[mentality_vision]]/100))^2))</f>
+        <v>2.7345050634765622</v>
+      </c>
+      <c r="DL86">
+        <f>1.585332 + 0.008219*Table1[[#This Row],[power_jumping]]+ 0.047559*Table1[[#This Row],[pace]] + 0.012348*Table1[[#This Row],[attacking_heading_accuracy]] + 0.362187*Table1[[#This Row],[develle_mcharo_passing]] + 0.015238*Table1[[#This Row],[dribbling]] + 0.189748*Table1[[#This Row],[weak_foot]] + 0.033917*Table1[[#This Row],[power_strength]] + 0.26019*Table1[[#This Row],[skill_moves]] + 0.808787*Table1[[#This Row],[Defender]] + 0.472467*Table1[[#This Row],[Midfielder]] + 0.081427*Table1[[#This Row],[Finesse_Shot]]</f>
+        <v>12.802813185425386</v>
+      </c>
     </row>
-    <row r="87" spans="1:114" x14ac:dyDescent="0.2">
+    <row r="87" spans="1:116" x14ac:dyDescent="0.2">
       <c r="A87">
         <v>207993</v>
       </c>
@@ -31794,8 +32498,16 @@
       <c r="DJ87" t="s">
         <v>787</v>
       </c>
+      <c r="DK87">
+        <f xml:space="preserve"> (Table1[[#This Row],[mentality_vision]]/100) + 0.809*(Table1[[#This Row],[skill_curve]]/100) + (0.75*(Table1[[#This Row],[attacking_short_passing]]/100) + 0.25*(Table1[[#This Row],[attacking_crossing]]/100)) + (0.625*(Table1[[#This Row],[skill_long_passing]]/100) + 0.1875*(Table1[[#This Row],[skill_fk_accuracy]]/100) + 0.1875*(Table1[[#This Row],[attacking_crossing]]/100)) - ((1 - ((0.75*(Table1[[#This Row],[attacking_short_passing]]/100) + 0.25*(Table1[[#This Row],[attacking_crossing]]/100) - (0.625*(Table1[[#This Row],[skill_long_passing]]/100) + 0.1875*(Table1[[#This Row],[skill_fk_accuracy]]/100) + 0.1875*(Table1[[#This Row],[attacking_crossing]]/100)))^2))  * ((1 - (Table1[[#This Row],[mentality_vision]]/100))^2))</f>
+        <v>2.3698759619140626</v>
+      </c>
+      <c r="DL87">
+        <f>1.585332 + 0.008219*Table1[[#This Row],[power_jumping]]+ 0.047559*Table1[[#This Row],[pace]] + 0.012348*Table1[[#This Row],[attacking_heading_accuracy]] + 0.362187*Table1[[#This Row],[develle_mcharo_passing]] + 0.015238*Table1[[#This Row],[dribbling]] + 0.189748*Table1[[#This Row],[weak_foot]] + 0.033917*Table1[[#This Row],[power_strength]] + 0.26019*Table1[[#This Row],[skill_moves]] + 0.808787*Table1[[#This Row],[Defender]] + 0.472467*Table1[[#This Row],[Midfielder]] + 0.081427*Table1[[#This Row],[Finesse_Shot]]</f>
+        <v>12.524152265017769</v>
+      </c>
     </row>
-    <row r="88" spans="1:114" x14ac:dyDescent="0.2">
+    <row r="88" spans="1:116" x14ac:dyDescent="0.2">
       <c r="A88">
         <v>238004</v>
       </c>
@@ -32124,8 +32836,16 @@
       <c r="DJ88" t="s">
         <v>792</v>
       </c>
+      <c r="DK88">
+        <f xml:space="preserve"> (Table1[[#This Row],[mentality_vision]]/100) + 0.809*(Table1[[#This Row],[skill_curve]]/100) + (0.75*(Table1[[#This Row],[attacking_short_passing]]/100) + 0.25*(Table1[[#This Row],[attacking_crossing]]/100)) + (0.625*(Table1[[#This Row],[skill_long_passing]]/100) + 0.1875*(Table1[[#This Row],[skill_fk_accuracy]]/100) + 0.1875*(Table1[[#This Row],[attacking_crossing]]/100)) - ((1 - ((0.75*(Table1[[#This Row],[attacking_short_passing]]/100) + 0.25*(Table1[[#This Row],[attacking_crossing]]/100) - (0.625*(Table1[[#This Row],[skill_long_passing]]/100) + 0.1875*(Table1[[#This Row],[skill_fk_accuracy]]/100) + 0.1875*(Table1[[#This Row],[attacking_crossing]]/100)))^2))  * ((1 - (Table1[[#This Row],[mentality_vision]]/100))^2))</f>
+        <v>2.61252132515625</v>
+      </c>
+      <c r="DL88">
+        <f>1.585332 + 0.008219*Table1[[#This Row],[power_jumping]]+ 0.047559*Table1[[#This Row],[pace]] + 0.012348*Table1[[#This Row],[attacking_heading_accuracy]] + 0.362187*Table1[[#This Row],[develle_mcharo_passing]] + 0.015238*Table1[[#This Row],[dribbling]] + 0.189748*Table1[[#This Row],[weak_foot]] + 0.033917*Table1[[#This Row],[power_strength]] + 0.26019*Table1[[#This Row],[skill_moves]] + 0.808787*Table1[[#This Row],[Defender]] + 0.472467*Table1[[#This Row],[Midfielder]] + 0.081427*Table1[[#This Row],[Finesse_Shot]]</f>
+        <v>13.469280261194367</v>
+      </c>
     </row>
-    <row r="89" spans="1:114" x14ac:dyDescent="0.2">
+    <row r="89" spans="1:116" x14ac:dyDescent="0.2">
       <c r="A89">
         <v>205175</v>
       </c>
@@ -32448,8 +33168,16 @@
       <c r="DJ89" t="s">
         <v>797</v>
       </c>
+      <c r="DK89">
+        <f xml:space="preserve"> (Table1[[#This Row],[mentality_vision]]/100) + 0.809*(Table1[[#This Row],[skill_curve]]/100) + (0.75*(Table1[[#This Row],[attacking_short_passing]]/100) + 0.25*(Table1[[#This Row],[attacking_crossing]]/100)) + (0.625*(Table1[[#This Row],[skill_long_passing]]/100) + 0.1875*(Table1[[#This Row],[skill_fk_accuracy]]/100) + 0.1875*(Table1[[#This Row],[attacking_crossing]]/100)) - ((1 - ((0.75*(Table1[[#This Row],[attacking_short_passing]]/100) + 0.25*(Table1[[#This Row],[attacking_crossing]]/100) - (0.625*(Table1[[#This Row],[skill_long_passing]]/100) + 0.1875*(Table1[[#This Row],[skill_fk_accuracy]]/100) + 0.1875*(Table1[[#This Row],[attacking_crossing]]/100)))^2))  * ((1 - (Table1[[#This Row],[mentality_vision]]/100))^2))</f>
+        <v>2.736561</v>
+      </c>
+      <c r="DL89">
+        <f>1.585332 + 0.008219*Table1[[#This Row],[power_jumping]]+ 0.047559*Table1[[#This Row],[pace]] + 0.012348*Table1[[#This Row],[attacking_heading_accuracy]] + 0.362187*Table1[[#This Row],[develle_mcharo_passing]] + 0.015238*Table1[[#This Row],[dribbling]] + 0.189748*Table1[[#This Row],[weak_foot]] + 0.033917*Table1[[#This Row],[power_strength]] + 0.26019*Table1[[#This Row],[skill_moves]] + 0.808787*Table1[[#This Row],[Defender]] + 0.472467*Table1[[#This Row],[Midfielder]] + 0.081427*Table1[[#This Row],[Finesse_Shot]]</f>
+        <v>11.762360818906998</v>
+      </c>
     </row>
-    <row r="90" spans="1:114" x14ac:dyDescent="0.2">
+    <row r="90" spans="1:116" x14ac:dyDescent="0.2">
       <c r="A90">
         <v>277846</v>
       </c>
@@ -32772,8 +33500,16 @@
       <c r="DJ90" t="s">
         <v>802</v>
       </c>
+      <c r="DK90">
+        <f xml:space="preserve"> (Table1[[#This Row],[mentality_vision]]/100) + 0.809*(Table1[[#This Row],[skill_curve]]/100) + (0.75*(Table1[[#This Row],[attacking_short_passing]]/100) + 0.25*(Table1[[#This Row],[attacking_crossing]]/100)) + (0.625*(Table1[[#This Row],[skill_long_passing]]/100) + 0.1875*(Table1[[#This Row],[skill_fk_accuracy]]/100) + 0.1875*(Table1[[#This Row],[attacking_crossing]]/100)) - ((1 - ((0.75*(Table1[[#This Row],[attacking_short_passing]]/100) + 0.25*(Table1[[#This Row],[attacking_crossing]]/100) - (0.625*(Table1[[#This Row],[skill_long_passing]]/100) + 0.1875*(Table1[[#This Row],[skill_fk_accuracy]]/100) + 0.1875*(Table1[[#This Row],[attacking_crossing]]/100)))^2))  * ((1 - (Table1[[#This Row],[mentality_vision]]/100))^2))</f>
+        <v>2.7919934025000002</v>
+      </c>
+      <c r="DL90">
+        <f>1.585332 + 0.008219*Table1[[#This Row],[power_jumping]]+ 0.047559*Table1[[#This Row],[pace]] + 0.012348*Table1[[#This Row],[attacking_heading_accuracy]] + 0.362187*Table1[[#This Row],[develle_mcharo_passing]] + 0.015238*Table1[[#This Row],[dribbling]] + 0.189748*Table1[[#This Row],[weak_foot]] + 0.033917*Table1[[#This Row],[power_strength]] + 0.26019*Table1[[#This Row],[skill_moves]] + 0.808787*Table1[[#This Row],[Defender]] + 0.472467*Table1[[#This Row],[Midfielder]] + 0.081427*Table1[[#This Row],[Finesse_Shot]]</f>
+        <v>13.101470714471267</v>
+      </c>
     </row>
-    <row r="91" spans="1:114" x14ac:dyDescent="0.2">
+    <row r="91" spans="1:116" x14ac:dyDescent="0.2">
       <c r="A91">
         <v>223671</v>
       </c>
@@ -33093,8 +33829,16 @@
       <c r="DJ91" t="s">
         <v>808</v>
       </c>
+      <c r="DK91">
+        <f xml:space="preserve"> (Table1[[#This Row],[mentality_vision]]/100) + 0.809*(Table1[[#This Row],[skill_curve]]/100) + (0.75*(Table1[[#This Row],[attacking_short_passing]]/100) + 0.25*(Table1[[#This Row],[attacking_crossing]]/100)) + (0.625*(Table1[[#This Row],[skill_long_passing]]/100) + 0.1875*(Table1[[#This Row],[skill_fk_accuracy]]/100) + 0.1875*(Table1[[#This Row],[attacking_crossing]]/100)) - ((1 - ((0.75*(Table1[[#This Row],[attacking_short_passing]]/100) + 0.25*(Table1[[#This Row],[attacking_crossing]]/100) - (0.625*(Table1[[#This Row],[skill_long_passing]]/100) + 0.1875*(Table1[[#This Row],[skill_fk_accuracy]]/100) + 0.1875*(Table1[[#This Row],[attacking_crossing]]/100)))^2))  * ((1 - (Table1[[#This Row],[mentality_vision]]/100))^2))</f>
+        <v>2.2708558164062498</v>
+      </c>
+      <c r="DL91">
+        <f>1.585332 + 0.008219*Table1[[#This Row],[power_jumping]]+ 0.047559*Table1[[#This Row],[pace]] + 0.012348*Table1[[#This Row],[attacking_heading_accuracy]] + 0.362187*Table1[[#This Row],[develle_mcharo_passing]] + 0.015238*Table1[[#This Row],[dribbling]] + 0.189748*Table1[[#This Row],[weak_foot]] + 0.033917*Table1[[#This Row],[power_strength]] + 0.26019*Table1[[#This Row],[skill_moves]] + 0.808787*Table1[[#This Row],[Defender]] + 0.472467*Table1[[#This Row],[Midfielder]] + 0.081427*Table1[[#This Row],[Finesse_Shot]]</f>
+        <v>13.109080455576731</v>
+      </c>
     </row>
-    <row r="92" spans="1:114" x14ac:dyDescent="0.2">
+    <row r="92" spans="1:116" x14ac:dyDescent="0.2">
       <c r="A92">
         <v>261050</v>
       </c>
@@ -33429,8 +34173,16 @@
       <c r="DJ92" t="s">
         <v>814</v>
       </c>
+      <c r="DK92">
+        <f xml:space="preserve"> (Table1[[#This Row],[mentality_vision]]/100) + 0.809*(Table1[[#This Row],[skill_curve]]/100) + (0.75*(Table1[[#This Row],[attacking_short_passing]]/100) + 0.25*(Table1[[#This Row],[attacking_crossing]]/100)) + (0.625*(Table1[[#This Row],[skill_long_passing]]/100) + 0.1875*(Table1[[#This Row],[skill_fk_accuracy]]/100) + 0.1875*(Table1[[#This Row],[attacking_crossing]]/100)) - ((1 - ((0.75*(Table1[[#This Row],[attacking_short_passing]]/100) + 0.25*(Table1[[#This Row],[attacking_crossing]]/100) - (0.625*(Table1[[#This Row],[skill_long_passing]]/100) + 0.1875*(Table1[[#This Row],[skill_fk_accuracy]]/100) + 0.1875*(Table1[[#This Row],[attacking_crossing]]/100)))^2))  * ((1 - (Table1[[#This Row],[mentality_vision]]/100))^2))</f>
+        <v>2.756999225625</v>
+      </c>
+      <c r="DL92">
+        <f>1.585332 + 0.008219*Table1[[#This Row],[power_jumping]]+ 0.047559*Table1[[#This Row],[pace]] + 0.012348*Table1[[#This Row],[attacking_heading_accuracy]] + 0.362187*Table1[[#This Row],[develle_mcharo_passing]] + 0.015238*Table1[[#This Row],[dribbling]] + 0.189748*Table1[[#This Row],[weak_foot]] + 0.033917*Table1[[#This Row],[power_strength]] + 0.26019*Table1[[#This Row],[skill_moves]] + 0.808787*Table1[[#This Row],[Defender]] + 0.472467*Table1[[#This Row],[Midfielder]] + 0.081427*Table1[[#This Row],[Finesse_Shot]]</f>
+        <v>11.821072278531442</v>
+      </c>
     </row>
-    <row r="93" spans="1:114" x14ac:dyDescent="0.2">
+    <row r="93" spans="1:116" x14ac:dyDescent="0.2">
       <c r="A93">
         <v>239763</v>
       </c>
@@ -33756,8 +34508,16 @@
       <c r="DJ93" t="s">
         <v>819</v>
       </c>
+      <c r="DK93">
+        <f xml:space="preserve"> (Table1[[#This Row],[mentality_vision]]/100) + 0.809*(Table1[[#This Row],[skill_curve]]/100) + (0.75*(Table1[[#This Row],[attacking_short_passing]]/100) + 0.25*(Table1[[#This Row],[attacking_crossing]]/100)) + (0.625*(Table1[[#This Row],[skill_long_passing]]/100) + 0.1875*(Table1[[#This Row],[skill_fk_accuracy]]/100) + 0.1875*(Table1[[#This Row],[attacking_crossing]]/100)) - ((1 - ((0.75*(Table1[[#This Row],[attacking_short_passing]]/100) + 0.25*(Table1[[#This Row],[attacking_crossing]]/100) - (0.625*(Table1[[#This Row],[skill_long_passing]]/100) + 0.1875*(Table1[[#This Row],[skill_fk_accuracy]]/100) + 0.1875*(Table1[[#This Row],[attacking_crossing]]/100)))^2))  * ((1 - (Table1[[#This Row],[mentality_vision]]/100))^2))</f>
+        <v>2.8680755506250004</v>
+      </c>
+      <c r="DL93">
+        <f>1.585332 + 0.008219*Table1[[#This Row],[power_jumping]]+ 0.047559*Table1[[#This Row],[pace]] + 0.012348*Table1[[#This Row],[attacking_heading_accuracy]] + 0.362187*Table1[[#This Row],[develle_mcharo_passing]] + 0.015238*Table1[[#This Row],[dribbling]] + 0.189748*Table1[[#This Row],[weak_foot]] + 0.033917*Table1[[#This Row],[power_strength]] + 0.26019*Table1[[#This Row],[skill_moves]] + 0.808787*Table1[[#This Row],[Defender]] + 0.472467*Table1[[#This Row],[Midfielder]] + 0.081427*Table1[[#This Row],[Finesse_Shot]]</f>
+        <v>12.539733679454216</v>
+      </c>
     </row>
-    <row r="94" spans="1:114" x14ac:dyDescent="0.2">
+    <row r="94" spans="1:116" x14ac:dyDescent="0.2">
       <c r="A94">
         <v>226710</v>
       </c>
@@ -34083,8 +34843,16 @@
       <c r="DJ94" t="s">
         <v>825</v>
       </c>
+      <c r="DK94">
+        <f xml:space="preserve"> (Table1[[#This Row],[mentality_vision]]/100) + 0.809*(Table1[[#This Row],[skill_curve]]/100) + (0.75*(Table1[[#This Row],[attacking_short_passing]]/100) + 0.25*(Table1[[#This Row],[attacking_crossing]]/100)) + (0.625*(Table1[[#This Row],[skill_long_passing]]/100) + 0.1875*(Table1[[#This Row],[skill_fk_accuracy]]/100) + 0.1875*(Table1[[#This Row],[attacking_crossing]]/100)) - ((1 - ((0.75*(Table1[[#This Row],[attacking_short_passing]]/100) + 0.25*(Table1[[#This Row],[attacking_crossing]]/100) - (0.625*(Table1[[#This Row],[skill_long_passing]]/100) + 0.1875*(Table1[[#This Row],[skill_fk_accuracy]]/100) + 0.1875*(Table1[[#This Row],[attacking_crossing]]/100)))^2))  * ((1 - (Table1[[#This Row],[mentality_vision]]/100))^2))</f>
+        <v>2.5041625624999995</v>
+      </c>
+      <c r="DL94">
+        <f>1.585332 + 0.008219*Table1[[#This Row],[power_jumping]]+ 0.047559*Table1[[#This Row],[pace]] + 0.012348*Table1[[#This Row],[attacking_heading_accuracy]] + 0.362187*Table1[[#This Row],[develle_mcharo_passing]] + 0.015238*Table1[[#This Row],[dribbling]] + 0.189748*Table1[[#This Row],[weak_foot]] + 0.033917*Table1[[#This Row],[power_strength]] + 0.26019*Table1[[#This Row],[skill_moves]] + 0.808787*Table1[[#This Row],[Defender]] + 0.472467*Table1[[#This Row],[Midfielder]] + 0.081427*Table1[[#This Row],[Finesse_Shot]]</f>
+        <v>12.607897126024188</v>
+      </c>
     </row>
-    <row r="95" spans="1:114" x14ac:dyDescent="0.2">
+    <row r="95" spans="1:116" x14ac:dyDescent="0.2">
       <c r="A95">
         <v>208165</v>
       </c>
@@ -34407,8 +35175,16 @@
       <c r="DJ95" t="s">
         <v>831</v>
       </c>
+      <c r="DK95">
+        <f xml:space="preserve"> (Table1[[#This Row],[mentality_vision]]/100) + 0.809*(Table1[[#This Row],[skill_curve]]/100) + (0.75*(Table1[[#This Row],[attacking_short_passing]]/100) + 0.25*(Table1[[#This Row],[attacking_crossing]]/100)) + (0.625*(Table1[[#This Row],[skill_long_passing]]/100) + 0.1875*(Table1[[#This Row],[skill_fk_accuracy]]/100) + 0.1875*(Table1[[#This Row],[attacking_crossing]]/100)) - ((1 - ((0.75*(Table1[[#This Row],[attacking_short_passing]]/100) + 0.25*(Table1[[#This Row],[attacking_crossing]]/100) - (0.625*(Table1[[#This Row],[skill_long_passing]]/100) + 0.1875*(Table1[[#This Row],[skill_fk_accuracy]]/100) + 0.1875*(Table1[[#This Row],[attacking_crossing]]/100)))^2))  * ((1 - (Table1[[#This Row],[mentality_vision]]/100))^2))</f>
+        <v>1.9531832656250003</v>
+      </c>
+      <c r="DL95">
+        <f>1.585332 + 0.008219*Table1[[#This Row],[power_jumping]]+ 0.047559*Table1[[#This Row],[pace]] + 0.012348*Table1[[#This Row],[attacking_heading_accuracy]] + 0.362187*Table1[[#This Row],[develle_mcharo_passing]] + 0.015238*Table1[[#This Row],[dribbling]] + 0.189748*Table1[[#This Row],[weak_foot]] + 0.033917*Table1[[#This Row],[power_strength]] + 0.26019*Table1[[#This Row],[skill_moves]] + 0.808787*Table1[[#This Row],[Defender]] + 0.472467*Table1[[#This Row],[Midfielder]] + 0.081427*Table1[[#This Row],[Finesse_Shot]]</f>
+        <v>12.412577587426922</v>
+      </c>
     </row>
-    <row r="96" spans="1:114" x14ac:dyDescent="0.2">
+    <row r="96" spans="1:116" x14ac:dyDescent="0.2">
       <c r="A96">
         <v>238744</v>
       </c>
@@ -34740,8 +35516,16 @@
       <c r="DJ96" t="s">
         <v>837</v>
       </c>
+      <c r="DK96">
+        <f xml:space="preserve"> (Table1[[#This Row],[mentality_vision]]/100) + 0.809*(Table1[[#This Row],[skill_curve]]/100) + (0.75*(Table1[[#This Row],[attacking_short_passing]]/100) + 0.25*(Table1[[#This Row],[attacking_crossing]]/100)) + (0.625*(Table1[[#This Row],[skill_long_passing]]/100) + 0.1875*(Table1[[#This Row],[skill_fk_accuracy]]/100) + 0.1875*(Table1[[#This Row],[attacking_crossing]]/100)) - ((1 - ((0.75*(Table1[[#This Row],[attacking_short_passing]]/100) + 0.25*(Table1[[#This Row],[attacking_crossing]]/100) - (0.625*(Table1[[#This Row],[skill_long_passing]]/100) + 0.1875*(Table1[[#This Row],[skill_fk_accuracy]]/100) + 0.1875*(Table1[[#This Row],[attacking_crossing]]/100)))^2))  * ((1 - (Table1[[#This Row],[mentality_vision]]/100))^2))</f>
+        <v>2.8510230625000004</v>
+      </c>
+      <c r="DL96">
+        <f>1.585332 + 0.008219*Table1[[#This Row],[power_jumping]]+ 0.047559*Table1[[#This Row],[pace]] + 0.012348*Table1[[#This Row],[attacking_heading_accuracy]] + 0.362187*Table1[[#This Row],[develle_mcharo_passing]] + 0.015238*Table1[[#This Row],[dribbling]] + 0.189748*Table1[[#This Row],[weak_foot]] + 0.033917*Table1[[#This Row],[power_strength]] + 0.26019*Table1[[#This Row],[skill_moves]] + 0.808787*Table1[[#This Row],[Defender]] + 0.472467*Table1[[#This Row],[Midfielder]] + 0.081427*Table1[[#This Row],[Finesse_Shot]]</f>
+        <v>13.697051489937687</v>
+      </c>
     </row>
-    <row r="97" spans="1:114" x14ac:dyDescent="0.2">
+    <row r="97" spans="1:116" x14ac:dyDescent="0.2">
       <c r="A97">
         <v>242280</v>
       </c>
@@ -35073,8 +35857,16 @@
       <c r="DJ97" t="s">
         <v>841</v>
       </c>
+      <c r="DK97">
+        <f xml:space="preserve"> (Table1[[#This Row],[mentality_vision]]/100) + 0.809*(Table1[[#This Row],[skill_curve]]/100) + (0.75*(Table1[[#This Row],[attacking_short_passing]]/100) + 0.25*(Table1[[#This Row],[attacking_crossing]]/100)) + (0.625*(Table1[[#This Row],[skill_long_passing]]/100) + 0.1875*(Table1[[#This Row],[skill_fk_accuracy]]/100) + 0.1875*(Table1[[#This Row],[attacking_crossing]]/100)) - ((1 - ((0.75*(Table1[[#This Row],[attacking_short_passing]]/100) + 0.25*(Table1[[#This Row],[attacking_crossing]]/100) - (0.625*(Table1[[#This Row],[skill_long_passing]]/100) + 0.1875*(Table1[[#This Row],[skill_fk_accuracy]]/100) + 0.1875*(Table1[[#This Row],[attacking_crossing]]/100)))^2))  * ((1 - (Table1[[#This Row],[mentality_vision]]/100))^2))</f>
+        <v>2.7469256100000004</v>
+      </c>
+      <c r="DL97">
+        <f>1.585332 + 0.008219*Table1[[#This Row],[power_jumping]]+ 0.047559*Table1[[#This Row],[pace]] + 0.012348*Table1[[#This Row],[attacking_heading_accuracy]] + 0.362187*Table1[[#This Row],[develle_mcharo_passing]] + 0.015238*Table1[[#This Row],[dribbling]] + 0.189748*Table1[[#This Row],[weak_foot]] + 0.033917*Table1[[#This Row],[power_strength]] + 0.26019*Table1[[#This Row],[skill_moves]] + 0.808787*Table1[[#This Row],[Defender]] + 0.472467*Table1[[#This Row],[Midfielder]] + 0.081427*Table1[[#This Row],[Finesse_Shot]]</f>
+        <v>13.183450745909068</v>
+      </c>
     </row>
-    <row r="98" spans="1:114" x14ac:dyDescent="0.2">
+    <row r="98" spans="1:116" x14ac:dyDescent="0.2">
       <c r="A98">
         <v>201389</v>
       </c>
@@ -35397,8 +36189,16 @@
       <c r="DJ98" t="s">
         <v>846</v>
       </c>
+      <c r="DK98">
+        <f xml:space="preserve"> (Table1[[#This Row],[mentality_vision]]/100) + 0.809*(Table1[[#This Row],[skill_curve]]/100) + (0.75*(Table1[[#This Row],[attacking_short_passing]]/100) + 0.25*(Table1[[#This Row],[attacking_crossing]]/100)) + (0.625*(Table1[[#This Row],[skill_long_passing]]/100) + 0.1875*(Table1[[#This Row],[skill_fk_accuracy]]/100) + 0.1875*(Table1[[#This Row],[attacking_crossing]]/100)) - ((1 - ((0.75*(Table1[[#This Row],[attacking_short_passing]]/100) + 0.25*(Table1[[#This Row],[attacking_crossing]]/100) - (0.625*(Table1[[#This Row],[skill_long_passing]]/100) + 0.1875*(Table1[[#This Row],[skill_fk_accuracy]]/100) + 0.1875*(Table1[[#This Row],[attacking_crossing]]/100)))^2))  * ((1 - (Table1[[#This Row],[mentality_vision]]/100))^2))</f>
+        <v>2.8881057656249998</v>
+      </c>
+      <c r="DL98">
+        <f>1.585332 + 0.008219*Table1[[#This Row],[power_jumping]]+ 0.047559*Table1[[#This Row],[pace]] + 0.012348*Table1[[#This Row],[attacking_heading_accuracy]] + 0.362187*Table1[[#This Row],[develle_mcharo_passing]] + 0.015238*Table1[[#This Row],[dribbling]] + 0.189748*Table1[[#This Row],[weak_foot]] + 0.033917*Table1[[#This Row],[power_strength]] + 0.26019*Table1[[#This Row],[skill_moves]] + 0.808787*Table1[[#This Row],[Defender]] + 0.472467*Table1[[#This Row],[Midfielder]] + 0.081427*Table1[[#This Row],[Finesse_Shot]]</f>
+        <v>13.09161036293442</v>
+      </c>
     </row>
-    <row r="99" spans="1:114" x14ac:dyDescent="0.2">
+    <row r="99" spans="1:116" x14ac:dyDescent="0.2">
       <c r="A99">
         <v>251530</v>
       </c>
@@ -35721,8 +36521,16 @@
       <c r="DJ99" t="s">
         <v>851</v>
       </c>
+      <c r="DK99">
+        <f xml:space="preserve"> (Table1[[#This Row],[mentality_vision]]/100) + 0.809*(Table1[[#This Row],[skill_curve]]/100) + (0.75*(Table1[[#This Row],[attacking_short_passing]]/100) + 0.25*(Table1[[#This Row],[attacking_crossing]]/100)) + (0.625*(Table1[[#This Row],[skill_long_passing]]/100) + 0.1875*(Table1[[#This Row],[skill_fk_accuracy]]/100) + 0.1875*(Table1[[#This Row],[attacking_crossing]]/100)) - ((1 - ((0.75*(Table1[[#This Row],[attacking_short_passing]]/100) + 0.25*(Table1[[#This Row],[attacking_crossing]]/100) - (0.625*(Table1[[#This Row],[skill_long_passing]]/100) + 0.1875*(Table1[[#This Row],[skill_fk_accuracy]]/100) + 0.1875*(Table1[[#This Row],[attacking_crossing]]/100)))^2))  * ((1 - (Table1[[#This Row],[mentality_vision]]/100))^2))</f>
+        <v>2.5814584056249998</v>
+      </c>
+      <c r="DL99">
+        <f>1.585332 + 0.008219*Table1[[#This Row],[power_jumping]]+ 0.047559*Table1[[#This Row],[pace]] + 0.012348*Table1[[#This Row],[attacking_heading_accuracy]] + 0.362187*Table1[[#This Row],[develle_mcharo_passing]] + 0.015238*Table1[[#This Row],[dribbling]] + 0.189748*Table1[[#This Row],[weak_foot]] + 0.033917*Table1[[#This Row],[power_strength]] + 0.26019*Table1[[#This Row],[skill_moves]] + 0.808787*Table1[[#This Row],[Defender]] + 0.472467*Table1[[#This Row],[Midfielder]] + 0.081427*Table1[[#This Row],[Finesse_Shot]]</f>
+        <v>14.274634675558099</v>
+      </c>
     </row>
-    <row r="100" spans="1:114" x14ac:dyDescent="0.2">
+    <row r="100" spans="1:116" x14ac:dyDescent="0.2">
       <c r="A100">
         <v>202884</v>
       </c>
@@ -36045,8 +36853,16 @@
       <c r="DJ100" t="s">
         <v>855</v>
       </c>
+      <c r="DK100">
+        <f xml:space="preserve"> (Table1[[#This Row],[mentality_vision]]/100) + 0.809*(Table1[[#This Row],[skill_curve]]/100) + (0.75*(Table1[[#This Row],[attacking_short_passing]]/100) + 0.25*(Table1[[#This Row],[attacking_crossing]]/100)) + (0.625*(Table1[[#This Row],[skill_long_passing]]/100) + 0.1875*(Table1[[#This Row],[skill_fk_accuracy]]/100) + 0.1875*(Table1[[#This Row],[attacking_crossing]]/100)) - ((1 - ((0.75*(Table1[[#This Row],[attacking_short_passing]]/100) + 0.25*(Table1[[#This Row],[attacking_crossing]]/100) - (0.625*(Table1[[#This Row],[skill_long_passing]]/100) + 0.1875*(Table1[[#This Row],[skill_fk_accuracy]]/100) + 0.1875*(Table1[[#This Row],[attacking_crossing]]/100)))^2))  * ((1 - (Table1[[#This Row],[mentality_vision]]/100))^2))</f>
+        <v>2.6383176506249999</v>
+      </c>
+      <c r="DL100">
+        <f>1.585332 + 0.008219*Table1[[#This Row],[power_jumping]]+ 0.047559*Table1[[#This Row],[pace]] + 0.012348*Table1[[#This Row],[attacking_heading_accuracy]] + 0.362187*Table1[[#This Row],[develle_mcharo_passing]] + 0.015238*Table1[[#This Row],[dribbling]] + 0.189748*Table1[[#This Row],[weak_foot]] + 0.033917*Table1[[#This Row],[power_strength]] + 0.26019*Table1[[#This Row],[skill_moves]] + 0.808787*Table1[[#This Row],[Defender]] + 0.472467*Table1[[#This Row],[Midfielder]] + 0.081427*Table1[[#This Row],[Finesse_Shot]]</f>
+        <v>14.016710354926916</v>
+      </c>
     </row>
-    <row r="101" spans="1:114" x14ac:dyDescent="0.2">
+    <row r="101" spans="1:116" x14ac:dyDescent="0.2">
       <c r="A101">
         <v>224031</v>
       </c>
@@ -36368,6 +37184,14 @@
       </c>
       <c r="DJ101" t="s">
         <v>861</v>
+      </c>
+      <c r="DK101">
+        <f xml:space="preserve"> (Table1[[#This Row],[mentality_vision]]/100) + 0.809*(Table1[[#This Row],[skill_curve]]/100) + (0.75*(Table1[[#This Row],[attacking_short_passing]]/100) + 0.25*(Table1[[#This Row],[attacking_crossing]]/100)) + (0.625*(Table1[[#This Row],[skill_long_passing]]/100) + 0.1875*(Table1[[#This Row],[skill_fk_accuracy]]/100) + 0.1875*(Table1[[#This Row],[attacking_crossing]]/100)) - ((1 - ((0.75*(Table1[[#This Row],[attacking_short_passing]]/100) + 0.25*(Table1[[#This Row],[attacking_crossing]]/100) - (0.625*(Table1[[#This Row],[skill_long_passing]]/100) + 0.1875*(Table1[[#This Row],[skill_fk_accuracy]]/100) + 0.1875*(Table1[[#This Row],[attacking_crossing]]/100)))^2))  * ((1 - (Table1[[#This Row],[mentality_vision]]/100))^2))</f>
+        <v>2.367756</v>
+      </c>
+      <c r="DL101">
+        <f>1.585332 + 0.008219*Table1[[#This Row],[power_jumping]]+ 0.047559*Table1[[#This Row],[pace]] + 0.012348*Table1[[#This Row],[attacking_heading_accuracy]] + 0.362187*Table1[[#This Row],[develle_mcharo_passing]] + 0.015238*Table1[[#This Row],[dribbling]] + 0.189748*Table1[[#This Row],[weak_foot]] + 0.033917*Table1[[#This Row],[power_strength]] + 0.26019*Table1[[#This Row],[skill_moves]] + 0.808787*Table1[[#This Row],[Defender]] + 0.472467*Table1[[#This Row],[Midfielder]] + 0.081427*Table1[[#This Row],[Finesse_Shot]]</f>
+        <v>13.955778442371999</v>
       </c>
     </row>
   </sheetData>
